--- a/STG.CO.xlsx
+++ b/STG.CO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC5F035-28ED-49CA-8C83-6A159FA6A586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D02019-B52D-417F-9279-96B61A21D55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{BD75BBDC-C4FD-4EC4-8461-B3C83FDDB12A}"/>
+    <workbookView xWindow="225" yWindow="3900" windowWidth="38175" windowHeight="15240" xr2:uid="{BD75BBDC-C4FD-4EC4-8461-B3C83FDDB12A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -679,7 +679,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0;[Red]#,##0.0"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -768,12 +768,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1008,7 +1002,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1136,7 +1130,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2582,7 +2575,7 @@
       <c r="E11" s="6">
         <v>1304.5</v>
       </c>
-      <c r="F11" s="81">
+      <c r="F11" s="6">
         <f>+S11-SUM(C11:E11)</f>
         <v>1295.4000000000005</v>
       </c>
@@ -2710,27 +2703,27 @@
         <v>3200.9</v>
       </c>
       <c r="N12" s="6">
-        <f>+N10-N11</f>
+        <f t="shared" ref="N12:S12" si="2">+N10-N11</f>
         <v>3142.5</v>
       </c>
       <c r="O12" s="6">
-        <f>+O10-O11</f>
+        <f t="shared" si="2"/>
         <v>3712.2</v>
       </c>
       <c r="P12" s="6">
-        <f>+P10-P11</f>
+        <f t="shared" si="2"/>
         <v>4113.1000000000004</v>
       </c>
       <c r="Q12" s="6">
-        <f>+Q10-Q11</f>
+        <f t="shared" si="2"/>
         <v>4307.3000000000011</v>
       </c>
       <c r="R12" s="6">
-        <f>+R10-R11</f>
+        <f t="shared" si="2"/>
         <v>4204.0999999999995</v>
       </c>
       <c r="S12" s="6">
-        <f>+S10-S11</f>
+        <f t="shared" si="2"/>
         <v>4278.5</v>
       </c>
       <c r="T12" s="6"/>
@@ -2792,7 +2785,7 @@
       <c r="E13" s="6">
         <v>293.8</v>
       </c>
-      <c r="F13" s="81">
+      <c r="F13" s="6">
         <f>+S13-SUM(C13:E13)</f>
         <v>312.59999999999991</v>
       </c>
@@ -2890,7 +2883,7 @@
       <c r="E14" s="6">
         <v>272.89999999999998</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="6">
         <f>+S14-SUM(C14:E14)</f>
         <v>274.20000000000005</v>
       </c>
@@ -2988,7 +2981,7 @@
       <c r="E15" s="6">
         <v>8.4</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="6">
         <f>+S15-SUM(C15:E15)</f>
         <v>20.699999999999996</v>
       </c>
@@ -3089,7 +3082,7 @@
         <f>68.9+48.9+48.8</f>
         <v>166.60000000000002</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="6">
         <f>+S16-SUM(C16:E16)</f>
         <v>254.2999999999999</v>
       </c>
@@ -3190,23 +3183,23 @@
         <v>26</v>
       </c>
       <c r="C17" s="6">
-        <f t="shared" ref="C17:G17" si="2">+C12-SUM(C13:C14,C16)+C15</f>
+        <f t="shared" ref="C17:G17" si="3">+C12-SUM(C13:C14,C16)+C15</f>
         <v>208.00000000000009</v>
       </c>
       <c r="D17" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>429.40000000000026</v>
       </c>
       <c r="E17" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>401.09999999999991</v>
       </c>
       <c r="F17" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>341.69999999999953</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>135.90000000000006</v>
       </c>
       <c r="H17" s="6">
@@ -3224,31 +3217,31 @@
         <v>913.00000000000034</v>
       </c>
       <c r="M17" s="6">
-        <f t="shared" ref="L17:S17" si="3">+M12-SUM(M13:M14,M16)+M15</f>
+        <f t="shared" ref="M17:S17" si="4">+M12-SUM(M13:M14,M16)+M15</f>
         <v>737.50000000000045</v>
       </c>
       <c r="N17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>977.20000000000016</v>
       </c>
       <c r="O17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>985.59999999999991</v>
       </c>
       <c r="P17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1814.2000000000003</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1953.0000000000009</v>
       </c>
       <c r="R17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1638.2999999999995</v>
       </c>
       <c r="S17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1380.1999999999998</v>
       </c>
       <c r="T17" s="6"/>
@@ -3310,7 +3303,7 @@
       <c r="E18" s="6">
         <v>7.5</v>
       </c>
-      <c r="F18" s="81">
+      <c r="F18" s="6">
         <f>+S18-SUM(C18:E18)</f>
         <v>4.5</v>
       </c>
@@ -3408,7 +3401,7 @@
       <c r="E19" s="6">
         <v>52.8</v>
       </c>
-      <c r="F19" s="81">
+      <c r="F19" s="6">
         <f>+S19-SUM(C19:E19)</f>
         <v>46.399999999999991</v>
       </c>
@@ -3506,7 +3499,7 @@
       <c r="E20" s="6">
         <v>78.400000000000006</v>
       </c>
-      <c r="F20" s="81">
+      <c r="F20" s="6">
         <f>+S20-SUM(C20:E20)</f>
         <v>100.29999999999998</v>
       </c>
@@ -3596,23 +3589,23 @@
         <v>30</v>
       </c>
       <c r="C21" s="6">
-        <f t="shared" ref="C21:G21" si="4">+C17+C18+C19-C20</f>
+        <f t="shared" ref="C21:G21" si="5">+C17+C18+C19-C20</f>
         <v>158.90000000000009</v>
       </c>
       <c r="D21" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>385.10000000000025</v>
       </c>
       <c r="E21" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>382.99999999999989</v>
       </c>
       <c r="F21" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>292.2999999999995</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>66.900000000000063</v>
       </c>
       <c r="H21" s="6">
@@ -3626,35 +3619,35 @@
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6">
-        <f t="shared" ref="L21:S21" si="5">+L17+L18+L19-L20</f>
+        <f t="shared" ref="L21:S21" si="6">+L17+L18+L19-L20</f>
         <v>851.70000000000039</v>
       </c>
       <c r="M21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>716.80000000000052</v>
       </c>
       <c r="N21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>948.60000000000025</v>
       </c>
       <c r="O21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>951.39999999999986</v>
       </c>
       <c r="P21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1768.5000000000002</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1856.5000000000011</v>
       </c>
       <c r="R21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1490.7999999999995</v>
       </c>
       <c r="S21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1219.3</v>
       </c>
       <c r="T21" s="6"/>
@@ -3716,7 +3709,7 @@
       <c r="E22" s="6">
         <v>85.9</v>
       </c>
-      <c r="F22" s="81">
+      <c r="F22" s="6">
         <f>+S22-SUM(C22:E22)</f>
         <v>71.300000000000011</v>
       </c>
@@ -3806,23 +3799,23 @@
         <v>32</v>
       </c>
       <c r="C23" s="6">
-        <f t="shared" ref="C23:G23" si="6">+C21-C22</f>
+        <f t="shared" ref="C23:G23" si="7">+C21-C22</f>
         <v>124.8000000000001</v>
       </c>
       <c r="D23" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>296.80000000000024</v>
       </c>
       <c r="E23" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>297.09999999999991</v>
       </c>
       <c r="F23" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>220.99999999999949</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>51.500000000000064</v>
       </c>
       <c r="H23" s="6">
@@ -3836,31 +3829,31 @@
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6">
-        <f t="shared" ref="L23:R23" si="7">+L21-L22</f>
+        <f t="shared" ref="L23:R23" si="8">+L21-L22</f>
         <v>711.60000000000036</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>665.50000000000057</v>
       </c>
       <c r="N23" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>747.70000000000027</v>
       </c>
       <c r="O23" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>677.89999999999986</v>
       </c>
       <c r="P23" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1390.6000000000004</v>
       </c>
       <c r="Q23" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1476.3000000000011</v>
       </c>
       <c r="R23" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1182.3999999999996</v>
       </c>
       <c r="S23" s="6">
@@ -3982,19 +3975,19 @@
         <v>33</v>
       </c>
       <c r="C25" s="6">
-        <f t="shared" ref="C25:F25" si="8">+C23/C26</f>
+        <f t="shared" ref="C25:F25" si="9">+C23/C26</f>
         <v>1.4618204818853746</v>
       </c>
       <c r="D25" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.5185053465158767</v>
       </c>
       <c r="E25" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.5759421301589964</v>
       </c>
       <c r="F25" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.6898079404104025</v>
       </c>
       <c r="G25" s="6">
@@ -4002,44 +3995,44 @@
         <v>0.65323000038052315</v>
       </c>
       <c r="H25" s="6">
-        <f t="shared" ref="H25:J25" si="9">+H23/H26</f>
+        <f t="shared" ref="H25:J25" si="10">+H23/H26</f>
         <v>2.8787014139876979</v>
       </c>
       <c r="I25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.8817749603803517</v>
       </c>
       <c r="J25" s="6" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="6">
-        <f t="shared" ref="L25:P25" si="10">+L23/L26</f>
+        <f t="shared" ref="L25:O25" si="11">+L23/L26</f>
         <v>7.1160000000000032</v>
       </c>
       <c r="M25" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.6681362283698942</v>
       </c>
       <c r="N25" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7.4814888933360049</v>
       </c>
       <c r="O25" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.8021954866093362</v>
       </c>
       <c r="P25" s="6">
-        <f t="shared" ref="P25:R25" si="11">+P23/P26</f>
+        <f t="shared" ref="P25:R25" si="12">+P23/P26</f>
         <v>14.532495898170119</v>
       </c>
       <c r="Q25" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16.249683547787047</v>
       </c>
       <c r="R25" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13.642867032814875</v>
       </c>
       <c r="S25" s="6">
@@ -4273,27 +4266,27 @@
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
       <c r="M28" s="21">
-        <f t="shared" ref="M28:M32" si="12">+M6/L6-1</f>
+        <f t="shared" ref="M28:M32" si="13">+M6/L6-1</f>
         <v>0.23689279950018216</v>
       </c>
       <c r="N28" s="21">
-        <f t="shared" ref="N28:N32" si="13">+N6/M6-1</f>
+        <f t="shared" ref="N28:N32" si="14">+N6/M6-1</f>
         <v>7.8629456581218227E-2</v>
       </c>
       <c r="O28" s="21">
-        <f t="shared" ref="O28:O32" si="14">+O6/N6-1</f>
+        <f t="shared" ref="O28:O32" si="15">+O6/N6-1</f>
         <v>0.12339512195121949</v>
       </c>
       <c r="P28" s="21">
-        <f t="shared" ref="P28:R32" si="15">+P6/O6-1</f>
+        <f t="shared" ref="P28:R32" si="16">+P6/O6-1</f>
         <v>5.4295341647271345E-2</v>
       </c>
       <c r="Q28" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.8039538714991705E-2</v>
       </c>
       <c r="R28" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-2.0077524074859077E-2</v>
       </c>
       <c r="S28" s="21">
@@ -4361,31 +4354,31 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-5.0090307043949456E-2</v>
       </c>
       <c r="N29" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-6.0675201757721675E-2</v>
       </c>
       <c r="O29" s="21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.30214565246727565</v>
       </c>
       <c r="P29" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.2907282022937068E-3</v>
       </c>
       <c r="Q29" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.1177196107989635E-2</v>
       </c>
       <c r="R29" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.42683899262409453</v>
       </c>
       <c r="S29" s="21">
-        <f t="shared" ref="S29:S32" si="16">+S7/R7-1</f>
+        <f t="shared" ref="S29:S32" si="17">+S7/R7-1</f>
         <v>3.1831412271509985E-2</v>
       </c>
       <c r="T29" s="6"/>
@@ -4449,31 +4442,31 @@
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
       <c r="M30" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-8.9651549641043493E-2</v>
       </c>
       <c r="N30" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-3.3083285247162864E-2</v>
       </c>
       <c r="O30" s="21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.13805450566938537</v>
       </c>
       <c r="P30" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.4186331061003346E-2</v>
       </c>
       <c r="Q30" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.0769358315370559E-2</v>
       </c>
       <c r="R30" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.84892536146932396</v>
       </c>
       <c r="S30" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.1774443869632694</v>
       </c>
       <c r="T30" s="6"/>
@@ -4537,31 +4530,31 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
       <c r="M31" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.8819711802881898E-2</v>
       </c>
       <c r="N31" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-7.8049823586014977E-3</v>
       </c>
       <c r="O31" s="21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.17262931034482754</v>
       </c>
       <c r="P31" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1.4335600073515975E-2</v>
       </c>
       <c r="Q31" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9.1460003729256112E-2</v>
       </c>
       <c r="R31" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.13966003245921244</v>
       </c>
       <c r="S31" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4.2990468625893508E-2</v>
       </c>
       <c r="T31" s="6"/>
@@ -4637,31 +4630,31 @@
       <c r="K32" s="22"/>
       <c r="L32" s="6"/>
       <c r="M32" s="22">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.9297594182718276E-2</v>
       </c>
       <c r="N32" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.2329735764792247E-4</v>
       </c>
       <c r="O32" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.19153147789849667</v>
       </c>
       <c r="P32" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.8329107283378674E-2</v>
       </c>
       <c r="Q32" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.4316688328251992E-2</v>
       </c>
       <c r="R32" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-3.5721622423593447E-3</v>
       </c>
       <c r="S32" s="22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>5.3969235703077656E-2</v>
       </c>
       <c r="T32" s="6"/>
@@ -4715,61 +4708,61 @@
         <v>112</v>
       </c>
       <c r="C33" s="21">
-        <f t="shared" ref="C33:H33" si="17">+C12/C10</f>
+        <f t="shared" ref="C33:H33" si="18">+C12/C10</f>
         <v>0.45229174151824669</v>
       </c>
       <c r="D33" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.46884774706230459</v>
       </c>
       <c r="E33" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.46327916066652952</v>
       </c>
       <c r="F33" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.47287894201424191</v>
       </c>
       <c r="G33" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.439124487004104</v>
       </c>
       <c r="H33" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.450326077750487</v>
       </c>
       <c r="I33" s="21">
-        <f t="shared" ref="I33:J33" si="18">+I12/I10</f>
+        <f t="shared" ref="I33:J33" si="19">+I12/I10</f>
         <v>0.44550969329317447</v>
       </c>
       <c r="J33" s="21" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="21"/>
       <c r="L33" s="6"/>
       <c r="M33" s="21">
-        <f t="shared" ref="M33:P33" si="19">+M12/M10</f>
+        <f t="shared" ref="M33:O33" si="20">+M12/M10</f>
         <v>0.4765016747301824</v>
       </c>
       <c r="N33" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.46770352731061171</v>
       </c>
       <c r="O33" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.46368303376260006</v>
       </c>
       <c r="P33" s="21">
-        <f t="shared" ref="P33:R33" si="20">+P12/P10</f>
+        <f t="shared" ref="P33:R33" si="21">+P12/P10</f>
         <v>0.49960523279118635</v>
       </c>
       <c r="Q33" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.49157745771609879</v>
       </c>
       <c r="R33" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.48151966005795505</v>
       </c>
       <c r="S33" s="21">
@@ -4827,61 +4820,61 @@
         <v>113</v>
       </c>
       <c r="C34" s="21">
-        <f t="shared" ref="C34:H34" si="21">+C17/C10</f>
+        <f t="shared" ref="C34:H34" si="22">+C17/C10</f>
         <v>0.10675973925986762</v>
       </c>
       <c r="D34" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.18150308563699394</v>
       </c>
       <c r="E34" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.16502777206336142</v>
       </c>
       <c r="F34" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.13904374364191233</v>
       </c>
       <c r="G34" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.8855449156406776E-2</v>
       </c>
       <c r="H34" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.14991106970441262</v>
       </c>
       <c r="I34" s="21">
-        <f t="shared" ref="I34:J34" si="22">+I17/I10</f>
+        <f t="shared" ref="I34:J34" si="23">+I17/I10</f>
         <v>0.15526237644763086</v>
       </c>
       <c r="J34" s="21" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K34" s="21"/>
       <c r="L34" s="6"/>
       <c r="M34" s="21">
-        <f t="shared" ref="M34:P34" si="23">+M17/M10</f>
+        <f t="shared" ref="M34:O34" si="24">+M17/M10</f>
         <v>0.10978786751023453</v>
       </c>
       <c r="N34" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.14543830927221316</v>
       </c>
       <c r="O34" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.12310920695986709</v>
       </c>
       <c r="P34" s="21">
-        <f t="shared" ref="P34:R34" si="24">+P17/P10</f>
+        <f t="shared" ref="P34:R34" si="25">+P17/P10</f>
         <v>0.22036512930144425</v>
       </c>
       <c r="Q34" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.22288922873251019</v>
       </c>
       <c r="R34" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.18764388551008482</v>
       </c>
       <c r="S34" s="21">
@@ -4939,61 +4932,61 @@
         <v>114</v>
       </c>
       <c r="C35" s="21">
-        <f t="shared" ref="C35:H35" si="25">+C22/C21</f>
+        <f t="shared" ref="C35:H35" si="26">+C22/C21</f>
         <v>0.2146003775959722</v>
       </c>
       <c r="D35" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.22929109322253943</v>
       </c>
       <c r="E35" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.22428198433420374</v>
       </c>
       <c r="F35" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.2439274717755735</v>
       </c>
       <c r="G35" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.23019431988041833</v>
       </c>
       <c r="H35" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.22998643147896883</v>
       </c>
       <c r="I35" s="21">
-        <f t="shared" ref="I35:J35" si="26">+I22/I21</f>
+        <f t="shared" ref="I35:J35" si="27">+I22/I21</f>
         <v>0.22975262622839696</v>
       </c>
       <c r="J35" s="21" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="21"/>
       <c r="L35" s="6"/>
       <c r="M35" s="21">
-        <f t="shared" ref="M35:P35" si="27">+M22/M21</f>
+        <f t="shared" ref="M35:O35" si="28">+M22/M21</f>
         <v>7.1568080357142808E-2</v>
       </c>
       <c r="N35" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.21178578958465102</v>
       </c>
       <c r="O35" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.28747109522808495</v>
       </c>
       <c r="P35" s="21">
-        <f t="shared" ref="P35:R35" si="28">+P22/P21</f>
+        <f t="shared" ref="P35:R35" si="29">+P22/P21</f>
         <v>0.21368391292055411</v>
       </c>
       <c r="Q35" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.20479396714247225</v>
       </c>
       <c r="R35" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.2068687952777033</v>
       </c>
       <c r="S35" s="21">
@@ -5872,31 +5865,31 @@
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
       <c r="L46" s="6">
-        <f t="shared" ref="L46:R46" si="29">+SUM(L37:L45)</f>
+        <f t="shared" ref="L46:R46" si="30">+SUM(L37:L45)</f>
         <v>9012.6</v>
       </c>
       <c r="M46" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>9374.7999999999993</v>
       </c>
       <c r="N46" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>9414.4</v>
       </c>
       <c r="O46" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>9966.5</v>
       </c>
       <c r="P46" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>10260.400000000003</v>
       </c>
       <c r="Q46" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>10757.900000000001</v>
       </c>
       <c r="R46" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>11210.600000000002</v>
       </c>
       <c r="S46" s="6">
@@ -6463,31 +6456,31 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
       <c r="L53" s="6">
-        <f t="shared" ref="L53:Q53" si="30">+SUM(L47:L52)</f>
+        <f t="shared" ref="L53:P53" si="31">+SUM(L47:L52)</f>
         <v>3977.8</v>
       </c>
       <c r="M53" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4028.2999999999997</v>
       </c>
       <c r="N53" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4457.6000000000004</v>
       </c>
       <c r="O53" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4029.5</v>
       </c>
       <c r="P53" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4323.3000000000011</v>
       </c>
       <c r="Q53" s="6">
-        <f t="shared" ref="Q53:R53" si="31">+SUM(Q47:Q52)</f>
+        <f t="shared" ref="Q53:R53" si="32">+SUM(Q47:Q52)</f>
         <v>4364.1999999999989</v>
       </c>
       <c r="R53" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4642.8</v>
       </c>
       <c r="S53" s="6">
@@ -6554,27 +6547,27 @@
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7">
-        <f t="shared" ref="L54" si="32">+L53+L46</f>
+        <f t="shared" ref="L54" si="33">+L53+L46</f>
         <v>12990.400000000001</v>
       </c>
       <c r="M54" s="7">
-        <f t="shared" ref="M54" si="33">+M53+M46</f>
+        <f t="shared" ref="M54" si="34">+M53+M46</f>
         <v>13403.099999999999</v>
       </c>
       <c r="N54" s="7">
-        <f t="shared" ref="N54" si="34">+N53+N46</f>
+        <f t="shared" ref="N54" si="35">+N53+N46</f>
         <v>13872</v>
       </c>
       <c r="O54" s="7">
-        <f t="shared" ref="O54:Q54" si="35">+O53+O46</f>
+        <f t="shared" ref="O54:Q54" si="36">+O53+O46</f>
         <v>13996</v>
       </c>
       <c r="P54" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>14583.700000000004</v>
       </c>
       <c r="Q54" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>15122.1</v>
       </c>
       <c r="R54" s="7">
@@ -7226,31 +7219,31 @@
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
       <c r="L62" s="6">
-        <f t="shared" ref="L62:Q62" si="36">+SUM(L56:L61)</f>
+        <f t="shared" ref="L62:P62" si="37">+SUM(L56:L61)</f>
         <v>3471.7000000000003</v>
       </c>
       <c r="M62" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>3475.7000000000003</v>
       </c>
       <c r="N62" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>3690.2000000000003</v>
       </c>
       <c r="O62" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>3959.8</v>
       </c>
       <c r="P62" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4150</v>
       </c>
       <c r="Q62" s="6">
-        <f t="shared" ref="Q62:R62" si="37">+SUM(Q56:Q61)</f>
+        <f t="shared" ref="Q62:R62" si="38">+SUM(Q56:Q61)</f>
         <v>4303.3</v>
       </c>
       <c r="R62" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>4868.7</v>
       </c>
       <c r="S62" s="6">
@@ -7815,35 +7808,35 @@
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
       <c r="L69" s="6">
-        <f t="shared" ref="L69:M69" si="38">+SUM(L63:L68)</f>
+        <f t="shared" ref="L69:M69" si="39">+SUM(L63:L68)</f>
         <v>1070.5</v>
       </c>
       <c r="M69" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1109.2</v>
       </c>
       <c r="N69" s="6">
-        <f>+SUM(N63:N68)</f>
+        <f t="shared" ref="N69:S69" si="40">+SUM(N63:N68)</f>
         <v>1079.0999999999999</v>
       </c>
       <c r="O69" s="6">
-        <f>+SUM(O63:O68)</f>
+        <f t="shared" si="40"/>
         <v>1663.9</v>
       </c>
       <c r="P69" s="6">
-        <f>+SUM(P63:P68)</f>
+        <f t="shared" si="40"/>
         <v>1465.9</v>
       </c>
       <c r="Q69" s="6">
-        <f>+SUM(Q63:Q68)</f>
+        <f t="shared" si="40"/>
         <v>1477.1999999999998</v>
       </c>
       <c r="R69" s="6">
-        <f>+SUM(R63:R68)</f>
+        <f t="shared" si="40"/>
         <v>1550.6999999999998</v>
       </c>
       <c r="S69" s="6">
-        <f>+SUM(S63:S68)</f>
+        <f t="shared" si="40"/>
         <v>2834.2000000000003</v>
       </c>
       <c r="T69" s="6"/>
@@ -7906,27 +7899,27 @@
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
       <c r="L70" s="6">
-        <f t="shared" ref="L70" si="39">+L69+L62</f>
+        <f t="shared" ref="L70" si="41">+L69+L62</f>
         <v>4542.2000000000007</v>
       </c>
       <c r="M70" s="6">
-        <f t="shared" ref="M70" si="40">+M69+M62</f>
+        <f t="shared" ref="M70" si="42">+M69+M62</f>
         <v>4584.9000000000005</v>
       </c>
       <c r="N70" s="6">
-        <f t="shared" ref="N70:Q70" si="41">+N69+N62</f>
+        <f t="shared" ref="N70:Q70" si="43">+N69+N62</f>
         <v>4769.3</v>
       </c>
       <c r="O70" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>5623.7000000000007</v>
       </c>
       <c r="P70" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>5615.9</v>
       </c>
       <c r="Q70" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>5780.5</v>
       </c>
       <c r="R70" s="6">
@@ -7998,27 +7991,27 @@
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7">
-        <f t="shared" ref="L71" si="42">+L70+L55</f>
+        <f t="shared" ref="L71" si="44">+L70+L55</f>
         <v>12990.400000000001</v>
       </c>
       <c r="M71" s="7">
-        <f t="shared" ref="M71" si="43">+M70+M55</f>
+        <f t="shared" ref="M71" si="45">+M70+M55</f>
         <v>13403.100000000002</v>
       </c>
       <c r="N71" s="7">
-        <f t="shared" ref="N71:Q71" si="44">+N70+N55</f>
+        <f t="shared" ref="N71:Q71" si="46">+N70+N55</f>
         <v>13872</v>
       </c>
       <c r="O71" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>13996</v>
       </c>
       <c r="P71" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>14583.699999999999</v>
       </c>
       <c r="Q71" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>15122.1</v>
       </c>
       <c r="R71" s="7">
@@ -8817,31 +8810,31 @@
       <c r="J81" s="6"/>
       <c r="K81" s="6"/>
       <c r="L81" s="7">
-        <f t="shared" ref="L81:P81" si="45">+SUM(L73:L80)</f>
+        <f t="shared" ref="L81:O81" si="47">+SUM(L73:L80)</f>
         <v>1048.4999999999998</v>
       </c>
       <c r="M81" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>784.50000000000023</v>
       </c>
       <c r="N81" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1299.6000000000004</v>
       </c>
       <c r="O81" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1585.3999999999999</v>
       </c>
       <c r="P81" s="7">
-        <f t="shared" ref="P81:R81" si="46">+SUM(P73:P80)</f>
+        <f t="shared" ref="P81:R81" si="48">+SUM(P73:P80)</f>
         <v>1566.7</v>
       </c>
       <c r="Q81" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>1392.5</v>
       </c>
       <c r="R81" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>1347</v>
       </c>
       <c r="S81" s="7">
@@ -9324,31 +9317,31 @@
       <c r="J87" s="6"/>
       <c r="K87" s="6"/>
       <c r="L87" s="7">
-        <f t="shared" ref="L87:Q87" si="47">+SUM(L82:L86)</f>
+        <f t="shared" ref="L87:P87" si="49">+SUM(L82:L86)</f>
         <v>-93.7</v>
       </c>
       <c r="M87" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-510.6</v>
       </c>
       <c r="N87" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-49.899999999999991</v>
       </c>
       <c r="O87" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1751.7</v>
       </c>
       <c r="P87" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-177.50000000000003</v>
       </c>
       <c r="Q87" s="7">
-        <f t="shared" ref="Q87:R87" si="48">+SUM(Q82:Q86)</f>
+        <f t="shared" ref="Q87:R87" si="50">+SUM(Q82:Q86)</f>
         <v>-131.80000000000004</v>
       </c>
       <c r="R87" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>-875.30000000000007</v>
       </c>
       <c r="S87" s="7">
@@ -9997,31 +9990,31 @@
       <c r="J95" s="6"/>
       <c r="K95" s="6"/>
       <c r="L95" s="7">
-        <f t="shared" ref="L95:Q95" si="49">+SUM(L88:L94)</f>
+        <f t="shared" ref="L95:P95" si="51">+SUM(L88:L94)</f>
         <v>-896.7</v>
       </c>
       <c r="M95" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-572.9</v>
       </c>
       <c r="N95" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-672.5</v>
       </c>
       <c r="O95" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-601.90000000000032</v>
       </c>
       <c r="P95" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-1337.8000000000002</v>
       </c>
       <c r="Q95" s="7">
-        <f t="shared" ref="Q95:R95" si="50">+SUM(Q88:Q94)</f>
+        <f t="shared" ref="Q95:R95" si="52">+SUM(Q88:Q94)</f>
         <v>-1401.5</v>
       </c>
       <c r="R95" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>-386.19999999999993</v>
       </c>
       <c r="S95" s="7">
@@ -10152,31 +10145,31 @@
       <c r="J97" s="6"/>
       <c r="K97" s="6"/>
       <c r="L97" s="7">
-        <f t="shared" ref="L97:P97" si="51">+SUM(L96,L95,L87,L81)</f>
+        <f t="shared" ref="L97:O97" si="53">+SUM(L96,L95,L87,L81)</f>
         <v>58.099999999999682</v>
       </c>
       <c r="M97" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-298.99999999999977</v>
       </c>
       <c r="N97" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>577.20000000000039</v>
       </c>
       <c r="O97" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-768.2000000000005</v>
       </c>
       <c r="P97" s="7">
-        <f t="shared" ref="P97:R97" si="52">+SUM(P96,P95,P87,P81)</f>
+        <f t="shared" ref="P97:R97" si="54">+SUM(P96,P95,P87,P81)</f>
         <v>51.399999999999864</v>
       </c>
       <c r="Q97" s="7">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>-140.79999999999995</v>
       </c>
       <c r="R97" s="7">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>85.5</v>
       </c>
       <c r="S97" s="7">
@@ -10409,19 +10402,19 @@
       <c r="J100" s="6"/>
       <c r="K100" s="6"/>
       <c r="L100" s="6">
-        <f t="shared" ref="L100:O100" si="53">+L99+L97+L98</f>
+        <f t="shared" ref="L100:O100" si="55">+L99+L97+L98</f>
         <v>605.19999999999959</v>
       </c>
       <c r="M100" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>310.8000000000003</v>
       </c>
       <c r="N100" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>897.50000000000045</v>
       </c>
       <c r="O100" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>116.99999999999955</v>
       </c>
       <c r="P100" s="6">
@@ -30807,14 +30800,14 @@
       </c>
       <c r="E4" s="27">
         <f ca="1">+TODAY()</f>
-        <v>45977</v>
+        <v>46077</v>
       </c>
       <c r="G4" t="s">
         <v>119</v>
       </c>
       <c r="J4" s="28">
         <f ca="1">V62</f>
-        <v>107.52888780978846</v>
+        <v>107.51271275253276</v>
       </c>
       <c r="L4" t="s">
         <v>120</v>
@@ -30836,7 +30829,7 @@
       </c>
       <c r="J5" s="31">
         <f ca="1">J4/J3-1</f>
-        <v>0.24310852959293006</v>
+        <v>0.24292153471136135</v>
       </c>
       <c r="L5" t="s">
         <v>122</v>
@@ -32332,43 +32325,43 @@
       <c r="L52" s="57"/>
       <c r="M52" s="57">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>139.06741862420071</v>
+        <v>166.5217540773167</v>
       </c>
       <c r="N52" s="57">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>1030.8850848472869</v>
+        <v>1028.6664930770028</v>
       </c>
       <c r="O52" s="57">
         <f t="shared" ref="O52:U52" ca="1" si="15">O51/(1+$E$18)^O53</f>
-        <v>955.22379421629262</v>
+        <v>953.16803486951585</v>
       </c>
       <c r="P52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>885.11562583344539</v>
+        <v>883.21074790661555</v>
       </c>
       <c r="Q52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>820.15301109337599</v>
+        <v>818.38794072080884</v>
       </c>
       <c r="R52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>759.95829468285308</v>
+        <v>758.32277075964862</v>
       </c>
       <c r="S52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>704.1815391097997</v>
+        <v>702.66605363967437</v>
       </c>
       <c r="T52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>652.49849036779574</v>
+        <v>651.0942331890559</v>
       </c>
       <c r="U52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>604.60869290960909</v>
+        <v>603.30750047793254</v>
       </c>
       <c r="V52" s="58">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>560.23374297128885</v>
+        <v>559.02805090157028</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -32377,43 +32370,43 @@
       </c>
       <c r="M53" s="74">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="N53" s="74">
         <f ca="1">M53+1</f>
-        <v>1.125</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="O53" s="74">
         <f ca="1">N53+1</f>
-        <v>2.125</v>
+        <v>2.15</v>
       </c>
       <c r="P53" s="74">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.125</v>
+        <v>3.15</v>
       </c>
       <c r="Q53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>4.125</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="R53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>5.125</v>
+        <v>5.15</v>
       </c>
       <c r="S53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>6.125</v>
+        <v>6.15</v>
       </c>
       <c r="T53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>7.125</v>
+        <v>7.15</v>
       </c>
       <c r="U53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>8.125</v>
+        <v>8.15</v>
       </c>
       <c r="V53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>9.125</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -32426,7 +32419,7 @@
       <c r="Q54" s="59"/>
       <c r="V54" s="3">
         <f ca="1">SUM(M52:V52)</f>
-        <v>7111.9256946559481</v>
+        <v>7124.3735796191413</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -32470,7 +32463,7 @@
       <c r="U56" s="61"/>
       <c r="V56" s="62">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>6376.8153313411149</v>
+        <v>6363.0916387368807</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -32498,7 +32491,7 @@
       <c r="U57" s="64"/>
       <c r="V57" s="65">
         <f ca="1">V54+V56</f>
-        <v>13488.741025997064</v>
+        <v>13487.465218356021</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -32552,7 +32545,7 @@
       <c r="Q60" s="59"/>
       <c r="V60" s="66">
         <f ca="1">V57+V58-V59</f>
-        <v>8481.3410259970642</v>
+        <v>8480.0652183560214</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -32589,7 +32582,7 @@
       </c>
       <c r="V62" s="66">
         <f ca="1">V60/V61</f>
-        <v>107.52888780978846</v>
+        <v>107.51271275253276</v>
       </c>
     </row>
     <row r="66" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32650,7 +32643,7 @@
       </c>
       <c r="C69" s="68">
         <f ca="1">+J4</f>
-        <v>107.52888780978846</v>
+        <v>107.51271275253276</v>
       </c>
       <c r="D69" s="69">
         <v>-5.0000000000000001E-3</v>
@@ -32678,7 +32671,7 @@
       </c>
       <c r="N69" s="68">
         <f ca="1">+J4</f>
-        <v>107.52888780978846</v>
+        <v>107.51271275253276</v>
       </c>
       <c r="O69" s="69">
         <v>0.08</v>
@@ -32709,25 +32702,25 @@
       </c>
       <c r="D70" s="71">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>184.53884725281412</v>
+        <v>184.53115252598974</v>
       </c>
       <c r="E70" s="71">
-        <v>190.56515794106548</v>
+        <v>190.54869094158121</v>
       </c>
       <c r="F70" s="71">
-        <v>197.6120612686436</v>
+        <v>197.5853363583752</v>
       </c>
       <c r="G70" s="72">
-        <v>205.98573502734655</v>
+        <v>205.9468208767326</v>
       </c>
       <c r="H70" s="71">
-        <v>216.12843602754933</v>
+        <v>216.07475753050784</v>
       </c>
       <c r="I70" s="71">
-        <v>228.70354948481429</v>
+        <v>228.63156587048249</v>
       </c>
       <c r="J70" s="71">
-        <v>244.75353788073949</v>
+        <v>244.65819090502785</v>
       </c>
       <c r="M70" s="79"/>
       <c r="N70" s="70">
@@ -32735,25 +32728,25 @@
       </c>
       <c r="O70" s="71">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>199.72800977224412</v>
+        <v>199.69820475572701</v>
       </c>
       <c r="P70" s="71">
-        <v>202.27745339469325</v>
+        <v>202.24393724947006</v>
       </c>
       <c r="Q70" s="71">
-        <v>204.31700829265259</v>
+        <v>204.28052324446449</v>
       </c>
       <c r="R70" s="72">
-        <v>205.98573502734655</v>
+        <v>205.9468208767326</v>
       </c>
       <c r="S70" s="71">
-        <v>207.37634063959155</v>
+        <v>207.3354022369561</v>
       </c>
       <c r="T70" s="71">
-        <v>208.55300692687581</v>
+        <v>208.51035569560676</v>
       </c>
       <c r="U70" s="71">
-        <v>209.56157803026233</v>
+        <v>209.51745866016444</v>
       </c>
     </row>
     <row r="71" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32762,50 +32755,50 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="71">
-        <v>150.37839858893122</v>
+        <v>150.3698084702871</v>
       </c>
       <c r="E71" s="71">
-        <v>153.84837878743784</v>
+        <v>153.83392427564183</v>
       </c>
       <c r="F71" s="71">
-        <v>157.79387376220672</v>
+        <v>157.77275121993577</v>
       </c>
       <c r="G71" s="72">
-        <v>162.33376220730324</v>
+        <v>162.30496708790366</v>
       </c>
       <c r="H71" s="71">
-        <v>167.63015143281689</v>
+        <v>167.59240522236576</v>
       </c>
       <c r="I71" s="71">
-        <v>173.90999167287279</v>
+        <v>173.86163230327026</v>
       </c>
       <c r="J71" s="71">
-        <v>181.50109993231834</v>
+        <v>181.43991131276465</v>
       </c>
       <c r="M71" s="79"/>
       <c r="N71" s="70">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="71">
-        <v>157.54719352817176</v>
+        <v>157.5264878844975</v>
       </c>
       <c r="P71" s="71">
-        <v>159.49727706411423</v>
+        <v>159.47327570810745</v>
       </c>
       <c r="Q71" s="71">
-        <v>161.05734389286818</v>
+        <v>161.03070596699536</v>
       </c>
       <c r="R71" s="72">
-        <v>162.33376220730324</v>
+        <v>162.30496708790366</v>
       </c>
       <c r="S71" s="71">
-        <v>163.39744413599914</v>
+        <v>163.36685135532727</v>
       </c>
       <c r="T71" s="71">
-        <v>164.29748269104951</v>
+        <v>164.26536881237806</v>
       </c>
       <c r="U71" s="71">
-        <v>165.06894430966412</v>
+        <v>165.03552663270725</v>
       </c>
     </row>
     <row r="72" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32814,50 +32807,50 @@
         <v>0.08</v>
       </c>
       <c r="D72" s="72">
-        <v>124.32485684869482</v>
+        <v>124.31620796001758</v>
       </c>
       <c r="E72" s="72">
-        <v>126.33258664708057</v>
+        <v>126.32007854781457</v>
       </c>
       <c r="F72" s="72">
-        <v>128.56157646406393</v>
+        <v>128.54478385345041</v>
       </c>
       <c r="G72" s="72">
-        <v>131.05923916077293</v>
+        <v>131.03764560217627</v>
       </c>
       <c r="H72" s="72">
-        <v>133.88757617099049</v>
+        <v>133.86054605008988</v>
       </c>
       <c r="I72" s="72">
-        <v>137.1292560730937</v>
+        <v>137.09599487198815</v>
       </c>
       <c r="J72" s="72">
-        <v>140.89700874668773</v>
+        <v>140.856505260776</v>
       </c>
       <c r="M72" s="79"/>
       <c r="N72" s="70">
         <v>0.08</v>
       </c>
       <c r="O72" s="72">
-        <v>127.29035570906559</v>
+        <v>127.27600660882996</v>
       </c>
       <c r="P72" s="72">
-        <v>128.82582674494637</v>
+        <v>128.8085261987118</v>
       </c>
       <c r="Q72" s="72">
-        <v>130.05420357365099</v>
+        <v>130.03454187061723</v>
       </c>
       <c r="R72" s="72">
-        <v>131.05923916077293</v>
+        <v>131.03764560217627</v>
       </c>
       <c r="S72" s="72">
-        <v>131.89676881670792</v>
+        <v>131.87356537847543</v>
       </c>
       <c r="T72" s="72">
-        <v>132.6054477563452</v>
+        <v>132.58088211226709</v>
       </c>
       <c r="U72" s="72">
-        <v>133.21288684746287</v>
+        <v>133.18715359837418</v>
       </c>
     </row>
     <row r="73" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32866,50 +32859,50 @@
         <v>0.09</v>
       </c>
       <c r="D73" s="71">
-        <v>103.81303862972794</v>
+        <v>103.80486053792622</v>
       </c>
       <c r="E73" s="71">
-        <v>104.94960726278248</v>
+        <v>104.93898313518808</v>
       </c>
       <c r="F73" s="71">
-        <v>106.18222084670664</v>
+        <v>106.16894398274675</v>
       </c>
       <c r="G73" s="72">
-        <v>107.52888780978846</v>
+        <v>107.51271275253276</v>
       </c>
       <c r="H73" s="71">
-        <v>109.01241882785948</v>
+        <v>108.99305102899173</v>
       </c>
       <c r="I73" s="71">
-        <v>110.66214191270311</v>
+        <v>110.63922370641065</v>
       </c>
       <c r="J73" s="71">
-        <v>112.51640907972839</v>
+        <v>112.48950026193407</v>
       </c>
       <c r="M73" s="79"/>
       <c r="N73" s="70">
         <v>0.09</v>
       </c>
       <c r="O73" s="71">
-        <v>104.49712140819997</v>
+        <v>104.48747108593838</v>
       </c>
       <c r="P73" s="71">
-        <v>105.732285497736</v>
+        <v>105.71997695010647</v>
       </c>
       <c r="Q73" s="71">
-        <v>106.72041676936489</v>
+        <v>106.70598164144094</v>
       </c>
       <c r="R73" s="72">
-        <v>107.52888780978846</v>
+        <v>107.51271275253276</v>
       </c>
       <c r="S73" s="71">
-        <v>108.20261367680813</v>
+        <v>108.18498867844264</v>
       </c>
       <c r="T73" s="71">
-        <v>108.77268941044015</v>
+        <v>108.75383753882792</v>
       </c>
       <c r="U73" s="71">
-        <v>109.26132575355331</v>
+        <v>109.24142227630104</v>
       </c>
     </row>
     <row r="74" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32918,50 +32911,50 @@
         <v>0.1</v>
       </c>
       <c r="D74" s="71">
-        <v>87.255412993573543</v>
+        <v>87.248049337119639</v>
       </c>
       <c r="E74" s="71">
-        <v>87.858612236868737</v>
+        <v>87.849813015684788</v>
       </c>
       <c r="F74" s="71">
-        <v>88.494297118725726</v>
+        <v>88.483985019656131</v>
       </c>
       <c r="G74" s="72">
-        <v>89.167881912238116</v>
+        <v>89.155966736601371</v>
       </c>
       <c r="H74" s="71">
-        <v>89.886054837109882</v>
+        <v>89.872430468810023</v>
       </c>
       <c r="I74" s="71">
-        <v>90.657176167970832</v>
+        <v>90.641716594144</v>
       </c>
       <c r="J74" s="71">
-        <v>91.491835586018809</v>
+        <v>91.474389591228302</v>
       </c>
       <c r="M74" s="79"/>
       <c r="N74" s="70">
         <v>0.1</v>
       </c>
       <c r="O74" s="71">
-        <v>86.688452464507321</v>
+        <v>86.682438127615598</v>
       </c>
       <c r="P74" s="71">
-        <v>87.698590387656921</v>
+        <v>87.690172005350561</v>
       </c>
       <c r="Q74" s="71">
-        <v>88.506700726176604</v>
+        <v>88.496359107538495</v>
       </c>
       <c r="R74" s="72">
-        <v>89.167881912238116</v>
+        <v>89.155966736601371</v>
       </c>
       <c r="S74" s="71">
-        <v>89.718866233956092</v>
+        <v>89.705639760820446</v>
       </c>
       <c r="T74" s="71">
-        <v>90.185083736948215</v>
+        <v>90.170747704390422</v>
       </c>
       <c r="U74" s="71">
-        <v>90.584698739512888</v>
+        <v>90.569411656021828</v>
       </c>
     </row>
     <row r="75" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32970,50 +32963,50 @@
         <v>0.11</v>
       </c>
       <c r="D75" s="71">
-        <v>73.616992828006701</v>
+        <v>73.610669319064939</v>
       </c>
       <c r="E75" s="71">
-        <v>73.888229057065615</v>
+        <v>73.881198815032661</v>
       </c>
       <c r="F75" s="71">
-        <v>74.159465286124515</v>
+        <v>74.151728311000369</v>
       </c>
       <c r="G75" s="72">
-        <v>74.430701515183387</v>
+        <v>74.422257806968076</v>
       </c>
       <c r="H75" s="71">
-        <v>74.701937744242315</v>
+        <v>74.692787302935784</v>
       </c>
       <c r="I75" s="71">
-        <v>74.973173973301215</v>
+        <v>74.96331679890352</v>
       </c>
       <c r="J75" s="71">
-        <v>75.244410202360115</v>
+        <v>75.233846294871242</v>
       </c>
       <c r="M75" s="79"/>
       <c r="N75" s="70">
         <v>0.11</v>
       </c>
       <c r="O75" s="71">
-        <v>72.37608708006222</v>
+        <v>72.372996875012632</v>
       </c>
       <c r="P75" s="71">
-        <v>73.213152220296749</v>
+        <v>73.207880958401887</v>
       </c>
       <c r="Q75" s="71">
-        <v>73.882804332484426</v>
+        <v>73.875788225113297</v>
       </c>
       <c r="R75" s="72">
-        <v>74.430701515183387</v>
+        <v>74.422257806968076</v>
       </c>
       <c r="S75" s="71">
-        <v>74.887282500765878</v>
+        <v>74.877649125180383</v>
       </c>
       <c r="T75" s="71">
-        <v>75.273620257797234</v>
+        <v>75.262980240590849</v>
       </c>
       <c r="U75" s="71">
-        <v>75.604766906681235</v>
+        <v>75.593264053799786</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -33022,50 +33015,50 @@
         <v>0.12</v>
       </c>
       <c r="D76" s="71">
-        <v>62.194282825513589</v>
+        <v>62.189147682629788</v>
       </c>
       <c r="E76" s="71">
-        <v>62.257596535119845</v>
+        <v>62.252282264622771</v>
       </c>
       <c r="F76" s="71">
-        <v>62.304683390090155</v>
+        <v>62.299235901116418</v>
       </c>
       <c r="G76" s="72">
-        <v>62.33333063751963</v>
+        <v>62.327802099542595</v>
       </c>
       <c r="H76" s="71">
-        <v>62.340904047759615</v>
+        <v>62.335354083034574</v>
       </c>
       <c r="I76" s="71">
-        <v>62.324242545231662</v>
+        <v>62.318739719352216</v>
       </c>
       <c r="J76" s="71">
-        <v>62.279519564761863</v>
+        <v>62.274143269467977</v>
       </c>
       <c r="M76" s="80"/>
       <c r="N76" s="70">
         <v>0.12</v>
       </c>
       <c r="O76" s="71">
-        <v>60.612273160484044</v>
+        <v>60.611613850989336</v>
       </c>
       <c r="P76" s="71">
-        <v>61.313444725202245</v>
+        <v>61.31080165595548</v>
       </c>
       <c r="Q76" s="71">
-        <v>61.874381976976792</v>
+        <v>61.870151899928402</v>
       </c>
       <c r="R76" s="72">
-        <v>62.33333063751963</v>
+        <v>62.327802099542595</v>
       </c>
       <c r="S76" s="71">
-        <v>62.715787854638663</v>
+        <v>62.709177265887774</v>
       </c>
       <c r="T76" s="71">
-        <v>63.039405499893213</v>
+        <v>63.031879329718308</v>
       </c>
       <c r="U76" s="71">
-        <v>63.316792052968552</v>
+        <v>63.308481098715887</v>
       </c>
     </row>
   </sheetData>

--- a/STG.CO.xlsx
+++ b/STG.CO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D02019-B52D-417F-9279-96B61A21D55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D1EEB2-B5B3-4EB6-BA47-F50CA7A7EB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3900" windowWidth="38175" windowHeight="15240" xr2:uid="{BD75BBDC-C4FD-4EC4-8461-B3C83FDDB12A}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{BD75BBDC-C4FD-4EC4-8461-B3C83FDDB12A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
     Changed reporting from Accessires to Next Gen</t>
       </text>
     </comment>
-    <comment ref="O82" authorId="2" shapeId="0" xr:uid="{301E1A6D-A607-4725-84D3-35AEB480AC53}">
+    <comment ref="O83" authorId="2" shapeId="0" xr:uid="{301E1A6D-A607-4725-84D3-35AEB480AC53}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="190">
   <si>
     <t>Scandivian Tobacco</t>
   </si>
@@ -665,6 +665,9 @@
   <si>
     <t>Merged in 2010 with Swedish Match Cigars</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
 </sst>
 </file>
 
@@ -1002,7 +1005,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1130,6 +1133,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1606,7 +1610,7 @@
   <threadedComment ref="R8" dT="2025-11-16T11:33:29.05" personId="{10C33167-272C-4E0C-8732-ACA733750BD3}" id="{7F70D672-7BA8-4A02-A1F8-509A8E4A96A4}">
     <text>Changed reporting from Accessires to Next Gen</text>
   </threadedComment>
-  <threadedComment ref="O82" dT="2025-11-16T11:45:23.70" personId="{10C33167-272C-4E0C-8732-ACA733750BD3}" id="{301E1A6D-A607-4725-84D3-35AEB480AC53}">
+  <threadedComment ref="O83" dT="2025-11-16T11:45:23.70" personId="{10C33167-272C-4E0C-8732-ACA733750BD3}" id="{301E1A6D-A607-4725-84D3-35AEB480AC53}">
     <text>Roayl Agio Cigars</text>
   </threadedComment>
 </ThreadedComments>
@@ -1633,7 +1637,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>86.5</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1641,10 +1645,10 @@
         <v>3</v>
       </c>
       <c r="J3" s="6">
-        <v>78.875</v>
+        <v>78.741</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="J4" s="6">
         <f>+J2*J3</f>
-        <v>6822.6875</v>
+        <v>7921.3445999999994</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1664,10 +1668,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="6">
-        <v>97.5</v>
+        <v>197.7</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1684,11 +1688,11 @@
         <v>6</v>
       </c>
       <c r="J6" s="6">
-        <f>3954.9+1150</f>
-        <v>5104.8999999999996</v>
+        <f>1150+204+3726.6</f>
+        <v>5080.6000000000004</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1706,7 +1710,7 @@
       </c>
       <c r="J7" s="6">
         <f>+J4-J5+J6</f>
-        <v>11830.0875</v>
+        <v>12804.2446</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1817,7 +1821,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A8E8A0-8674-4392-9CB4-751825DBF326}">
-  <dimension ref="A1:BL455"/>
+  <dimension ref="A1:BL456"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1878,6 +1882,9 @@
       </c>
       <c r="S2" s="5" t="s">
         <v>44</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:64" x14ac:dyDescent="0.2">
@@ -1917,7 +1924,9 @@
       <c r="S3" s="6">
         <v>4911.8999999999996</v>
       </c>
-      <c r="T3" s="6"/>
+      <c r="T3" s="6">
+        <v>4538.1000000000004</v>
+      </c>
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
@@ -2000,7 +2009,9 @@
       <c r="S4" s="6">
         <v>3756.2</v>
       </c>
-      <c r="T4" s="6"/>
+      <c r="T4" s="6">
+        <v>3933.6</v>
+      </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
@@ -2083,7 +2094,9 @@
       <c r="S5" s="6">
         <v>534</v>
       </c>
-      <c r="T5" s="6"/>
+      <c r="T5" s="6">
+        <v>564</v>
+      </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
@@ -2166,7 +2179,9 @@
       <c r="S6" s="6">
         <v>3299.5</v>
       </c>
-      <c r="T6" s="6"/>
+      <c r="T6" s="6">
+        <v>3164.1</v>
+      </c>
       <c r="U6" s="6"/>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
@@ -2249,7 +2264,9 @@
       <c r="S7" s="6">
         <v>4431.2</v>
       </c>
-      <c r="T7" s="6"/>
+      <c r="T7" s="6">
+        <v>4541.5</v>
+      </c>
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
@@ -2334,7 +2351,9 @@
       <c r="S8" s="6">
         <v>420.9</v>
       </c>
-      <c r="T8" s="6"/>
+      <c r="T8" s="6">
+        <v>428.2</v>
+      </c>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
@@ -2417,7 +2436,9 @@
       <c r="S9" s="6">
         <v>1050.5</v>
       </c>
-      <c r="T9" s="6"/>
+      <c r="T9" s="6">
+        <v>902</v>
+      </c>
       <c r="U9" s="6"/>
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
@@ -2490,7 +2511,10 @@
       <c r="I10" s="7">
         <v>2357.3000000000002</v>
       </c>
-      <c r="J10" s="7"/>
+      <c r="J10" s="7">
+        <f>+T10-SUM(G10:I10)</f>
+        <v>2343.3000000000002</v>
+      </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7">
         <v>6463.5</v>
@@ -2516,7 +2540,9 @@
       <c r="S10" s="7">
         <v>9202.1</v>
       </c>
-      <c r="T10" s="7"/>
+      <c r="T10" s="7">
+        <v>9035.7000000000007</v>
+      </c>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
       <c r="W10" s="7"/>
@@ -2588,7 +2614,10 @@
       <c r="I11" s="6">
         <v>1307.0999999999999</v>
       </c>
-      <c r="J11" s="6"/>
+      <c r="J11" s="81">
+        <f>+T11-SUM(G11:I11)</f>
+        <v>1322.4</v>
+      </c>
       <c r="K11" s="6"/>
       <c r="L11" s="6">
         <v>3368.2</v>
@@ -2614,7 +2643,9 @@
       <c r="S11" s="6">
         <v>4923.6000000000004</v>
       </c>
-      <c r="T11" s="6"/>
+      <c r="T11" s="6">
+        <v>5034.5</v>
+      </c>
       <c r="U11" s="6"/>
       <c r="V11" s="6"/>
       <c r="W11" s="6"/>
@@ -2692,7 +2723,10 @@
         <f>+I10-I11</f>
         <v>1050.2000000000003</v>
       </c>
-      <c r="J12" s="6"/>
+      <c r="J12" s="6">
+        <f>+J10-J11</f>
+        <v>1020.9000000000001</v>
+      </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6">
         <f t="shared" ref="L12:M12" si="1">+L10-L11</f>
@@ -2703,7 +2737,7 @@
         <v>3200.9</v>
       </c>
       <c r="N12" s="6">
-        <f t="shared" ref="N12:S12" si="2">+N10-N11</f>
+        <f t="shared" ref="N12:T12" si="2">+N10-N11</f>
         <v>3142.5</v>
       </c>
       <c r="O12" s="6">
@@ -2726,7 +2760,10 @@
         <f t="shared" si="2"/>
         <v>4278.5</v>
       </c>
-      <c r="T12" s="6"/>
+      <c r="T12" s="6">
+        <f t="shared" si="2"/>
+        <v>4001.2000000000007</v>
+      </c>
       <c r="U12" s="6"/>
       <c r="V12" s="6"/>
       <c r="W12" s="6"/>
@@ -2798,7 +2835,10 @@
       <c r="I13" s="6">
         <v>317.60000000000002</v>
       </c>
-      <c r="J13" s="6"/>
+      <c r="J13" s="81">
+        <f>+T13-SUM(G13:I13)</f>
+        <v>363.70000000000005</v>
+      </c>
       <c r="K13" s="6"/>
       <c r="L13" s="6">
         <v>1141.5</v>
@@ -2824,7 +2864,9 @@
       <c r="S13" s="6">
         <v>1190.8</v>
       </c>
-      <c r="T13" s="6"/>
+      <c r="T13" s="6">
+        <v>1244.2</v>
+      </c>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
@@ -2896,7 +2938,10 @@
       <c r="I14" s="6">
         <v>232.9</v>
       </c>
-      <c r="J14" s="6"/>
+      <c r="J14" s="81">
+        <f>+T14-SUM(G14:I14)</f>
+        <v>221.30000000000007</v>
+      </c>
       <c r="K14" s="6"/>
       <c r="L14" s="6">
         <v>735.5</v>
@@ -2922,7 +2967,9 @@
       <c r="S14" s="6">
         <v>1057.2</v>
       </c>
-      <c r="T14" s="6"/>
+      <c r="T14" s="6">
+        <v>1023.3</v>
+      </c>
       <c r="U14" s="6"/>
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
@@ -2994,7 +3041,10 @@
       <c r="I15" s="6">
         <v>18.899999999999999</v>
       </c>
-      <c r="J15" s="6"/>
+      <c r="J15" s="81">
+        <f>+T15-SUM(G15:I15)</f>
+        <v>20.399999999999999</v>
+      </c>
       <c r="K15" s="6"/>
       <c r="L15" s="6">
         <v>13.4</v>
@@ -3020,7 +3070,9 @@
       <c r="S15" s="6">
         <v>48.5</v>
       </c>
-      <c r="T15" s="6"/>
+      <c r="T15" s="6">
+        <v>57.3</v>
+      </c>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
@@ -3098,7 +3150,10 @@
         <f>61.2+50.1+41.3</f>
         <v>152.60000000000002</v>
       </c>
-      <c r="J16" s="6"/>
+      <c r="J16" s="81">
+        <f>+T16-SUM(G16:I16)</f>
+        <v>169.99999999999989</v>
+      </c>
       <c r="K16" s="6"/>
       <c r="L16" s="6">
         <f>148.2+170.5</f>
@@ -3132,7 +3187,10 @@
         <f>236.3+183.5+279</f>
         <v>698.8</v>
       </c>
-      <c r="T16" s="6"/>
+      <c r="T16" s="6">
+        <f>252.1+197+199.7</f>
+        <v>648.79999999999995</v>
+      </c>
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
@@ -3210,14 +3268,17 @@
         <f>+I12-SUM(I13:I14,I16)+I15</f>
         <v>366.00000000000023</v>
       </c>
-      <c r="J17" s="6"/>
+      <c r="J17" s="6">
+        <f>+J12-SUM(J13:J14,J16)+J15</f>
+        <v>286.30000000000007</v>
+      </c>
       <c r="K17" s="6"/>
       <c r="L17" s="6">
         <f>+L12-SUM(L13:L14,L16)+L15</f>
         <v>913.00000000000034</v>
       </c>
       <c r="M17" s="6">
-        <f t="shared" ref="M17:S17" si="4">+M12-SUM(M13:M14,M16)+M15</f>
+        <f t="shared" ref="M17:T17" si="4">+M12-SUM(M13:M14,M16)+M15</f>
         <v>737.50000000000045</v>
       </c>
       <c r="N17" s="6">
@@ -3244,7 +3305,10 @@
         <f t="shared" si="4"/>
         <v>1380.1999999999998</v>
       </c>
-      <c r="T17" s="6"/>
+      <c r="T17" s="6">
+        <f t="shared" si="4"/>
+        <v>1142.2000000000005</v>
+      </c>
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
       <c r="W17" s="6"/>
@@ -3316,7 +3380,10 @@
       <c r="I18" s="6">
         <v>6.7</v>
       </c>
-      <c r="J18" s="6"/>
+      <c r="J18" s="81">
+        <f>+T18-SUM(G18:I18)</f>
+        <v>4.8000000000000007</v>
+      </c>
       <c r="K18" s="6"/>
       <c r="L18" s="6">
         <v>16.100000000000001</v>
@@ -3342,7 +3409,9 @@
       <c r="S18" s="6">
         <v>25.4</v>
       </c>
-      <c r="T18" s="6"/>
+      <c r="T18" s="6">
+        <v>23.2</v>
+      </c>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
       <c r="W18" s="6"/>
@@ -3414,7 +3483,10 @@
       <c r="I19" s="6">
         <v>8.5</v>
       </c>
-      <c r="J19" s="6"/>
+      <c r="J19" s="81">
+        <f>+T19-SUM(G19:I19)</f>
+        <v>27.799999999999997</v>
+      </c>
       <c r="K19" s="6"/>
       <c r="L19" s="6">
         <v>23.5</v>
@@ -3440,7 +3512,9 @@
       <c r="S19" s="6">
         <v>130.19999999999999</v>
       </c>
-      <c r="T19" s="6"/>
+      <c r="T19" s="6">
+        <v>71.3</v>
+      </c>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
@@ -3512,7 +3586,10 @@
       <c r="I20" s="6">
         <v>86.1</v>
       </c>
-      <c r="J20" s="6"/>
+      <c r="J20" s="81">
+        <f>+T20-SUM(G20:I20)</f>
+        <v>97.899999999999977</v>
+      </c>
       <c r="K20" s="6"/>
       <c r="L20" s="6">
         <v>100.9</v>
@@ -3538,7 +3615,9 @@
       <c r="S20" s="6">
         <v>316.5</v>
       </c>
-      <c r="T20" s="6"/>
+      <c r="T20" s="6">
+        <v>358.9</v>
+      </c>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6"/>
@@ -3616,10 +3695,13 @@
         <f>+I17+I18+I19-I20</f>
         <v>295.10000000000025</v>
       </c>
-      <c r="J21" s="6"/>
+      <c r="J21" s="6">
+        <f>+J17+J18+J19-J20</f>
+        <v>221.00000000000011</v>
+      </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6">
-        <f t="shared" ref="L21:S21" si="6">+L17+L18+L19-L20</f>
+        <f t="shared" ref="L21:T21" si="6">+L17+L18+L19-L20</f>
         <v>851.70000000000039</v>
       </c>
       <c r="M21" s="6">
@@ -3650,7 +3732,10 @@
         <f t="shared" si="6"/>
         <v>1219.3</v>
       </c>
-      <c r="T21" s="6"/>
+      <c r="T21" s="6">
+        <f t="shared" si="6"/>
+        <v>877.80000000000052</v>
+      </c>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
       <c r="W21" s="6"/>
@@ -3722,7 +3807,10 @@
       <c r="I22" s="6">
         <v>67.8</v>
       </c>
-      <c r="J22" s="6"/>
+      <c r="J22" s="81">
+        <f>+T22-SUM(G22:I22)</f>
+        <v>57.400000000000006</v>
+      </c>
       <c r="K22" s="6"/>
       <c r="L22" s="6">
         <v>140.1</v>
@@ -3748,7 +3836,9 @@
       <c r="S22" s="6">
         <v>279.60000000000002</v>
       </c>
-      <c r="T22" s="6"/>
+      <c r="T22" s="6">
+        <v>208.4</v>
+      </c>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
@@ -3826,7 +3916,10 @@
         <f>+I21-I22</f>
         <v>227.30000000000024</v>
       </c>
-      <c r="J23" s="6"/>
+      <c r="J23" s="6">
+        <f>+J21-J22</f>
+        <v>163.60000000000011</v>
+      </c>
       <c r="K23" s="6"/>
       <c r="L23" s="6">
         <f t="shared" ref="L23:R23" si="8">+L21-L22</f>
@@ -3860,7 +3953,10 @@
         <f>+S21-S22</f>
         <v>939.69999999999993</v>
       </c>
-      <c r="T23" s="6"/>
+      <c r="T23" s="6">
+        <f>+T21-T22</f>
+        <v>669.40000000000055</v>
+      </c>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
       <c r="W23" s="6"/>
@@ -4002,9 +4098,9 @@
         <f t="shared" si="10"/>
         <v>2.8817749603803517</v>
       </c>
-      <c r="J25" s="6" t="e">
+      <c r="J25" s="6">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>2.0741679873217129</v>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="6">
@@ -4039,7 +4135,10 @@
         <f>+S23/S26</f>
         <v>11.437160731238283</v>
       </c>
-      <c r="T25" s="6"/>
+      <c r="T25" s="6">
+        <f>+T23/T26</f>
+        <v>8.5012890362073197</v>
+      </c>
       <c r="U25" s="6"/>
       <c r="V25" s="6"/>
       <c r="W25" s="6"/>
@@ -4111,7 +4210,9 @@
       <c r="I26" s="6">
         <v>78.875</v>
       </c>
-      <c r="J26" s="6"/>
+      <c r="J26" s="6">
+        <v>78.875</v>
+      </c>
       <c r="K26" s="6"/>
       <c r="L26" s="6">
         <f>+KPI!C4</f>
@@ -4141,7 +4242,9 @@
       <c r="S26" s="6">
         <v>82.162000000000006</v>
       </c>
-      <c r="T26" s="6"/>
+      <c r="T26" s="6">
+        <v>78.741</v>
+      </c>
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
       <c r="W26" s="6"/>
@@ -4293,7 +4396,10 @@
         <f>+S6/R6-1</f>
         <v>1.9654501066163954E-2</v>
       </c>
-      <c r="T28" s="6"/>
+      <c r="T28" s="21">
+        <f>+T6/S6-1</f>
+        <v>-4.1036520684952338E-2</v>
+      </c>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
@@ -4378,10 +4484,13 @@
         <v>0.42683899262409453</v>
       </c>
       <c r="S29" s="21">
-        <f t="shared" ref="S29:S32" si="17">+S7/R7-1</f>
+        <f t="shared" ref="S29:T32" si="17">+S7/R7-1</f>
         <v>3.1831412271509985E-2</v>
       </c>
-      <c r="T29" s="6"/>
+      <c r="T29" s="21">
+        <f t="shared" si="17"/>
+        <v>2.4891677198050299E-2</v>
+      </c>
       <c r="U29" s="6"/>
       <c r="V29" s="6"/>
       <c r="W29" s="6"/>
@@ -4469,7 +4578,10 @@
         <f t="shared" si="17"/>
         <v>1.1774443869632694</v>
       </c>
-      <c r="T30" s="6"/>
+      <c r="T30" s="21">
+        <f t="shared" si="17"/>
+        <v>1.7343787122832133E-2</v>
+      </c>
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
       <c r="W30" s="6"/>
@@ -4557,7 +4669,10 @@
         <f t="shared" si="17"/>
         <v>4.2990468625893508E-2</v>
       </c>
-      <c r="T31" s="6"/>
+      <c r="T31" s="21">
+        <f t="shared" si="17"/>
+        <v>-0.1413612565445026</v>
+      </c>
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
       <c r="W31" s="6"/>
@@ -4625,7 +4740,7 @@
       </c>
       <c r="J32" s="22">
         <f>+J10/F10-1</f>
-        <v>-1</v>
+        <v>-4.6469989827059965E-2</v>
       </c>
       <c r="K32" s="22"/>
       <c r="L32" s="6"/>
@@ -4657,7 +4772,10 @@
         <f t="shared" si="17"/>
         <v>5.3969235703077656E-2</v>
       </c>
-      <c r="T32" s="6"/>
+      <c r="T32" s="22">
+        <f t="shared" si="17"/>
+        <v>-1.8082828919485761E-2</v>
+      </c>
       <c r="U32" s="6"/>
       <c r="V32" s="6"/>
       <c r="W32" s="6"/>
@@ -4735,9 +4853,9 @@
         <f t="shared" ref="I33:J33" si="19">+I12/I10</f>
         <v>0.44550969329317447</v>
       </c>
-      <c r="J33" s="21" t="e">
+      <c r="J33" s="21">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.43566764818845216</v>
       </c>
       <c r="K33" s="21"/>
       <c r="L33" s="6"/>
@@ -4769,7 +4887,10 @@
         <f>+S12/S10</f>
         <v>0.46494821834146549</v>
       </c>
-      <c r="T33" s="6"/>
+      <c r="T33" s="21">
+        <f>+T12/T10</f>
+        <v>0.44282125347233753</v>
+      </c>
       <c r="U33" s="6"/>
       <c r="V33" s="6"/>
       <c r="W33" s="6"/>
@@ -4847,9 +4968,9 @@
         <f t="shared" ref="I34:J34" si="23">+I17/I10</f>
         <v>0.15526237644763086</v>
       </c>
-      <c r="J34" s="21" t="e">
+      <c r="J34" s="21">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>0.12217812486664108</v>
       </c>
       <c r="K34" s="21"/>
       <c r="L34" s="6"/>
@@ -4881,7 +5002,10 @@
         <f>+S17/S10</f>
         <v>0.1499875028526097</v>
       </c>
-      <c r="T34" s="6"/>
+      <c r="T34" s="21">
+        <f>+T17/T10</f>
+        <v>0.12640968602321906</v>
+      </c>
       <c r="U34" s="6"/>
       <c r="V34" s="6"/>
       <c r="W34" s="6"/>
@@ -4959,9 +5083,9 @@
         <f t="shared" ref="I35:J35" si="27">+I22/I21</f>
         <v>0.22975262622839696</v>
       </c>
-      <c r="J35" s="21" t="e">
+      <c r="J35" s="21">
         <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
+        <v>0.25972850678733023</v>
       </c>
       <c r="K35" s="21"/>
       <c r="L35" s="6"/>
@@ -4993,7 +5117,10 @@
         <f>+S22/S21</f>
         <v>0.22931190027064713</v>
       </c>
-      <c r="T35" s="6"/>
+      <c r="T35" s="21">
+        <f>+T22/T21</f>
+        <v>0.23741171109592149</v>
+      </c>
       <c r="U35" s="6"/>
       <c r="V35" s="6"/>
       <c r="W35" s="6"/>
@@ -5140,7 +5267,9 @@
       <c r="S37" s="6">
         <v>5409.9</v>
       </c>
-      <c r="T37" s="6"/>
+      <c r="T37" s="6">
+        <v>5071.8</v>
+      </c>
       <c r="U37" s="6"/>
       <c r="V37" s="6"/>
       <c r="W37" s="6"/>
@@ -5223,7 +5352,9 @@
       <c r="S38" s="6">
         <v>3224.1</v>
       </c>
-      <c r="T38" s="6"/>
+      <c r="T38" s="6">
+        <v>3003</v>
+      </c>
       <c r="U38" s="6"/>
       <c r="V38" s="6"/>
       <c r="W38" s="6"/>
@@ -5306,7 +5437,9 @@
       <c r="S39" s="6">
         <v>65.3</v>
       </c>
-      <c r="T39" s="6"/>
+      <c r="T39" s="6">
+        <v>179.7</v>
+      </c>
       <c r="U39" s="6"/>
       <c r="V39" s="6"/>
       <c r="W39" s="6"/>
@@ -5389,7 +5522,9 @@
       <c r="S40" s="6">
         <v>400</v>
       </c>
-      <c r="T40" s="6"/>
+      <c r="T40" s="6">
+        <v>345.2</v>
+      </c>
       <c r="U40" s="6"/>
       <c r="V40" s="6"/>
       <c r="W40" s="6"/>
@@ -5472,7 +5607,9 @@
       <c r="S41" s="6">
         <v>215.5</v>
       </c>
-      <c r="T41" s="6"/>
+      <c r="T41" s="6">
+        <v>97</v>
+      </c>
       <c r="U41" s="6"/>
       <c r="V41" s="6"/>
       <c r="W41" s="6"/>
@@ -5555,7 +5692,9 @@
       <c r="S42" s="6">
         <v>1664.2</v>
       </c>
-      <c r="T42" s="6"/>
+      <c r="T42" s="6">
+        <v>1538.5</v>
+      </c>
       <c r="U42" s="6"/>
       <c r="V42" s="6"/>
       <c r="W42" s="6"/>
@@ -5638,7 +5777,9 @@
       <c r="S43" s="6">
         <v>402.3</v>
       </c>
-      <c r="T43" s="6"/>
+      <c r="T43" s="6">
+        <v>368.9</v>
+      </c>
       <c r="U43" s="6"/>
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
@@ -5722,7 +5863,9 @@
       <c r="S44" s="6">
         <v>261.89999999999998</v>
       </c>
-      <c r="T44" s="6"/>
+      <c r="T44" s="6">
+        <v>243.6</v>
+      </c>
       <c r="U44" s="6"/>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
@@ -5805,7 +5948,9 @@
       <c r="S45" s="6">
         <v>129.80000000000001</v>
       </c>
-      <c r="T45" s="6"/>
+      <c r="T45" s="6">
+        <v>114.2</v>
+      </c>
       <c r="U45" s="6"/>
       <c r="V45" s="6"/>
       <c r="W45" s="6"/>
@@ -5896,7 +6041,10 @@
         <f>+SUM(S37:S45)</f>
         <v>11772.999999999998</v>
       </c>
-      <c r="T46" s="6"/>
+      <c r="T46" s="6">
+        <f>+SUM(T37:T45)</f>
+        <v>10961.900000000001</v>
+      </c>
       <c r="U46" s="6"/>
       <c r="V46" s="6"/>
       <c r="W46" s="6"/>
@@ -5979,7 +6127,9 @@
       <c r="S47" s="6">
         <v>3478.2</v>
       </c>
-      <c r="T47" s="6"/>
+      <c r="T47" s="6">
+        <v>3210.7</v>
+      </c>
       <c r="U47" s="6"/>
       <c r="V47" s="6"/>
       <c r="W47" s="6"/>
@@ -6062,7 +6212,9 @@
       <c r="S48" s="6">
         <v>1213.7</v>
       </c>
-      <c r="T48" s="6"/>
+      <c r="T48" s="6">
+        <v>1429.6</v>
+      </c>
       <c r="U48" s="6"/>
       <c r="V48" s="6"/>
       <c r="W48" s="6"/>
@@ -6145,7 +6297,9 @@
       <c r="S49" s="6">
         <v>207</v>
       </c>
-      <c r="T49" s="6"/>
+      <c r="T49" s="6">
+        <v>167.3</v>
+      </c>
       <c r="U49" s="6"/>
       <c r="V49" s="6"/>
       <c r="W49" s="6"/>
@@ -6228,7 +6382,9 @@
       <c r="S50" s="6">
         <v>97.4</v>
       </c>
-      <c r="T50" s="6"/>
+      <c r="T50" s="6">
+        <v>143</v>
+      </c>
       <c r="U50" s="6"/>
       <c r="V50" s="6"/>
       <c r="W50" s="6"/>
@@ -6313,7 +6469,9 @@
       <c r="S51" s="6">
         <v>174.6</v>
       </c>
-      <c r="T51" s="6"/>
+      <c r="T51" s="6">
+        <v>157.80000000000001</v>
+      </c>
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
       <c r="W51" s="6"/>
@@ -6396,7 +6554,9 @@
       <c r="S52" s="6">
         <v>160.1</v>
       </c>
-      <c r="T52" s="6"/>
+      <c r="T52" s="6">
+        <v>197.7</v>
+      </c>
       <c r="U52" s="6"/>
       <c r="V52" s="6"/>
       <c r="W52" s="6"/>
@@ -6444,7 +6604,7 @@
     </row>
     <row r="53" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
@@ -6456,38 +6616,32 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
       <c r="L53" s="6">
-        <f t="shared" ref="L53:P53" si="31">+SUM(L47:L52)</f>
-        <v>3977.8</v>
+        <v>0</v>
       </c>
       <c r="M53" s="6">
-        <f t="shared" si="31"/>
-        <v>4028.2999999999997</v>
+        <v>0</v>
       </c>
       <c r="N53" s="6">
-        <f t="shared" si="31"/>
-        <v>4457.6000000000004</v>
+        <v>0</v>
       </c>
       <c r="O53" s="6">
-        <f t="shared" si="31"/>
-        <v>4029.5</v>
+        <v>0</v>
       </c>
       <c r="P53" s="6">
-        <f t="shared" si="31"/>
-        <v>4323.3000000000011</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="6">
-        <f t="shared" ref="Q53:R53" si="32">+SUM(Q47:Q52)</f>
-        <v>4364.1999999999989</v>
+        <v>0</v>
       </c>
       <c r="R53" s="6">
-        <f t="shared" si="32"/>
-        <v>4642.8</v>
+        <v>0</v>
       </c>
       <c r="S53" s="6">
-        <f>+SUM(S47:S52)</f>
-        <v>5331</v>
-      </c>
-      <c r="T53" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="6">
+        <v>35.299999999999997</v>
+      </c>
       <c r="U53" s="6"/>
       <c r="V53" s="6"/>
       <c r="W53" s="6"/>
@@ -6534,51 +6688,54 @@
       <c r="BL53" s="6"/>
     </row>
     <row r="54" spans="2:64" x14ac:dyDescent="0.2">
-      <c r="B54" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7">
-        <f t="shared" ref="L54" si="33">+L53+L46</f>
-        <v>12990.400000000001</v>
-      </c>
-      <c r="M54" s="7">
-        <f t="shared" ref="M54" si="34">+M53+M46</f>
-        <v>13403.099999999999</v>
-      </c>
-      <c r="N54" s="7">
-        <f t="shared" ref="N54" si="35">+N53+N46</f>
-        <v>13872</v>
-      </c>
-      <c r="O54" s="7">
-        <f t="shared" ref="O54:Q54" si="36">+O53+O46</f>
-        <v>13996</v>
-      </c>
-      <c r="P54" s="7">
-        <f t="shared" si="36"/>
-        <v>14583.700000000004</v>
-      </c>
-      <c r="Q54" s="7">
-        <f t="shared" si="36"/>
-        <v>15122.1</v>
-      </c>
-      <c r="R54" s="7">
-        <f>+R53+R46</f>
-        <v>15853.400000000001</v>
-      </c>
-      <c r="S54" s="7">
-        <f>+S53+S46</f>
-        <v>17104</v>
-      </c>
-      <c r="T54" s="6"/>
+      <c r="B54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6">
+        <f t="shared" ref="L54:S54" si="31">+SUM(L47:L53)</f>
+        <v>3977.8</v>
+      </c>
+      <c r="M54" s="6">
+        <f t="shared" si="31"/>
+        <v>4028.2999999999997</v>
+      </c>
+      <c r="N54" s="6">
+        <f t="shared" si="31"/>
+        <v>4457.6000000000004</v>
+      </c>
+      <c r="O54" s="6">
+        <f t="shared" si="31"/>
+        <v>4029.5</v>
+      </c>
+      <c r="P54" s="6">
+        <f t="shared" si="31"/>
+        <v>4323.3000000000011</v>
+      </c>
+      <c r="Q54" s="6">
+        <f t="shared" si="31"/>
+        <v>4364.1999999999989</v>
+      </c>
+      <c r="R54" s="6">
+        <f t="shared" si="31"/>
+        <v>4642.8</v>
+      </c>
+      <c r="S54" s="6">
+        <f t="shared" si="31"/>
+        <v>5331</v>
+      </c>
+      <c r="T54" s="6">
+        <f>+SUM(T47:T53)</f>
+        <v>5341.4</v>
+      </c>
       <c r="U54" s="6"/>
       <c r="V54" s="6"/>
       <c r="W54" s="6"/>
@@ -6625,43 +6782,54 @@
       <c r="BL54" s="6"/>
     </row>
     <row r="55" spans="2:64" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6">
-        <v>8448.2000000000007</v>
-      </c>
-      <c r="M55" s="6">
-        <v>8818.2000000000007</v>
-      </c>
-      <c r="N55" s="6">
-        <v>9102.7000000000007</v>
-      </c>
-      <c r="O55" s="6">
-        <v>8372.2999999999993</v>
-      </c>
-      <c r="P55" s="6">
-        <v>8967.7999999999993</v>
-      </c>
-      <c r="Q55" s="6">
-        <v>9341.6</v>
-      </c>
-      <c r="R55" s="6">
-        <v>9434</v>
-      </c>
-      <c r="S55" s="6">
-        <v>9217</v>
-      </c>
-      <c r="T55" s="6"/>
+      <c r="B55" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7">
+        <f>+L54+L46</f>
+        <v>12990.400000000001</v>
+      </c>
+      <c r="M55" s="7">
+        <f>+M54+M46</f>
+        <v>13403.099999999999</v>
+      </c>
+      <c r="N55" s="7">
+        <f>+N54+N46</f>
+        <v>13872</v>
+      </c>
+      <c r="O55" s="7">
+        <f>+O54+O46</f>
+        <v>13996</v>
+      </c>
+      <c r="P55" s="7">
+        <f>+P54+P46</f>
+        <v>14583.700000000004</v>
+      </c>
+      <c r="Q55" s="7">
+        <f>+Q54+Q46</f>
+        <v>15122.1</v>
+      </c>
+      <c r="R55" s="7">
+        <f>+R54+R46</f>
+        <v>15853.400000000001</v>
+      </c>
+      <c r="S55" s="7">
+        <f>+S54+S46</f>
+        <v>17104</v>
+      </c>
+      <c r="T55" s="7">
+        <f>+T54+T46</f>
+        <v>16303.300000000001</v>
+      </c>
       <c r="U55" s="6"/>
       <c r="V55" s="6"/>
       <c r="W55" s="6"/>
@@ -6709,7 +6877,7 @@
     </row>
     <row r="56" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
@@ -6721,30 +6889,32 @@
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
       <c r="L56" s="6">
-        <v>2606.3000000000002</v>
+        <v>8448.2000000000007</v>
       </c>
       <c r="M56" s="6">
-        <v>2658.1</v>
+        <v>8818.2000000000007</v>
       </c>
       <c r="N56" s="6">
-        <v>2682.1</v>
+        <v>9102.7000000000007</v>
       </c>
       <c r="O56" s="6">
-        <v>2843.5</v>
+        <v>8372.2999999999993</v>
       </c>
       <c r="P56" s="6">
-        <v>2918</v>
+        <v>8967.7999999999993</v>
       </c>
       <c r="Q56" s="6">
-        <v>3101.1</v>
+        <v>9341.6</v>
       </c>
       <c r="R56" s="6">
-        <v>3656.7</v>
+        <v>9434</v>
       </c>
       <c r="S56" s="6">
-        <v>3710.6</v>
-      </c>
-      <c r="T56" s="6"/>
+        <v>9217</v>
+      </c>
+      <c r="T56" s="6">
+        <v>8572.4</v>
+      </c>
       <c r="U56" s="6"/>
       <c r="V56" s="6"/>
       <c r="W56" s="6"/>
@@ -6792,7 +6962,7 @@
     </row>
     <row r="57" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
@@ -6804,30 +6974,32 @@
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
       <c r="L57" s="6">
-        <v>571.5</v>
+        <v>2606.3000000000002</v>
       </c>
       <c r="M57" s="6">
-        <v>515.70000000000005</v>
+        <v>2658.1</v>
       </c>
       <c r="N57" s="6">
-        <v>516.70000000000005</v>
+        <v>2682.1</v>
       </c>
       <c r="O57" s="6">
-        <v>628.20000000000005</v>
+        <v>2843.5</v>
       </c>
       <c r="P57" s="6">
-        <v>698.9</v>
+        <v>2918</v>
       </c>
       <c r="Q57" s="6">
-        <v>673.5</v>
+        <v>3101.1</v>
       </c>
       <c r="R57" s="6">
-        <v>706.8</v>
+        <v>3656.7</v>
       </c>
       <c r="S57" s="6">
-        <v>742.3</v>
-      </c>
-      <c r="T57" s="6"/>
+        <v>3710.6</v>
+      </c>
+      <c r="T57" s="6">
+        <v>3726.6</v>
+      </c>
       <c r="U57" s="6"/>
       <c r="V57" s="6"/>
       <c r="W57" s="6"/>
@@ -6875,7 +7047,7 @@
     </row>
     <row r="58" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
@@ -6887,30 +7059,32 @@
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
       <c r="L58" s="6">
-        <v>237.8</v>
+        <v>571.5</v>
       </c>
       <c r="M58" s="6">
-        <v>240.8</v>
+        <v>515.70000000000005</v>
       </c>
       <c r="N58" s="6">
-        <v>281.7</v>
+        <v>516.70000000000005</v>
       </c>
       <c r="O58" s="6">
-        <v>289.3</v>
+        <v>628.20000000000005</v>
       </c>
       <c r="P58" s="6">
-        <v>307.39999999999998</v>
+        <v>698.9</v>
       </c>
       <c r="Q58" s="6">
-        <v>204.7</v>
+        <v>673.5</v>
       </c>
       <c r="R58" s="6">
-        <v>195.3</v>
+        <v>706.8</v>
       </c>
       <c r="S58" s="6">
-        <v>213.7</v>
-      </c>
-      <c r="T58" s="6"/>
+        <v>742.3</v>
+      </c>
+      <c r="T58" s="6">
+        <v>701.7</v>
+      </c>
       <c r="U58" s="6"/>
       <c r="V58" s="6"/>
       <c r="W58" s="6"/>
@@ -6958,7 +7132,7 @@
     </row>
     <row r="59" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
@@ -6970,30 +7144,32 @@
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
       <c r="L59" s="6">
-        <v>33.700000000000003</v>
+        <v>237.8</v>
       </c>
       <c r="M59" s="6">
-        <v>33.700000000000003</v>
+        <v>240.8</v>
       </c>
       <c r="N59" s="6">
-        <v>18.5</v>
+        <v>281.7</v>
       </c>
       <c r="O59" s="6">
-        <v>20</v>
+        <v>289.3</v>
       </c>
       <c r="P59" s="6">
-        <v>17.899999999999999</v>
+        <v>307.39999999999998</v>
       </c>
       <c r="Q59" s="6">
-        <v>17.899999999999999</v>
+        <v>204.7</v>
       </c>
       <c r="R59" s="6">
-        <v>17.899999999999999</v>
+        <v>195.3</v>
       </c>
       <c r="S59" s="6">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="T59" s="6"/>
+        <v>213.7</v>
+      </c>
+      <c r="T59" s="6">
+        <v>194.6</v>
+      </c>
       <c r="U59" s="6"/>
       <c r="V59" s="6"/>
       <c r="W59" s="6"/>
@@ -7041,7 +7217,7 @@
     </row>
     <row r="60" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
@@ -7053,30 +7229,32 @@
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
       <c r="L60" s="6">
-        <v>0</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="M60" s="6">
-        <v>0</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="N60" s="6">
-        <v>159.80000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="O60" s="6">
-        <v>159.80000000000001</v>
+        <v>20</v>
       </c>
       <c r="P60" s="6">
-        <v>149.4</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="Q60" s="6">
-        <v>275.10000000000002</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="R60" s="6">
-        <v>245.8</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="S60" s="6">
-        <v>337.3</v>
-      </c>
-      <c r="T60" s="6"/>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="T60" s="6">
+        <v>16.5</v>
+      </c>
       <c r="U60" s="6"/>
       <c r="V60" s="6"/>
       <c r="W60" s="6"/>
@@ -7124,7 +7302,7 @@
     </row>
     <row r="61" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
@@ -7136,30 +7314,32 @@
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
       <c r="L61" s="6">
-        <v>22.4</v>
+        <v>0</v>
       </c>
       <c r="M61" s="6">
-        <v>27.4</v>
+        <v>0</v>
       </c>
       <c r="N61" s="6">
-        <v>31.4</v>
+        <v>159.80000000000001</v>
       </c>
       <c r="O61" s="6">
-        <v>19</v>
+        <v>159.80000000000001</v>
       </c>
       <c r="P61" s="6">
-        <v>58.4</v>
+        <v>149.4</v>
       </c>
       <c r="Q61" s="6">
-        <v>31</v>
+        <v>275.10000000000002</v>
       </c>
       <c r="R61" s="6">
-        <v>46.2</v>
+        <v>245.8</v>
       </c>
       <c r="S61" s="6">
-        <v>32.5</v>
-      </c>
-      <c r="T61" s="6"/>
+        <v>337.3</v>
+      </c>
+      <c r="T61" s="6">
+        <v>323</v>
+      </c>
       <c r="U61" s="6"/>
       <c r="V61" s="6"/>
       <c r="W61" s="6"/>
@@ -7207,7 +7387,7 @@
     </row>
     <row r="62" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
@@ -7219,38 +7399,32 @@
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
       <c r="L62" s="6">
-        <f t="shared" ref="L62:P62" si="37">+SUM(L56:L61)</f>
-        <v>3471.7000000000003</v>
+        <v>22.4</v>
       </c>
       <c r="M62" s="6">
-        <f t="shared" si="37"/>
-        <v>3475.7000000000003</v>
+        <v>27.4</v>
       </c>
       <c r="N62" s="6">
-        <f t="shared" si="37"/>
-        <v>3690.2000000000003</v>
+        <v>31.4</v>
       </c>
       <c r="O62" s="6">
-        <f t="shared" si="37"/>
-        <v>3959.8</v>
+        <v>19</v>
       </c>
       <c r="P62" s="6">
-        <f t="shared" si="37"/>
-        <v>4150</v>
+        <v>58.4</v>
       </c>
       <c r="Q62" s="6">
-        <f t="shared" ref="Q62:R62" si="38">+SUM(Q56:Q61)</f>
-        <v>4303.3</v>
+        <v>31</v>
       </c>
       <c r="R62" s="6">
-        <f t="shared" si="38"/>
-        <v>4868.7</v>
+        <v>46.2</v>
       </c>
       <c r="S62" s="6">
-        <f>+SUM(S56:S61)</f>
-        <v>5052.7999999999993</v>
-      </c>
-      <c r="T62" s="6"/>
+        <v>32.5</v>
+      </c>
+      <c r="T62" s="6">
+        <v>34.799999999999997</v>
+      </c>
       <c r="U62" s="6"/>
       <c r="V62" s="6"/>
       <c r="W62" s="6"/>
@@ -7298,7 +7472,7 @@
     </row>
     <row r="63" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -7310,30 +7484,41 @@
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
       <c r="L63" s="6">
-        <v>0</v>
+        <f t="shared" ref="L63:P63" si="32">+SUM(L57:L62)</f>
+        <v>3471.7000000000003</v>
       </c>
       <c r="M63" s="6">
-        <v>0</v>
+        <f t="shared" si="32"/>
+        <v>3475.7000000000003</v>
       </c>
       <c r="N63" s="6">
-        <v>0</v>
+        <f t="shared" si="32"/>
+        <v>3690.2000000000003</v>
       </c>
       <c r="O63" s="6">
-        <v>0</v>
+        <f t="shared" si="32"/>
+        <v>3959.8</v>
       </c>
       <c r="P63" s="6">
-        <v>0</v>
+        <f t="shared" si="32"/>
+        <v>4150</v>
       </c>
       <c r="Q63" s="6">
-        <v>0</v>
+        <f t="shared" ref="Q63:R63" si="33">+SUM(Q57:Q62)</f>
+        <v>4303.3</v>
       </c>
       <c r="R63" s="6">
-        <v>0</v>
+        <f t="shared" si="33"/>
+        <v>4868.7</v>
       </c>
       <c r="S63" s="6">
-        <v>1247.8</v>
-      </c>
-      <c r="T63" s="6"/>
+        <f>+SUM(S57:S62)</f>
+        <v>5052.7999999999993</v>
+      </c>
+      <c r="T63" s="6">
+        <f>+SUM(T57:T62)</f>
+        <v>4997.2000000000007</v>
+      </c>
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
       <c r="W63" s="6"/>
@@ -7381,7 +7566,7 @@
     </row>
     <row r="64" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
@@ -7393,30 +7578,33 @@
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
       <c r="L64" s="6">
-        <v>365.4</v>
+        <v>0</v>
       </c>
       <c r="M64" s="6">
-        <v>377.1</v>
+        <v>0</v>
       </c>
       <c r="N64" s="6">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="O64" s="6">
-        <v>525.1</v>
+        <v>0</v>
       </c>
       <c r="P64" s="6">
-        <v>504.5</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="6">
-        <v>506.8</v>
+        <v>0</v>
       </c>
       <c r="R64" s="6">
-        <v>508.2</v>
+        <v>0</v>
       </c>
       <c r="S64" s="6">
-        <v>383.6</v>
-      </c>
-      <c r="T64" s="6"/>
+        <v>1247.8</v>
+      </c>
+      <c r="T64" s="6">
+        <f>1150+204</f>
+        <v>1354</v>
+      </c>
       <c r="U64" s="6"/>
       <c r="V64" s="6"/>
       <c r="W64" s="6"/>
@@ -7464,7 +7652,7 @@
     </row>
     <row r="65" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
@@ -7476,30 +7664,32 @@
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
       <c r="L65" s="6">
-        <v>170.5</v>
+        <v>365.4</v>
       </c>
       <c r="M65" s="6">
-        <v>132.4</v>
+        <v>377.1</v>
       </c>
       <c r="N65" s="6">
-        <v>121.5</v>
+        <v>334</v>
       </c>
       <c r="O65" s="6">
-        <v>136.69999999999999</v>
+        <v>525.1</v>
       </c>
       <c r="P65" s="6">
-        <v>102.4</v>
+        <v>504.5</v>
       </c>
       <c r="Q65" s="6">
-        <v>207.4</v>
+        <v>506.8</v>
       </c>
       <c r="R65" s="6">
-        <v>120.3</v>
+        <v>508.2</v>
       </c>
       <c r="S65" s="6">
-        <v>85.1</v>
-      </c>
-      <c r="T65" s="6"/>
+        <v>383.6</v>
+      </c>
+      <c r="T65" s="6">
+        <v>422</v>
+      </c>
       <c r="U65" s="6"/>
       <c r="V65" s="6"/>
       <c r="W65" s="6"/>
@@ -7547,7 +7737,7 @@
     </row>
     <row r="66" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
@@ -7559,30 +7749,32 @@
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
       <c r="L66" s="6">
-        <v>27.4</v>
+        <v>170.5</v>
       </c>
       <c r="M66" s="6">
-        <v>104.1</v>
+        <v>132.4</v>
       </c>
       <c r="N66" s="6">
-        <v>38.4</v>
+        <v>121.5</v>
       </c>
       <c r="O66" s="6">
-        <v>211.2</v>
+        <v>136.69999999999999</v>
       </c>
       <c r="P66" s="6">
-        <v>64.3</v>
+        <v>102.4</v>
       </c>
       <c r="Q66" s="6">
-        <v>19.8</v>
+        <v>207.4</v>
       </c>
       <c r="R66" s="6">
-        <v>17.8</v>
+        <v>120.3</v>
       </c>
       <c r="S66" s="6">
-        <v>46.9</v>
-      </c>
-      <c r="T66" s="6"/>
+        <v>85.1</v>
+      </c>
+      <c r="T66" s="6">
+        <v>30.4</v>
+      </c>
       <c r="U66" s="6"/>
       <c r="V66" s="6"/>
       <c r="W66" s="6"/>
@@ -7630,7 +7822,7 @@
     </row>
     <row r="67" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
@@ -7642,30 +7834,32 @@
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
       <c r="L67" s="6">
-        <v>0</v>
+        <v>27.4</v>
       </c>
       <c r="M67" s="6">
-        <v>0</v>
+        <v>104.1</v>
       </c>
       <c r="N67" s="6">
-        <v>67</v>
+        <v>38.4</v>
       </c>
       <c r="O67" s="6">
-        <v>54.6</v>
+        <v>211.2</v>
       </c>
       <c r="P67" s="6">
-        <v>48.5</v>
+        <v>64.3</v>
       </c>
       <c r="Q67" s="6">
-        <v>56.3</v>
+        <v>19.8</v>
       </c>
       <c r="R67" s="6">
-        <v>59.1</v>
+        <v>17.8</v>
       </c>
       <c r="S67" s="6">
-        <v>73.400000000000006</v>
-      </c>
-      <c r="T67" s="6"/>
+        <v>46.9</v>
+      </c>
+      <c r="T67" s="6">
+        <v>18.399999999999999</v>
+      </c>
       <c r="U67" s="6"/>
       <c r="V67" s="6"/>
       <c r="W67" s="6"/>
@@ -7713,7 +7907,7 @@
     </row>
     <row r="68" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
@@ -7725,30 +7919,32 @@
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
       <c r="L68" s="6">
-        <v>507.2</v>
+        <v>0</v>
       </c>
       <c r="M68" s="6">
-        <v>495.6</v>
+        <v>0</v>
       </c>
       <c r="N68" s="6">
-        <v>518.20000000000005</v>
+        <v>67</v>
       </c>
       <c r="O68" s="6">
-        <v>736.3</v>
+        <v>54.6</v>
       </c>
       <c r="P68" s="6">
-        <v>746.2</v>
+        <v>48.5</v>
       </c>
       <c r="Q68" s="6">
-        <v>686.9</v>
+        <v>56.3</v>
       </c>
       <c r="R68" s="6">
-        <v>845.3</v>
+        <v>59.1</v>
       </c>
       <c r="S68" s="6">
-        <v>997.4</v>
-      </c>
-      <c r="T68" s="6"/>
+        <v>73.400000000000006</v>
+      </c>
+      <c r="T68" s="6">
+        <v>61.1</v>
+      </c>
       <c r="U68" s="6"/>
       <c r="V68" s="6"/>
       <c r="W68" s="6"/>
@@ -7796,7 +7992,7 @@
     </row>
     <row r="69" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
@@ -7808,38 +8004,32 @@
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
       <c r="L69" s="6">
-        <f t="shared" ref="L69:M69" si="39">+SUM(L63:L68)</f>
-        <v>1070.5</v>
+        <v>507.2</v>
       </c>
       <c r="M69" s="6">
-        <f t="shared" si="39"/>
-        <v>1109.2</v>
+        <v>495.6</v>
       </c>
       <c r="N69" s="6">
-        <f t="shared" ref="N69:S69" si="40">+SUM(N63:N68)</f>
-        <v>1079.0999999999999</v>
+        <v>518.20000000000005</v>
       </c>
       <c r="O69" s="6">
-        <f t="shared" si="40"/>
-        <v>1663.9</v>
+        <v>736.3</v>
       </c>
       <c r="P69" s="6">
-        <f t="shared" si="40"/>
-        <v>1465.9</v>
+        <v>746.2</v>
       </c>
       <c r="Q69" s="6">
-        <f t="shared" si="40"/>
-        <v>1477.1999999999998</v>
+        <v>686.9</v>
       </c>
       <c r="R69" s="6">
-        <f t="shared" si="40"/>
-        <v>1550.6999999999998</v>
+        <v>845.3</v>
       </c>
       <c r="S69" s="6">
-        <f t="shared" si="40"/>
-        <v>2834.2000000000003</v>
-      </c>
-      <c r="T69" s="6"/>
+        <v>997.4</v>
+      </c>
+      <c r="T69" s="6">
+        <v>847.8</v>
+      </c>
       <c r="U69" s="6"/>
       <c r="V69" s="6"/>
       <c r="W69" s="6"/>
@@ -7887,7 +8077,7 @@
     </row>
     <row r="70" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
@@ -7899,38 +8089,41 @@
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
       <c r="L70" s="6">
-        <f t="shared" ref="L70" si="41">+L69+L62</f>
-        <v>4542.2000000000007</v>
+        <f t="shared" ref="L70:M70" si="34">+SUM(L64:L69)</f>
+        <v>1070.5</v>
       </c>
       <c r="M70" s="6">
-        <f t="shared" ref="M70" si="42">+M69+M62</f>
-        <v>4584.9000000000005</v>
+        <f t="shared" si="34"/>
+        <v>1109.2</v>
       </c>
       <c r="N70" s="6">
-        <f t="shared" ref="N70:Q70" si="43">+N69+N62</f>
-        <v>4769.3</v>
+        <f t="shared" ref="N70:T70" si="35">+SUM(N64:N69)</f>
+        <v>1079.0999999999999</v>
       </c>
       <c r="O70" s="6">
-        <f t="shared" si="43"/>
-        <v>5623.7000000000007</v>
+        <f t="shared" si="35"/>
+        <v>1663.9</v>
       </c>
       <c r="P70" s="6">
-        <f t="shared" si="43"/>
-        <v>5615.9</v>
+        <f t="shared" si="35"/>
+        <v>1465.9</v>
       </c>
       <c r="Q70" s="6">
-        <f t="shared" si="43"/>
-        <v>5780.5</v>
+        <f t="shared" si="35"/>
+        <v>1477.1999999999998</v>
       </c>
       <c r="R70" s="6">
-        <f>+R69+R62</f>
-        <v>6419.4</v>
+        <f t="shared" si="35"/>
+        <v>1550.6999999999998</v>
       </c>
       <c r="S70" s="6">
-        <f>+S69+S62</f>
-        <v>7887</v>
-      </c>
-      <c r="T70" s="6"/>
+        <f t="shared" si="35"/>
+        <v>2834.2000000000003</v>
+      </c>
+      <c r="T70" s="6">
+        <f t="shared" si="35"/>
+        <v>2733.7</v>
+      </c>
       <c r="U70" s="6"/>
       <c r="V70" s="6"/>
       <c r="W70" s="6"/>
@@ -7977,52 +8170,54 @@
       <c r="BL70" s="6"/>
     </row>
     <row r="71" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="7">
-        <f t="shared" ref="L71" si="44">+L70+L55</f>
-        <v>12990.400000000001</v>
-      </c>
-      <c r="M71" s="7">
-        <f t="shared" ref="M71" si="45">+M70+M55</f>
-        <v>13403.100000000002</v>
-      </c>
-      <c r="N71" s="7">
-        <f t="shared" ref="N71:Q71" si="46">+N70+N55</f>
-        <v>13872</v>
-      </c>
-      <c r="O71" s="7">
-        <f t="shared" si="46"/>
-        <v>13996</v>
-      </c>
-      <c r="P71" s="7">
-        <f t="shared" si="46"/>
-        <v>14583.699999999999</v>
-      </c>
-      <c r="Q71" s="7">
-        <f t="shared" si="46"/>
-        <v>15122.1</v>
-      </c>
-      <c r="R71" s="7">
-        <f>+R70+R55</f>
-        <v>15853.4</v>
-      </c>
-      <c r="S71" s="7">
-        <f>+S70+S55</f>
-        <v>17104</v>
-      </c>
-      <c r="T71" s="6"/>
+      <c r="B71" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6">
+        <f t="shared" ref="L71" si="36">+L70+L63</f>
+        <v>4542.2000000000007</v>
+      </c>
+      <c r="M71" s="6">
+        <f t="shared" ref="M71" si="37">+M70+M63</f>
+        <v>4584.9000000000005</v>
+      </c>
+      <c r="N71" s="6">
+        <f t="shared" ref="N71:Q71" si="38">+N70+N63</f>
+        <v>4769.3</v>
+      </c>
+      <c r="O71" s="6">
+        <f t="shared" si="38"/>
+        <v>5623.7000000000007</v>
+      </c>
+      <c r="P71" s="6">
+        <f t="shared" si="38"/>
+        <v>5615.9</v>
+      </c>
+      <c r="Q71" s="6">
+        <f t="shared" si="38"/>
+        <v>5780.5</v>
+      </c>
+      <c r="R71" s="6">
+        <f>+R70+R63</f>
+        <v>6419.4</v>
+      </c>
+      <c r="S71" s="6">
+        <f>+S70+S63</f>
+        <v>7887</v>
+      </c>
+      <c r="T71" s="6">
+        <f>+T70+T63</f>
+        <v>7730.9000000000005</v>
+      </c>
       <c r="U71" s="6"/>
       <c r="V71" s="6"/>
       <c r="W71" s="6"/>
@@ -8069,24 +8264,55 @@
       <c r="BL71" s="6"/>
     </row>
     <row r="72" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6"/>
-      <c r="N72" s="6"/>
-      <c r="O72" s="6"/>
-      <c r="P72" s="6"/>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
+      <c r="A72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7">
+        <f t="shared" ref="L72" si="39">+L71+L56</f>
+        <v>12990.400000000001</v>
+      </c>
+      <c r="M72" s="7">
+        <f t="shared" ref="M72" si="40">+M71+M56</f>
+        <v>13403.100000000002</v>
+      </c>
+      <c r="N72" s="7">
+        <f t="shared" ref="N72:Q72" si="41">+N71+N56</f>
+        <v>13872</v>
+      </c>
+      <c r="O72" s="7">
+        <f t="shared" si="41"/>
+        <v>13996</v>
+      </c>
+      <c r="P72" s="7">
+        <f t="shared" si="41"/>
+        <v>14583.699999999999</v>
+      </c>
+      <c r="Q72" s="7">
+        <f t="shared" si="41"/>
+        <v>15122.1</v>
+      </c>
+      <c r="R72" s="7">
+        <f>+R71+R56</f>
+        <v>15853.4</v>
+      </c>
+      <c r="S72" s="7">
+        <f>+S71+S56</f>
+        <v>17104</v>
+      </c>
+      <c r="T72" s="7">
+        <f>+T71+T56</f>
+        <v>16303.3</v>
+      </c>
       <c r="U72" s="6"/>
       <c r="V72" s="6"/>
       <c r="W72" s="6"/>
@@ -8133,9 +8359,6 @@
       <c r="BL72" s="6"/>
     </row>
     <row r="73" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="B73" t="s">
-        <v>32</v>
-      </c>
       <c r="C73" s="6"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -8145,30 +8368,14 @@
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
-      <c r="L73" s="6">
-        <v>711.6</v>
-      </c>
-      <c r="M73" s="6">
-        <v>665.5</v>
-      </c>
-      <c r="N73" s="6">
-        <v>747.7</v>
-      </c>
-      <c r="O73" s="6">
-        <v>677.9</v>
-      </c>
-      <c r="P73" s="6">
-        <v>1390.6</v>
-      </c>
-      <c r="Q73" s="6">
-        <v>1476.3</v>
-      </c>
-      <c r="R73" s="6">
-        <v>1182.4000000000001</v>
-      </c>
-      <c r="S73" s="6">
-        <v>939.7</v>
-      </c>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="6"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="6"/>
+      <c r="R73" s="6"/>
+      <c r="S73" s="6"/>
       <c r="T73" s="6"/>
       <c r="U73" s="6"/>
       <c r="V73" s="6"/>
@@ -8217,7 +8424,7 @@
     </row>
     <row r="74" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
@@ -8229,30 +8436,32 @@
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
       <c r="L74" s="6">
-        <v>318.7</v>
+        <v>711.6</v>
       </c>
       <c r="M74" s="6">
-        <v>351.2</v>
+        <v>665.5</v>
       </c>
       <c r="N74" s="6">
-        <v>503.1</v>
+        <v>747.7</v>
       </c>
       <c r="O74" s="6">
-        <v>460</v>
+        <v>677.9</v>
       </c>
       <c r="P74" s="6">
-        <v>361.5</v>
+        <v>1390.6</v>
       </c>
       <c r="Q74" s="6">
-        <v>352.3</v>
+        <v>1476.3</v>
       </c>
       <c r="R74" s="6">
-        <v>375</v>
+        <v>1182.4000000000001</v>
       </c>
       <c r="S74" s="6">
-        <v>419.8</v>
-      </c>
-      <c r="T74" s="6"/>
+        <v>939.7</v>
+      </c>
+      <c r="T74" s="6">
+        <v>669.4</v>
+      </c>
       <c r="U74" s="6"/>
       <c r="V74" s="6"/>
       <c r="W74" s="6"/>
@@ -8300,7 +8509,7 @@
     </row>
     <row r="75" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
@@ -8312,30 +8521,32 @@
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
       <c r="L75" s="6">
-        <v>180</v>
+        <v>318.7</v>
       </c>
       <c r="M75" s="6">
-        <v>206.7</v>
+        <v>351.2</v>
       </c>
       <c r="N75" s="6">
-        <v>291.2</v>
+        <v>503.1</v>
       </c>
       <c r="O75" s="6">
-        <v>774.1</v>
+        <v>460</v>
       </c>
       <c r="P75" s="6">
-        <v>498.2</v>
+        <v>361.5</v>
       </c>
       <c r="Q75" s="6">
-        <v>428.4</v>
+        <v>352.3</v>
       </c>
       <c r="R75" s="6">
-        <v>513</v>
+        <v>375</v>
       </c>
       <c r="S75" s="6">
-        <v>694.8</v>
-      </c>
-      <c r="T75" s="6"/>
+        <v>419.8</v>
+      </c>
+      <c r="T75" s="6">
+        <v>449.1</v>
+      </c>
       <c r="U75" s="6"/>
       <c r="V75" s="6"/>
       <c r="W75" s="6"/>
@@ -8383,7 +8594,7 @@
     </row>
     <row r="76" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="6"/>
@@ -8395,30 +8606,32 @@
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
       <c r="L76" s="6">
-        <v>168.1</v>
+        <v>180</v>
       </c>
       <c r="M76" s="6">
-        <v>-101.1</v>
+        <v>206.7</v>
       </c>
       <c r="N76" s="6">
-        <v>100.9</v>
+        <v>291.2</v>
       </c>
       <c r="O76" s="6">
-        <v>294.2</v>
+        <v>774.1</v>
       </c>
       <c r="P76" s="6">
-        <v>-6.2</v>
+        <v>498.2</v>
       </c>
       <c r="Q76" s="6">
-        <v>-363.9</v>
+        <v>428.4</v>
       </c>
       <c r="R76" s="6">
-        <v>-36.700000000000003</v>
+        <v>513</v>
       </c>
       <c r="S76" s="6">
-        <v>-138.4</v>
-      </c>
-      <c r="T76" s="6"/>
+        <v>694.8</v>
+      </c>
+      <c r="T76" s="6">
+        <v>687.6</v>
+      </c>
       <c r="U76" s="6"/>
       <c r="V76" s="6"/>
       <c r="W76" s="6"/>
@@ -8466,7 +8679,7 @@
     </row>
     <row r="77" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77" s="6"/>
       <c r="D77" s="6"/>
@@ -8478,30 +8691,32 @@
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
       <c r="L77" s="6">
-        <v>-122.3</v>
+        <v>168.1</v>
       </c>
       <c r="M77" s="6">
-        <v>-103.1</v>
+        <v>-101.1</v>
       </c>
       <c r="N77" s="6">
-        <v>-174.3</v>
+        <v>100.9</v>
       </c>
       <c r="O77" s="6">
-        <v>-196.4</v>
+        <v>294.2</v>
       </c>
       <c r="P77" s="6">
-        <v>-219.1</v>
+        <v>-6.2</v>
       </c>
       <c r="Q77" s="6">
-        <v>-140.80000000000001</v>
+        <v>-363.9</v>
       </c>
       <c r="R77" s="6">
-        <v>-98.3</v>
+        <v>-36.700000000000003</v>
       </c>
       <c r="S77" s="6">
-        <v>-211</v>
-      </c>
-      <c r="T77" s="6"/>
+        <v>-138.4</v>
+      </c>
+      <c r="T77" s="6">
+        <v>-213.9</v>
+      </c>
       <c r="U77" s="6"/>
       <c r="V77" s="6"/>
       <c r="W77" s="6"/>
@@ -8549,7 +8764,7 @@
     </row>
     <row r="78" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="6"/>
@@ -8561,30 +8776,32 @@
       <c r="J78" s="6"/>
       <c r="K78" s="6"/>
       <c r="L78" s="6">
-        <v>8.3000000000000007</v>
+        <v>-122.3</v>
       </c>
       <c r="M78" s="6">
-        <v>96.5</v>
+        <v>-103.1</v>
       </c>
       <c r="N78" s="6">
-        <v>124.8</v>
+        <v>-174.3</v>
       </c>
       <c r="O78" s="6">
-        <v>115.8</v>
+        <v>-196.4</v>
       </c>
       <c r="P78" s="6">
-        <v>33.9</v>
+        <v>-219.1</v>
       </c>
       <c r="Q78" s="6">
-        <v>93</v>
+        <v>-140.80000000000001</v>
       </c>
       <c r="R78" s="6">
-        <v>49.9</v>
+        <v>-98.3</v>
       </c>
       <c r="S78" s="6">
-        <v>51.4</v>
-      </c>
-      <c r="T78" s="6"/>
+        <v>-211</v>
+      </c>
+      <c r="T78" s="6">
+        <v>-242.2</v>
+      </c>
       <c r="U78" s="6"/>
       <c r="V78" s="6"/>
       <c r="W78" s="6"/>
@@ -8632,7 +8849,7 @@
     </row>
     <row r="79" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
@@ -8644,30 +8861,32 @@
       <c r="J79" s="6"/>
       <c r="K79" s="6"/>
       <c r="L79" s="6">
-        <v>-148.9</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="M79" s="6">
-        <v>-111.4</v>
+        <v>96.5</v>
       </c>
       <c r="N79" s="6">
-        <v>-127</v>
+        <v>124.8</v>
       </c>
       <c r="O79" s="6">
-        <v>-312.2</v>
+        <v>115.8</v>
       </c>
       <c r="P79" s="6">
-        <v>-118</v>
+        <v>33.9</v>
       </c>
       <c r="Q79" s="6">
-        <v>-199.2</v>
+        <v>93</v>
       </c>
       <c r="R79" s="6">
-        <v>-248.7</v>
+        <v>49.9</v>
       </c>
       <c r="S79" s="6">
-        <v>-226.1</v>
-      </c>
-      <c r="T79" s="6"/>
+        <v>51.4</v>
+      </c>
+      <c r="T79" s="6">
+        <v>42.4</v>
+      </c>
       <c r="U79" s="6"/>
       <c r="V79" s="6"/>
       <c r="W79" s="6"/>
@@ -8715,7 +8934,7 @@
     </row>
     <row r="80" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="6"/>
@@ -8727,30 +8946,32 @@
       <c r="J80" s="6"/>
       <c r="K80" s="6"/>
       <c r="L80" s="6">
-        <v>-67</v>
+        <v>-148.9</v>
       </c>
       <c r="M80" s="6">
-        <v>-219.8</v>
+        <v>-111.4</v>
       </c>
       <c r="N80" s="6">
-        <v>-166.8</v>
+        <v>-127</v>
       </c>
       <c r="O80" s="6">
-        <v>-228</v>
+        <v>-312.2</v>
       </c>
       <c r="P80" s="6">
-        <v>-374.2</v>
+        <v>-118</v>
       </c>
       <c r="Q80" s="6">
-        <v>-253.6</v>
+        <v>-199.2</v>
       </c>
       <c r="R80" s="6">
-        <v>-389.6</v>
+        <v>-248.7</v>
       </c>
       <c r="S80" s="6">
-        <v>-351.1</v>
-      </c>
-      <c r="T80" s="6"/>
+        <v>-226.1</v>
+      </c>
+      <c r="T80" s="6">
+        <v>-315.3</v>
+      </c>
       <c r="U80" s="6"/>
       <c r="V80" s="6"/>
       <c r="W80" s="6"/>
@@ -8797,8 +9018,8 @@
       <c r="BL80" s="6"/>
     </row>
     <row r="81" spans="2:64" x14ac:dyDescent="0.2">
-      <c r="B81" s="2" t="s">
-        <v>79</v>
+      <c r="B81" t="s">
+        <v>85</v>
       </c>
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
@@ -8809,39 +9030,33 @@
       <c r="I81" s="6"/>
       <c r="J81" s="6"/>
       <c r="K81" s="6"/>
-      <c r="L81" s="7">
-        <f t="shared" ref="L81:O81" si="47">+SUM(L73:L80)</f>
-        <v>1048.4999999999998</v>
-      </c>
-      <c r="M81" s="7">
-        <f t="shared" si="47"/>
-        <v>784.50000000000023</v>
-      </c>
-      <c r="N81" s="7">
-        <f t="shared" si="47"/>
-        <v>1299.6000000000004</v>
-      </c>
-      <c r="O81" s="7">
-        <f t="shared" si="47"/>
-        <v>1585.3999999999999</v>
-      </c>
-      <c r="P81" s="7">
-        <f t="shared" ref="P81:R81" si="48">+SUM(P73:P80)</f>
-        <v>1566.7</v>
-      </c>
-      <c r="Q81" s="7">
-        <f t="shared" si="48"/>
-        <v>1392.5</v>
-      </c>
-      <c r="R81" s="7">
-        <f t="shared" si="48"/>
-        <v>1347</v>
-      </c>
-      <c r="S81" s="7">
-        <f>+SUM(S73:S80)</f>
-        <v>1179.1000000000004</v>
-      </c>
-      <c r="T81" s="6"/>
+      <c r="L81" s="6">
+        <v>-67</v>
+      </c>
+      <c r="M81" s="6">
+        <v>-219.8</v>
+      </c>
+      <c r="N81" s="6">
+        <v>-166.8</v>
+      </c>
+      <c r="O81" s="6">
+        <v>-228</v>
+      </c>
+      <c r="P81" s="6">
+        <v>-374.2</v>
+      </c>
+      <c r="Q81" s="6">
+        <v>-253.6</v>
+      </c>
+      <c r="R81" s="6">
+        <v>-389.6</v>
+      </c>
+      <c r="S81" s="6">
+        <v>-351.1</v>
+      </c>
+      <c r="T81" s="6">
+        <v>-322.60000000000002</v>
+      </c>
       <c r="U81" s="6"/>
       <c r="V81" s="6"/>
       <c r="W81" s="6"/>
@@ -8888,8 +9103,8 @@
       <c r="BL81" s="6"/>
     </row>
     <row r="82" spans="2:64" x14ac:dyDescent="0.2">
-      <c r="B82" t="s">
-        <v>86</v>
+      <c r="B82" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="6"/>
@@ -8900,31 +9115,42 @@
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
       <c r="K82" s="6"/>
-      <c r="L82" s="6">
-        <v>-7.9</v>
-      </c>
-      <c r="M82" s="6">
-        <v>-394.1</v>
-      </c>
-      <c r="N82" s="6">
-        <v>-5.9</v>
-      </c>
-      <c r="O82" s="6">
-        <v>-1560.1</v>
-      </c>
-      <c r="P82" s="6">
-        <v>-3.9</v>
-      </c>
-      <c r="Q82" s="6">
-        <v>-3.7</v>
-      </c>
-      <c r="R82" s="6">
-        <v>-581.70000000000005</v>
-      </c>
-      <c r="S82" s="6">
-        <v>-575.6</v>
-      </c>
-      <c r="T82" s="6"/>
+      <c r="L82" s="7">
+        <f t="shared" ref="L82:O82" si="42">+SUM(L74:L81)</f>
+        <v>1048.4999999999998</v>
+      </c>
+      <c r="M82" s="7">
+        <f t="shared" si="42"/>
+        <v>784.50000000000023</v>
+      </c>
+      <c r="N82" s="7">
+        <f t="shared" si="42"/>
+        <v>1299.6000000000004</v>
+      </c>
+      <c r="O82" s="7">
+        <f t="shared" si="42"/>
+        <v>1585.3999999999999</v>
+      </c>
+      <c r="P82" s="7">
+        <f t="shared" ref="P82:R82" si="43">+SUM(P74:P81)</f>
+        <v>1566.7</v>
+      </c>
+      <c r="Q82" s="7">
+        <f t="shared" si="43"/>
+        <v>1392.5</v>
+      </c>
+      <c r="R82" s="7">
+        <f t="shared" si="43"/>
+        <v>1347</v>
+      </c>
+      <c r="S82" s="7">
+        <f>+SUM(S74:S81)</f>
+        <v>1179.1000000000004</v>
+      </c>
+      <c r="T82" s="7">
+        <f>+SUM(T74:T81)</f>
+        <v>754.49999999999989</v>
+      </c>
       <c r="U82" s="6"/>
       <c r="V82" s="6"/>
       <c r="W82" s="6"/>
@@ -8972,7 +9198,7 @@
     </row>
     <row r="83" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
@@ -8984,30 +9210,32 @@
       <c r="J83" s="6"/>
       <c r="K83" s="6"/>
       <c r="L83" s="6">
-        <v>-54.4</v>
+        <v>-7.9</v>
       </c>
       <c r="M83" s="6">
-        <v>-15.3</v>
+        <v>-394.1</v>
       </c>
       <c r="N83" s="6">
-        <v>-28.2</v>
+        <v>-5.9</v>
       </c>
       <c r="O83" s="6">
-        <v>-44.2</v>
+        <v>-1560.1</v>
       </c>
       <c r="P83" s="6">
-        <v>-28.8</v>
+        <v>-3.9</v>
       </c>
       <c r="Q83" s="6">
-        <v>-125.4</v>
+        <v>-3.7</v>
       </c>
       <c r="R83" s="6">
-        <v>-109.4</v>
+        <v>-581.70000000000005</v>
       </c>
       <c r="S83" s="6">
-        <v>-48.3</v>
-      </c>
-      <c r="T83" s="6"/>
+        <v>-575.6</v>
+      </c>
+      <c r="T83" s="6">
+        <v>-4.3</v>
+      </c>
       <c r="U83" s="6"/>
       <c r="V83" s="6"/>
       <c r="W83" s="6"/>
@@ -9055,7 +9283,7 @@
     </row>
     <row r="84" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="6"/>
@@ -9067,30 +9295,32 @@
       <c r="J84" s="6"/>
       <c r="K84" s="6"/>
       <c r="L84" s="6">
-        <v>-54.1</v>
+        <v>-54.4</v>
       </c>
       <c r="M84" s="6">
-        <v>-109.7</v>
+        <v>-15.3</v>
       </c>
       <c r="N84" s="6">
-        <v>-93.5</v>
+        <v>-28.2</v>
       </c>
       <c r="O84" s="6">
-        <v>-156.5</v>
+        <v>-44.2</v>
       </c>
       <c r="P84" s="6">
-        <v>-211.6</v>
+        <v>-28.8</v>
       </c>
       <c r="Q84" s="6">
-        <v>-264.10000000000002</v>
+        <v>-125.4</v>
       </c>
       <c r="R84" s="6">
-        <v>-199</v>
+        <v>-109.4</v>
       </c>
       <c r="S84" s="6">
-        <v>-216</v>
-      </c>
-      <c r="T84" s="6"/>
+        <v>-48.3</v>
+      </c>
+      <c r="T84" s="6">
+        <v>-23.7</v>
+      </c>
       <c r="U84" s="6"/>
       <c r="V84" s="6"/>
       <c r="W84" s="6"/>
@@ -9138,7 +9368,7 @@
     </row>
     <row r="85" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
@@ -9150,31 +9380,32 @@
       <c r="J85" s="6"/>
       <c r="K85" s="6"/>
       <c r="L85" s="6">
-        <v>15.9</v>
+        <v>-54.1</v>
       </c>
       <c r="M85" s="6">
-        <v>1.1000000000000001</v>
+        <v>-109.7</v>
       </c>
       <c r="N85" s="6">
-        <f>1.2+68.5</f>
-        <v>69.7</v>
+        <v>-93.5</v>
       </c>
       <c r="O85" s="6">
-        <v>1.6</v>
+        <v>-156.5</v>
       </c>
       <c r="P85" s="6">
-        <v>57.2</v>
+        <v>-211.6</v>
       </c>
       <c r="Q85" s="6">
-        <v>245.8</v>
+        <v>-264.10000000000002</v>
       </c>
       <c r="R85" s="6">
-        <v>2.4</v>
+        <v>-199</v>
       </c>
       <c r="S85" s="6">
-        <v>2.9</v>
-      </c>
-      <c r="T85" s="6"/>
+        <v>-216</v>
+      </c>
+      <c r="T85" s="6">
+        <v>-158.1</v>
+      </c>
       <c r="U85" s="6"/>
       <c r="V85" s="6"/>
       <c r="W85" s="6"/>
@@ -9222,7 +9453,7 @@
     </row>
     <row r="86" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
@@ -9234,30 +9465,33 @@
       <c r="J86" s="6"/>
       <c r="K86" s="6"/>
       <c r="L86" s="6">
-        <v>6.8</v>
+        <v>15.9</v>
       </c>
       <c r="M86" s="6">
-        <v>7.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N86" s="6">
-        <v>8</v>
+        <f>1.2+68.5</f>
+        <v>69.7</v>
       </c>
       <c r="O86" s="6">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="P86" s="6">
-        <v>9.6</v>
+        <v>57.2</v>
       </c>
       <c r="Q86" s="6">
-        <v>15.6</v>
+        <v>245.8</v>
       </c>
       <c r="R86" s="6">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="S86" s="6">
-        <v>12.9</v>
-      </c>
-      <c r="T86" s="6"/>
+        <v>2.9</v>
+      </c>
+      <c r="T86" s="6">
+        <v>10.1</v>
+      </c>
       <c r="U86" s="6"/>
       <c r="V86" s="6"/>
       <c r="W86" s="6"/>
@@ -9304,8 +9538,8 @@
       <c r="BL86" s="6"/>
     </row>
     <row r="87" spans="2:64" x14ac:dyDescent="0.2">
-      <c r="B87" s="2" t="s">
-        <v>91</v>
+      <c r="B87" t="s">
+        <v>90</v>
       </c>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
@@ -9316,39 +9550,33 @@
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
       <c r="K87" s="6"/>
-      <c r="L87" s="7">
-        <f t="shared" ref="L87:P87" si="49">+SUM(L82:L86)</f>
-        <v>-93.7</v>
-      </c>
-      <c r="M87" s="7">
-        <f t="shared" si="49"/>
-        <v>-510.6</v>
-      </c>
-      <c r="N87" s="7">
-        <f t="shared" si="49"/>
-        <v>-49.899999999999991</v>
-      </c>
-      <c r="O87" s="7">
-        <f t="shared" si="49"/>
-        <v>-1751.7</v>
-      </c>
-      <c r="P87" s="7">
-        <f t="shared" si="49"/>
-        <v>-177.50000000000003</v>
-      </c>
-      <c r="Q87" s="7">
-        <f t="shared" ref="Q87:R87" si="50">+SUM(Q82:Q86)</f>
-        <v>-131.80000000000004</v>
-      </c>
-      <c r="R87" s="7">
-        <f t="shared" si="50"/>
-        <v>-875.30000000000007</v>
-      </c>
-      <c r="S87" s="7">
-        <f>+SUM(S82:S86)</f>
-        <v>-824.1</v>
-      </c>
-      <c r="T87" s="6"/>
+      <c r="L87" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="M87" s="6">
+        <v>7.4</v>
+      </c>
+      <c r="N87" s="6">
+        <v>8</v>
+      </c>
+      <c r="O87" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="P87" s="6">
+        <v>9.6</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>15.6</v>
+      </c>
+      <c r="R87" s="6">
+        <v>12.4</v>
+      </c>
+      <c r="S87" s="6">
+        <v>12.9</v>
+      </c>
+      <c r="T87" s="6">
+        <v>12.6</v>
+      </c>
       <c r="U87" s="6"/>
       <c r="V87" s="6"/>
       <c r="W87" s="6"/>
@@ -9395,8 +9623,8 @@
       <c r="BL87" s="6"/>
     </row>
     <row r="88" spans="2:64" x14ac:dyDescent="0.2">
-      <c r="B88" t="s">
-        <v>92</v>
+      <c r="B88" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
@@ -9407,31 +9635,42 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
       <c r="K88" s="6"/>
-      <c r="L88" s="6">
-        <v>0</v>
-      </c>
-      <c r="M88" s="6">
-        <v>0</v>
-      </c>
-      <c r="N88" s="6">
-        <v>-81.3</v>
-      </c>
-      <c r="O88" s="6">
-        <v>-70.3</v>
-      </c>
-      <c r="P88" s="6">
-        <v>-58.8</v>
-      </c>
-      <c r="Q88" s="6">
-        <v>-67.400000000000006</v>
-      </c>
-      <c r="R88" s="6">
-        <v>-67.8</v>
-      </c>
-      <c r="S88" s="6">
-        <v>-94.3</v>
-      </c>
-      <c r="T88" s="6"/>
+      <c r="L88" s="7">
+        <f t="shared" ref="L88:P88" si="44">+SUM(L83:L87)</f>
+        <v>-93.7</v>
+      </c>
+      <c r="M88" s="7">
+        <f t="shared" si="44"/>
+        <v>-510.6</v>
+      </c>
+      <c r="N88" s="7">
+        <f t="shared" si="44"/>
+        <v>-49.899999999999991</v>
+      </c>
+      <c r="O88" s="7">
+        <f t="shared" si="44"/>
+        <v>-1751.7</v>
+      </c>
+      <c r="P88" s="7">
+        <f t="shared" si="44"/>
+        <v>-177.50000000000003</v>
+      </c>
+      <c r="Q88" s="7">
+        <f t="shared" ref="Q88:R88" si="45">+SUM(Q83:Q87)</f>
+        <v>-131.80000000000004</v>
+      </c>
+      <c r="R88" s="7">
+        <f t="shared" si="45"/>
+        <v>-875.30000000000007</v>
+      </c>
+      <c r="S88" s="7">
+        <f>+SUM(S83:S87)</f>
+        <v>-824.1</v>
+      </c>
+      <c r="T88" s="7">
+        <f>+SUM(T83:T87)</f>
+        <v>-163.4</v>
+      </c>
       <c r="U88" s="6"/>
       <c r="V88" s="6"/>
       <c r="W88" s="6"/>
@@ -9479,7 +9718,7 @@
     </row>
     <row r="89" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
@@ -9497,25 +9736,26 @@
         <v>0</v>
       </c>
       <c r="N89" s="6">
-        <v>6.8</v>
+        <v>-81.3</v>
       </c>
       <c r="O89" s="6">
-        <f>14.7+7549.5</f>
-        <v>7564.2</v>
+        <v>-70.3</v>
       </c>
       <c r="P89" s="6">
-        <v>-45.2</v>
+        <v>-58.8</v>
       </c>
       <c r="Q89" s="6">
-        <v>138.30000000000001</v>
+        <v>-67.400000000000006</v>
       </c>
       <c r="R89" s="6">
-        <v>581</v>
+        <v>-67.8</v>
       </c>
       <c r="S89" s="6">
-        <v>405</v>
-      </c>
-      <c r="T89" s="6"/>
+        <v>-94.3</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-80.3</v>
+      </c>
       <c r="U89" s="6"/>
       <c r="V89" s="6"/>
       <c r="W89" s="6"/>
@@ -9563,7 +9803,7 @@
     </row>
     <row r="90" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
@@ -9581,24 +9821,27 @@
         <v>0</v>
       </c>
       <c r="N90" s="6">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O90" s="6">
-        <v>0</v>
+        <f>14.7+7549.5</f>
+        <v>7564.2</v>
       </c>
       <c r="P90" s="6">
-        <v>0</v>
+        <v>-45.2</v>
       </c>
       <c r="Q90" s="6">
-        <v>0</v>
+        <v>138.30000000000001</v>
       </c>
       <c r="R90" s="6">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="S90" s="6">
-        <v>2233</v>
-      </c>
-      <c r="T90" s="6"/>
+        <v>405</v>
+      </c>
+      <c r="T90" s="6">
+        <v>860.4</v>
+      </c>
       <c r="U90" s="6"/>
       <c r="V90" s="6"/>
       <c r="W90" s="6"/>
@@ -9646,7 +9889,7 @@
     </row>
     <row r="91" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
@@ -9679,9 +9922,11 @@
         <v>0</v>
       </c>
       <c r="S91" s="6">
-        <v>-1355</v>
-      </c>
-      <c r="T91" s="6"/>
+        <v>2233</v>
+      </c>
+      <c r="T91" s="6">
+        <v>0</v>
+      </c>
       <c r="U91" s="6"/>
       <c r="V91" s="6"/>
       <c r="W91" s="6"/>
@@ -9729,7 +9974,7 @@
     </row>
     <row r="92" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="6"/>
@@ -9750,21 +9995,23 @@
         <v>0</v>
       </c>
       <c r="O92" s="6">
-        <v>-7299</v>
+        <v>0</v>
       </c>
       <c r="P92" s="6">
         <v>0</v>
       </c>
       <c r="Q92" s="6">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="R92" s="6">
-        <v>-4.2</v>
+        <v>0</v>
       </c>
       <c r="S92" s="6">
-        <v>-4.0999999999999996</v>
-      </c>
-      <c r="T92" s="6"/>
+        <v>-1355</v>
+      </c>
+      <c r="T92" s="6">
+        <v>-846.9</v>
+      </c>
       <c r="U92" s="6"/>
       <c r="V92" s="6"/>
       <c r="W92" s="6"/>
@@ -9812,7 +10059,7 @@
     </row>
     <row r="93" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
@@ -9824,30 +10071,32 @@
       <c r="J93" s="6"/>
       <c r="K93" s="6"/>
       <c r="L93" s="6">
-        <v>-896.7</v>
+        <v>0</v>
       </c>
       <c r="M93" s="6">
-        <v>-572.9</v>
+        <v>0</v>
       </c>
       <c r="N93" s="6">
-        <v>-598</v>
+        <v>0</v>
       </c>
       <c r="O93" s="6">
-        <v>-608.29999999999995</v>
+        <v>-7299</v>
       </c>
       <c r="P93" s="6">
-        <v>-626.70000000000005</v>
+        <v>0</v>
       </c>
       <c r="Q93" s="6">
-        <v>-692</v>
+        <v>-4</v>
       </c>
       <c r="R93" s="6">
-        <v>-714.6</v>
+        <v>-4.2</v>
       </c>
       <c r="S93" s="6">
-        <v>-709.8</v>
-      </c>
-      <c r="T93" s="6"/>
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="T93" s="6">
+        <v>-10.5</v>
+      </c>
       <c r="U93" s="6"/>
       <c r="V93" s="6"/>
       <c r="W93" s="6"/>
@@ -9895,7 +10144,7 @@
     </row>
     <row r="94" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
@@ -9907,30 +10156,32 @@
       <c r="J94" s="6"/>
       <c r="K94" s="6"/>
       <c r="L94" s="6">
-        <v>0</v>
+        <v>-896.7</v>
       </c>
       <c r="M94" s="6">
-        <v>0</v>
+        <v>-572.9</v>
       </c>
       <c r="N94" s="6">
-        <v>0</v>
+        <v>-598</v>
       </c>
       <c r="O94" s="6">
-        <v>-188.5</v>
+        <v>-608.29999999999995</v>
       </c>
       <c r="P94" s="6">
-        <v>-607.1</v>
+        <v>-626.70000000000005</v>
       </c>
       <c r="Q94" s="6">
-        <v>-776.4</v>
+        <v>-692</v>
       </c>
       <c r="R94" s="6">
-        <v>-180.6</v>
+        <v>-714.6</v>
       </c>
       <c r="S94" s="6">
-        <v>-773.6</v>
-      </c>
-      <c r="T94" s="6"/>
+        <v>-709.8</v>
+      </c>
+      <c r="T94" s="6">
+        <v>-669.3</v>
+      </c>
       <c r="U94" s="6"/>
       <c r="V94" s="6"/>
       <c r="W94" s="6"/>
@@ -9977,8 +10228,8 @@
       <c r="BL94" s="6"/>
     </row>
     <row r="95" spans="2:64" x14ac:dyDescent="0.2">
-      <c r="B95" s="2" t="s">
-        <v>99</v>
+      <c r="B95" t="s">
+        <v>98</v>
       </c>
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
@@ -9989,39 +10240,33 @@
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
       <c r="K95" s="6"/>
-      <c r="L95" s="7">
-        <f t="shared" ref="L95:P95" si="51">+SUM(L88:L94)</f>
-        <v>-896.7</v>
-      </c>
-      <c r="M95" s="7">
-        <f t="shared" si="51"/>
-        <v>-572.9</v>
-      </c>
-      <c r="N95" s="7">
-        <f t="shared" si="51"/>
-        <v>-672.5</v>
-      </c>
-      <c r="O95" s="7">
-        <f t="shared" si="51"/>
-        <v>-601.90000000000032</v>
-      </c>
-      <c r="P95" s="7">
-        <f t="shared" si="51"/>
-        <v>-1337.8000000000002</v>
-      </c>
-      <c r="Q95" s="7">
-        <f t="shared" ref="Q95:R95" si="52">+SUM(Q88:Q94)</f>
-        <v>-1401.5</v>
-      </c>
-      <c r="R95" s="7">
-        <f t="shared" si="52"/>
-        <v>-386.19999999999993</v>
-      </c>
-      <c r="S95" s="7">
-        <f>+SUM(S88:S94)</f>
-        <v>-298.80000000000007</v>
-      </c>
-      <c r="T95" s="6"/>
+      <c r="L95" s="6">
+        <v>0</v>
+      </c>
+      <c r="M95" s="6">
+        <v>0</v>
+      </c>
+      <c r="N95" s="6">
+        <v>0</v>
+      </c>
+      <c r="O95" s="6">
+        <v>-188.5</v>
+      </c>
+      <c r="P95" s="6">
+        <v>-607.1</v>
+      </c>
+      <c r="Q95" s="6">
+        <v>-776.4</v>
+      </c>
+      <c r="R95" s="6">
+        <v>-180.6</v>
+      </c>
+      <c r="S95" s="6">
+        <v>-773.6</v>
+      </c>
+      <c r="T95" s="6">
+        <v>0</v>
+      </c>
       <c r="U95" s="6"/>
       <c r="V95" s="6"/>
       <c r="W95" s="6"/>
@@ -10068,6 +10313,9 @@
       <c r="BL95" s="6"/>
     </row>
     <row r="96" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="B96" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
@@ -10077,15 +10325,42 @@
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
       <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
-      <c r="M96" s="6"/>
-      <c r="N96" s="6"/>
-      <c r="O96" s="6"/>
-      <c r="P96" s="6"/>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
-      <c r="S96" s="6"/>
-      <c r="T96" s="6"/>
+      <c r="L96" s="7">
+        <f t="shared" ref="L96:P96" si="46">+SUM(L89:L95)</f>
+        <v>-896.7</v>
+      </c>
+      <c r="M96" s="7">
+        <f t="shared" si="46"/>
+        <v>-572.9</v>
+      </c>
+      <c r="N96" s="7">
+        <f t="shared" si="46"/>
+        <v>-672.5</v>
+      </c>
+      <c r="O96" s="7">
+        <f t="shared" si="46"/>
+        <v>-601.90000000000032</v>
+      </c>
+      <c r="P96" s="7">
+        <f t="shared" si="46"/>
+        <v>-1337.8000000000002</v>
+      </c>
+      <c r="Q96" s="7">
+        <f t="shared" ref="Q96:R96" si="47">+SUM(Q89:Q95)</f>
+        <v>-1401.5</v>
+      </c>
+      <c r="R96" s="7">
+        <f t="shared" si="47"/>
+        <v>-386.19999999999993</v>
+      </c>
+      <c r="S96" s="7">
+        <f>+SUM(S89:S95)</f>
+        <v>-298.80000000000007</v>
+      </c>
+      <c r="T96" s="7">
+        <f>+SUM(T89:T95)</f>
+        <v>-746.59999999999991</v>
+      </c>
       <c r="U96" s="6"/>
       <c r="V96" s="6"/>
       <c r="W96" s="6"/>
@@ -10132,9 +10407,6 @@
       <c r="BL96" s="6"/>
     </row>
     <row r="97" spans="2:64" x14ac:dyDescent="0.2">
-      <c r="B97" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
@@ -10144,38 +10416,14 @@
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
       <c r="K97" s="6"/>
-      <c r="L97" s="7">
-        <f t="shared" ref="L97:O97" si="53">+SUM(L96,L95,L87,L81)</f>
-        <v>58.099999999999682</v>
-      </c>
-      <c r="M97" s="7">
-        <f t="shared" si="53"/>
-        <v>-298.99999999999977</v>
-      </c>
-      <c r="N97" s="7">
-        <f t="shared" si="53"/>
-        <v>577.20000000000039</v>
-      </c>
-      <c r="O97" s="7">
-        <f t="shared" si="53"/>
-        <v>-768.2000000000005</v>
-      </c>
-      <c r="P97" s="7">
-        <f t="shared" ref="P97:R97" si="54">+SUM(P96,P95,P87,P81)</f>
-        <v>51.399999999999864</v>
-      </c>
-      <c r="Q97" s="7">
-        <f t="shared" si="54"/>
-        <v>-140.79999999999995</v>
-      </c>
-      <c r="R97" s="7">
-        <f t="shared" si="54"/>
-        <v>85.5</v>
-      </c>
-      <c r="S97" s="7">
-        <f>+SUM(S96,S95,S87,S81)</f>
-        <v>56.200000000000273</v>
-      </c>
+      <c r="L97" s="6"/>
+      <c r="M97" s="6"/>
+      <c r="N97" s="6"/>
+      <c r="O97" s="6"/>
+      <c r="P97" s="6"/>
+      <c r="Q97" s="6"/>
+      <c r="R97" s="6"/>
+      <c r="S97" s="6"/>
       <c r="T97" s="6"/>
       <c r="U97" s="6"/>
       <c r="V97" s="6"/>
@@ -10223,8 +10471,8 @@
       <c r="BL97" s="6"/>
     </row>
     <row r="98" spans="2:64" x14ac:dyDescent="0.2">
-      <c r="B98" t="s">
-        <v>100</v>
+      <c r="B98" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
@@ -10235,31 +10483,42 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
       <c r="K98" s="6"/>
-      <c r="L98" s="6">
-        <v>570.29999999999995</v>
-      </c>
-      <c r="M98" s="6">
-        <v>605.20000000000005</v>
-      </c>
-      <c r="N98" s="6">
-        <v>310.8</v>
-      </c>
-      <c r="O98" s="6">
-        <v>897.5</v>
-      </c>
-      <c r="P98" s="6">
-        <v>117</v>
-      </c>
-      <c r="Q98" s="6">
-        <v>-10.6</v>
-      </c>
-      <c r="R98" s="6">
-        <v>-8.1</v>
-      </c>
-      <c r="S98" s="6">
-        <v>4.3</v>
-      </c>
-      <c r="T98" s="6"/>
+      <c r="L98" s="7">
+        <f t="shared" ref="L98:O98" si="48">+SUM(L97,L96,L88,L82)</f>
+        <v>58.099999999999682</v>
+      </c>
+      <c r="M98" s="7">
+        <f t="shared" si="48"/>
+        <v>-298.99999999999977</v>
+      </c>
+      <c r="N98" s="7">
+        <f t="shared" si="48"/>
+        <v>577.20000000000039</v>
+      </c>
+      <c r="O98" s="7">
+        <f t="shared" si="48"/>
+        <v>-768.2000000000005</v>
+      </c>
+      <c r="P98" s="7">
+        <f t="shared" ref="P98:R98" si="49">+SUM(P97,P96,P88,P82)</f>
+        <v>51.399999999999864</v>
+      </c>
+      <c r="Q98" s="7">
+        <f t="shared" si="49"/>
+        <v>-140.79999999999995</v>
+      </c>
+      <c r="R98" s="7">
+        <f t="shared" si="49"/>
+        <v>85.5</v>
+      </c>
+      <c r="S98" s="7">
+        <f>+SUM(S97,S96,S88,S82)</f>
+        <v>56.200000000000273</v>
+      </c>
+      <c r="T98" s="7">
+        <f>+SUM(T97,T96,T88,T82)</f>
+        <v>-155.5</v>
+      </c>
       <c r="U98" s="6"/>
       <c r="V98" s="6"/>
       <c r="W98" s="6"/>
@@ -10307,7 +10566,7 @@
     </row>
     <row r="99" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B99" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
@@ -10319,30 +10578,32 @@
       <c r="J99" s="6"/>
       <c r="K99" s="6"/>
       <c r="L99" s="6">
-        <v>-23.2</v>
+        <v>570.29999999999995</v>
       </c>
       <c r="M99" s="6">
-        <v>4.5999999999999996</v>
+        <v>605.20000000000005</v>
       </c>
       <c r="N99" s="6">
-        <v>9.5</v>
+        <v>310.8</v>
       </c>
       <c r="O99" s="6">
-        <v>-12.3</v>
+        <v>897.5</v>
       </c>
       <c r="P99" s="6">
-        <v>5.2</v>
+        <v>117</v>
       </c>
       <c r="Q99" s="6">
-        <v>173.6</v>
+        <v>-10.6</v>
       </c>
       <c r="R99" s="6">
-        <v>22.2</v>
+        <v>-8.1</v>
       </c>
       <c r="S99" s="6">
-        <v>99.6</v>
-      </c>
-      <c r="T99" s="6"/>
+        <v>4.3</v>
+      </c>
+      <c r="T99" s="6">
+        <v>-10.9</v>
+      </c>
       <c r="U99" s="6"/>
       <c r="V99" s="6"/>
       <c r="W99" s="6"/>
@@ -10390,7 +10651,7 @@
     </row>
     <row r="100" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
@@ -10402,38 +10663,33 @@
       <c r="J100" s="6"/>
       <c r="K100" s="6"/>
       <c r="L100" s="6">
-        <f t="shared" ref="L100:O100" si="55">+L99+L97+L98</f>
-        <v>605.19999999999959</v>
+        <v>-23.2</v>
       </c>
       <c r="M100" s="6">
-        <f t="shared" si="55"/>
-        <v>310.8000000000003</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="N100" s="6">
-        <f t="shared" si="55"/>
-        <v>897.50000000000045</v>
+        <v>9.5</v>
       </c>
       <c r="O100" s="6">
-        <f t="shared" si="55"/>
-        <v>116.99999999999955</v>
+        <v>-12.3</v>
       </c>
       <c r="P100" s="6">
-        <f>+P99+P97+P98</f>
-        <v>173.59999999999985</v>
+        <v>5.2</v>
       </c>
       <c r="Q100" s="6">
-        <f>+Q99+Q97+Q98</f>
-        <v>22.200000000000038</v>
+        <v>173.6</v>
       </c>
       <c r="R100" s="6">
-        <f>+R99+R97+R98</f>
-        <v>99.600000000000009</v>
+        <v>22.2</v>
       </c>
       <c r="S100" s="6">
-        <f>+S99+S97+S98</f>
+        <v>99.6</v>
+      </c>
+      <c r="T100" s="6">
+        <f>+S101</f>
         <v>160.10000000000028</v>
       </c>
-      <c r="T100" s="6"/>
       <c r="U100" s="6"/>
       <c r="V100" s="6"/>
       <c r="W100" s="6"/>
@@ -10480,6 +10736,9 @@
       <c r="BL100" s="6"/>
     </row>
     <row r="101" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="B101" t="s">
+        <v>103</v>
+      </c>
       <c r="C101" s="6"/>
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
@@ -10489,15 +10748,42 @@
       <c r="I101" s="6"/>
       <c r="J101" s="6"/>
       <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="6"/>
-      <c r="N101" s="6"/>
-      <c r="O101" s="6"/>
-      <c r="P101" s="6"/>
-      <c r="Q101" s="6"/>
-      <c r="R101" s="6"/>
-      <c r="S101" s="6"/>
-      <c r="T101" s="6"/>
+      <c r="L101" s="6">
+        <f t="shared" ref="L101:O101" si="50">+L100+L98+L99</f>
+        <v>605.19999999999959</v>
+      </c>
+      <c r="M101" s="6">
+        <f t="shared" si="50"/>
+        <v>310.8000000000003</v>
+      </c>
+      <c r="N101" s="6">
+        <f t="shared" si="50"/>
+        <v>897.50000000000045</v>
+      </c>
+      <c r="O101" s="6">
+        <f t="shared" si="50"/>
+        <v>116.99999999999955</v>
+      </c>
+      <c r="P101" s="6">
+        <f>+P100+P98+P99</f>
+        <v>173.59999999999985</v>
+      </c>
+      <c r="Q101" s="6">
+        <f>+Q100+Q98+Q99</f>
+        <v>22.200000000000038</v>
+      </c>
+      <c r="R101" s="6">
+        <f>+R100+R98+R99</f>
+        <v>99.600000000000009</v>
+      </c>
+      <c r="S101" s="6">
+        <f>+S100+S98+S99</f>
+        <v>160.10000000000028</v>
+      </c>
+      <c r="T101" s="6">
+        <f>+T100+T98</f>
+        <v>4.6000000000002785</v>
+      </c>
       <c r="U101" s="6"/>
       <c r="V101" s="6"/>
       <c r="W101" s="6"/>
@@ -27568,36 +27854,68 @@
       <c r="BL367" s="6"/>
     </row>
     <row r="368" spans="3:64" x14ac:dyDescent="0.2">
-      <c r="C368" s="3"/>
-      <c r="D368" s="3"/>
-      <c r="E368" s="3"/>
-      <c r="F368" s="3"/>
-      <c r="G368" s="3"/>
-      <c r="H368" s="3"/>
-      <c r="I368" s="3"/>
-      <c r="J368" s="3"/>
-      <c r="K368" s="3"/>
-      <c r="L368" s="3"/>
-      <c r="M368" s="3"/>
-      <c r="N368" s="3"/>
-      <c r="O368" s="3"/>
-      <c r="P368" s="3"/>
-      <c r="Q368" s="3"/>
-      <c r="R368" s="3"/>
-      <c r="S368" s="3"/>
-      <c r="T368" s="3"/>
-      <c r="U368" s="3"/>
-      <c r="V368" s="3"/>
-      <c r="W368" s="3"/>
-      <c r="X368" s="3"/>
-      <c r="Y368" s="3"/>
-      <c r="Z368" s="3"/>
-      <c r="AA368" s="3"/>
-      <c r="AB368" s="3"/>
-      <c r="AC368" s="3"/>
-      <c r="AD368" s="3"/>
-      <c r="AE368" s="3"/>
-      <c r="AF368" s="3"/>
+      <c r="C368" s="6"/>
+      <c r="D368" s="6"/>
+      <c r="E368" s="6"/>
+      <c r="F368" s="6"/>
+      <c r="G368" s="6"/>
+      <c r="H368" s="6"/>
+      <c r="I368" s="6"/>
+      <c r="J368" s="6"/>
+      <c r="K368" s="6"/>
+      <c r="L368" s="6"/>
+      <c r="M368" s="6"/>
+      <c r="N368" s="6"/>
+      <c r="O368" s="6"/>
+      <c r="P368" s="6"/>
+      <c r="Q368" s="6"/>
+      <c r="R368" s="6"/>
+      <c r="S368" s="6"/>
+      <c r="T368" s="6"/>
+      <c r="U368" s="6"/>
+      <c r="V368" s="6"/>
+      <c r="W368" s="6"/>
+      <c r="X368" s="6"/>
+      <c r="Y368" s="6"/>
+      <c r="Z368" s="6"/>
+      <c r="AA368" s="6"/>
+      <c r="AB368" s="6"/>
+      <c r="AC368" s="6"/>
+      <c r="AD368" s="6"/>
+      <c r="AE368" s="6"/>
+      <c r="AF368" s="6"/>
+      <c r="AG368" s="6"/>
+      <c r="AH368" s="6"/>
+      <c r="AI368" s="6"/>
+      <c r="AJ368" s="6"/>
+      <c r="AK368" s="6"/>
+      <c r="AL368" s="6"/>
+      <c r="AM368" s="6"/>
+      <c r="AN368" s="6"/>
+      <c r="AO368" s="6"/>
+      <c r="AP368" s="6"/>
+      <c r="AQ368" s="6"/>
+      <c r="AR368" s="6"/>
+      <c r="AS368" s="6"/>
+      <c r="AT368" s="6"/>
+      <c r="AU368" s="6"/>
+      <c r="AV368" s="6"/>
+      <c r="AW368" s="6"/>
+      <c r="AX368" s="6"/>
+      <c r="AY368" s="6"/>
+      <c r="AZ368" s="6"/>
+      <c r="BA368" s="6"/>
+      <c r="BB368" s="6"/>
+      <c r="BC368" s="6"/>
+      <c r="BD368" s="6"/>
+      <c r="BE368" s="6"/>
+      <c r="BF368" s="6"/>
+      <c r="BG368" s="6"/>
+      <c r="BH368" s="6"/>
+      <c r="BI368" s="6"/>
+      <c r="BJ368" s="6"/>
+      <c r="BK368" s="6"/>
+      <c r="BL368" s="6"/>
     </row>
     <row r="369" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C369" s="3"/>
@@ -30383,6 +30701,38 @@
       <c r="AE455" s="3"/>
       <c r="AF455" s="3"/>
     </row>
+    <row r="456" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="C456" s="3"/>
+      <c r="D456" s="3"/>
+      <c r="E456" s="3"/>
+      <c r="F456" s="3"/>
+      <c r="G456" s="3"/>
+      <c r="H456" s="3"/>
+      <c r="I456" s="3"/>
+      <c r="J456" s="3"/>
+      <c r="K456" s="3"/>
+      <c r="L456" s="3"/>
+      <c r="M456" s="3"/>
+      <c r="N456" s="3"/>
+      <c r="O456" s="3"/>
+      <c r="P456" s="3"/>
+      <c r="Q456" s="3"/>
+      <c r="R456" s="3"/>
+      <c r="S456" s="3"/>
+      <c r="T456" s="3"/>
+      <c r="U456" s="3"/>
+      <c r="V456" s="3"/>
+      <c r="W456" s="3"/>
+      <c r="X456" s="3"/>
+      <c r="Y456" s="3"/>
+      <c r="Z456" s="3"/>
+      <c r="AA456" s="3"/>
+      <c r="AB456" s="3"/>
+      <c r="AC456" s="3"/>
+      <c r="AD456" s="3"/>
+      <c r="AE456" s="3"/>
+      <c r="AF456" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{045468A1-3DAF-463D-BF7D-92662B42E658}"/>
@@ -30569,35 +30919,35 @@
         <v>6</v>
       </c>
       <c r="C7" s="3">
-        <f>+Model!L56+Model!L63</f>
+        <f>+Model!L57+Model!L64</f>
         <v>2606.3000000000002</v>
       </c>
       <c r="D7" s="3">
-        <f>+Model!M56+Model!M63</f>
+        <f>+Model!M57+Model!M64</f>
         <v>2658.1</v>
       </c>
       <c r="E7" s="3">
-        <f>+Model!N56+Model!N63</f>
+        <f>+Model!N57+Model!N64</f>
         <v>2682.1</v>
       </c>
       <c r="F7" s="3">
-        <f>+Model!O56+Model!O63</f>
+        <f>+Model!O57+Model!O64</f>
         <v>2843.5</v>
       </c>
       <c r="G7" s="3">
-        <f>+Model!P56+Model!P63</f>
+        <f>+Model!P57+Model!P64</f>
         <v>2918</v>
       </c>
       <c r="H7" s="3">
-        <f>+Model!Q56+Model!Q63</f>
+        <f>+Model!Q57+Model!Q64</f>
         <v>3101.1</v>
       </c>
       <c r="I7" s="3">
-        <f>+Model!R56+Model!R63</f>
+        <f>+Model!R57+Model!R64</f>
         <v>3656.7</v>
       </c>
       <c r="J7" s="3">
-        <f>+Model!S56+Model!S63</f>
+        <f>+Model!S57+Model!S64</f>
         <v>4958.3999999999996</v>
       </c>
     </row>
@@ -30658,35 +31008,35 @@
         <v>180</v>
       </c>
       <c r="C14" s="21">
-        <f>+Model!L23/Model!L55</f>
+        <f>+Model!L23/Model!L56</f>
         <v>8.4230960441277467E-2</v>
       </c>
       <c r="D14" s="21">
-        <f>+Model!M23/Model!M55</f>
+        <f>+Model!M23/Model!M56</f>
         <v>7.5468916558934993E-2</v>
       </c>
       <c r="E14" s="21">
-        <f>+Model!N23/Model!N55</f>
+        <f>+Model!N23/Model!N56</f>
         <v>8.2140463818427517E-2</v>
       </c>
       <c r="F14" s="21">
-        <f>+Model!O23/Model!O55</f>
+        <f>+Model!O23/Model!O56</f>
         <v>8.0969387145706673E-2</v>
       </c>
       <c r="G14" s="21">
-        <f>+Model!P23/Model!P55</f>
+        <f>+Model!P23/Model!P56</f>
         <v>0.15506590245099139</v>
       </c>
       <c r="H14" s="21">
-        <f>+Model!Q23/Model!Q55</f>
+        <f>+Model!Q23/Model!Q56</f>
         <v>0.15803502611972264</v>
       </c>
       <c r="I14" s="21">
-        <f>+Model!R23/Model!R55</f>
+        <f>+Model!R23/Model!R56</f>
         <v>0.12533389866440531</v>
       </c>
       <c r="J14" s="21">
-        <f>+Model!S23/Model!S55</f>
+        <f>+Model!S23/Model!S56</f>
         <v>0.10195291309536725</v>
       </c>
     </row>
@@ -30784,14 +31134,14 @@
       </c>
       <c r="J3" s="26">
         <f>+Main!J2</f>
-        <v>86.5</v>
+        <v>100.6</v>
       </c>
       <c r="L3" t="s">
         <v>117</v>
       </c>
       <c r="O3" s="26">
         <f>+J3</f>
-        <v>86.5</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -30800,14 +31150,14 @@
       </c>
       <c r="E4" s="27">
         <f ca="1">+TODAY()</f>
-        <v>46077</v>
+        <v>46085</v>
       </c>
       <c r="G4" t="s">
         <v>119</v>
       </c>
       <c r="J4" s="28">
         <f ca="1">V62</f>
-        <v>107.51271275253276</v>
+        <v>109.2579575150971</v>
       </c>
       <c r="L4" t="s">
         <v>120</v>
@@ -30829,7 +31179,7 @@
       </c>
       <c r="J5" s="31">
         <f ca="1">J4/J3-1</f>
-        <v>0.24292153471136135</v>
+        <v>8.6063195975120355E-2</v>
       </c>
       <c r="L5" t="s">
         <v>122</v>
@@ -31893,11 +32243,11 @@
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3">
-        <f>+Model!R74</f>
+        <f>+Model!R75</f>
         <v>375</v>
       </c>
       <c r="L42" s="3">
-        <f>+Model!S74</f>
+        <f>+Model!S75</f>
         <v>419.8</v>
       </c>
       <c r="M42" s="3">
@@ -32013,11 +32363,11 @@
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3">
-        <f>+Model!R83+Model!R84</f>
+        <f>+Model!R84+Model!R85</f>
         <v>-308.39999999999998</v>
       </c>
       <c r="L45" s="3">
-        <f>+Model!S83+Model!S84</f>
+        <f>+Model!S84+Model!S85</f>
         <v>-264.3</v>
       </c>
       <c r="M45" s="3">
@@ -32129,11 +32479,11 @@
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3">
-        <f>+Model!R76</f>
+        <f>+Model!R77</f>
         <v>-36.700000000000003</v>
       </c>
       <c r="L48" s="3">
-        <f>+Model!S76</f>
+        <f>+Model!S77</f>
         <v>-138.4</v>
       </c>
       <c r="M48" s="3">
@@ -32325,43 +32675,43 @@
       <c r="L52" s="57"/>
       <c r="M52" s="57">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>166.5217540773167</v>
+        <v>196.88723780053093</v>
       </c>
       <c r="N52" s="57">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>1028.6664930770028</v>
+        <v>1026.2069906002448</v>
       </c>
       <c r="O52" s="57">
         <f t="shared" ref="O52:U52" ca="1" si="15">O51/(1+$E$18)^O53</f>
-        <v>953.16803486951585</v>
+        <v>950.88904633600612</v>
       </c>
       <c r="P52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>883.21074790661555</v>
+        <v>881.0990245865745</v>
       </c>
       <c r="Q52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>818.38794072080884</v>
+        <v>816.43120626829375</v>
       </c>
       <c r="R52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>758.32277075964862</v>
+        <v>756.5096498449326</v>
       </c>
       <c r="S52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>702.66605363967437</v>
+        <v>700.98600581961648</v>
       </c>
       <c r="T52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>651.0942331890559</v>
+        <v>649.53749163102054</v>
       </c>
       <c r="U52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>603.30750047793254</v>
+        <v>601.86501518103762</v>
       </c>
       <c r="V52" s="58">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>559.02805090157028</v>
+        <v>557.69143608518141</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -32370,43 +32720,43 @@
       </c>
       <c r="M53" s="74">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.15</v>
+        <v>0.17777777777777778</v>
       </c>
       <c r="N53" s="74">
         <f ca="1">M53+1</f>
-        <v>1.1499999999999999</v>
+        <v>1.1777777777777778</v>
       </c>
       <c r="O53" s="74">
         <f ca="1">N53+1</f>
-        <v>2.15</v>
+        <v>2.177777777777778</v>
       </c>
       <c r="P53" s="74">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.15</v>
+        <v>3.177777777777778</v>
       </c>
       <c r="Q53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>4.1500000000000004</v>
+        <v>4.177777777777778</v>
       </c>
       <c r="R53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>5.15</v>
+        <v>5.177777777777778</v>
       </c>
       <c r="S53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>6.15</v>
+        <v>6.177777777777778</v>
       </c>
       <c r="T53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>7.15</v>
+        <v>7.177777777777778</v>
       </c>
       <c r="U53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>8.15</v>
+        <v>8.1777777777777771</v>
       </c>
       <c r="V53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>9.15</v>
+        <v>9.1777777777777771</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -32419,7 +32769,7 @@
       <c r="Q54" s="59"/>
       <c r="V54" s="3">
         <f ca="1">SUM(M52:V52)</f>
-        <v>7124.3735796191413</v>
+        <v>7138.1031041534388</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -32463,7 +32813,7 @@
       <c r="U56" s="61"/>
       <c r="V56" s="62">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>6363.0916387368807</v>
+        <v>6347.8777285428223</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -32491,7 +32841,7 @@
       <c r="U57" s="64"/>
       <c r="V57" s="65">
         <f ca="1">V54+V56</f>
-        <v>13487.465218356021</v>
+        <v>13485.980832696261</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -32504,7 +32854,7 @@
       <c r="Q58" s="59"/>
       <c r="V58" s="66">
         <f>+Main!J5</f>
-        <v>97.5</v>
+        <v>197.7</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.2">
@@ -32532,7 +32882,7 @@
       <c r="U59" s="61"/>
       <c r="V59" s="62">
         <f>+Main!J6</f>
-        <v>5104.8999999999996</v>
+        <v>5080.6000000000004</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.2">
@@ -32545,7 +32895,7 @@
       <c r="Q60" s="59"/>
       <c r="V60" s="66">
         <f ca="1">V57+V58-V59</f>
-        <v>8480.0652183560214</v>
+        <v>8603.0808326962615</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -32573,7 +32923,7 @@
       <c r="U61" s="61"/>
       <c r="V61" s="62">
         <f>+Main!J3</f>
-        <v>78.875</v>
+        <v>78.741</v>
       </c>
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.2">
@@ -32582,7 +32932,7 @@
       </c>
       <c r="V62" s="66">
         <f ca="1">V60/V61</f>
-        <v>107.51271275253276</v>
+        <v>109.2579575150971</v>
       </c>
     </row>
     <row r="66" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32643,7 +32993,7 @@
       </c>
       <c r="C69" s="68">
         <f ca="1">+J4</f>
-        <v>107.51271275253276</v>
+        <v>109.2579575150971</v>
       </c>
       <c r="D69" s="69">
         <v>-5.0000000000000001E-3</v>
@@ -32671,7 +33021,7 @@
       </c>
       <c r="N69" s="68">
         <f ca="1">+J4</f>
-        <v>107.51271275253276</v>
+        <v>109.2579575150971</v>
       </c>
       <c r="O69" s="69">
         <v>0.08</v>
@@ -32702,25 +33052,25 @@
       </c>
       <c r="D70" s="71">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>184.53115252598974</v>
+        <v>186.41716206359601</v>
       </c>
       <c r="E70" s="71">
-        <v>190.54869094158121</v>
+        <v>192.4351924608635</v>
       </c>
       <c r="F70" s="71">
-        <v>197.5853363583752</v>
+        <v>199.47241317944474</v>
       </c>
       <c r="G70" s="72">
-        <v>205.9468208767326</v>
+        <v>207.83458131573406</v>
       </c>
       <c r="H70" s="71">
-        <v>216.07475753050784</v>
+        <v>217.96334600896739</v>
       </c>
       <c r="I70" s="71">
-        <v>228.63156587048249</v>
+        <v>230.52118096799882</v>
       </c>
       <c r="J70" s="71">
-        <v>244.65819090502785</v>
+        <v>246.54911630674161</v>
       </c>
       <c r="M70" s="79"/>
       <c r="N70" s="70">
@@ -32728,25 +33078,25 @@
       </c>
       <c r="O70" s="71">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>199.69820475572701</v>
+        <v>201.58545432061024</v>
       </c>
       <c r="P70" s="71">
-        <v>202.24393724947006</v>
+        <v>204.1313949482533</v>
       </c>
       <c r="Q70" s="71">
-        <v>204.28052324446449</v>
+        <v>206.16814745036774</v>
       </c>
       <c r="R70" s="72">
-        <v>205.9468208767326</v>
+        <v>207.83458131573406</v>
       </c>
       <c r="S70" s="71">
-        <v>207.3354022369561</v>
+        <v>209.22327620353931</v>
       </c>
       <c r="T70" s="71">
-        <v>208.51035569560676</v>
+        <v>210.39832572399007</v>
       </c>
       <c r="U70" s="71">
-        <v>209.51745866016444</v>
+        <v>211.40551102723344</v>
       </c>
     </row>
     <row r="71" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32755,50 +33105,50 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="71">
-        <v>150.3698084702871</v>
+        <v>152.1965938941056</v>
       </c>
       <c r="E71" s="71">
-        <v>153.83392427564183</v>
+        <v>155.66008943058125</v>
       </c>
       <c r="F71" s="71">
-        <v>157.77275121993577</v>
+        <v>159.59821110637063</v>
       </c>
       <c r="G71" s="72">
-        <v>162.30496708790366</v>
+        <v>164.12961545630219</v>
       </c>
       <c r="H71" s="71">
-        <v>167.59240522236576</v>
+        <v>169.41610684605098</v>
       </c>
       <c r="I71" s="71">
-        <v>173.86163230327026</v>
+        <v>175.6842113875623</v>
       </c>
       <c r="J71" s="71">
-        <v>181.43991131276465</v>
+        <v>183.26113346475691</v>
       </c>
       <c r="M71" s="79"/>
       <c r="N71" s="70">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="71">
-        <v>157.5264878844975</v>
+        <v>159.35199186572927</v>
       </c>
       <c r="P71" s="71">
-        <v>159.47327570810745</v>
+        <v>161.29843110633306</v>
       </c>
       <c r="Q71" s="71">
-        <v>161.03070596699536</v>
+        <v>162.85558249881606</v>
       </c>
       <c r="R71" s="72">
-        <v>162.30496708790366</v>
+        <v>164.12961545630219</v>
       </c>
       <c r="S71" s="71">
-        <v>163.36685135532727</v>
+        <v>165.19130958754059</v>
       </c>
       <c r="T71" s="71">
-        <v>164.26536881237806</v>
+        <v>166.08966616012694</v>
       </c>
       <c r="U71" s="71">
-        <v>165.03552663270725</v>
+        <v>166.85968607948672</v>
       </c>
     </row>
     <row r="72" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32807,50 +33157,50 @@
         <v>0.08</v>
       </c>
       <c r="D72" s="72">
-        <v>124.31620796001758</v>
+        <v>126.09849781091805</v>
       </c>
       <c r="E72" s="72">
-        <v>126.32007854781457</v>
+        <v>128.10149195457313</v>
       </c>
       <c r="F72" s="72">
-        <v>128.54478385345041</v>
+        <v>130.32522422834532</v>
       </c>
       <c r="G72" s="72">
-        <v>131.03764560217627</v>
+        <v>132.81699566011682</v>
       </c>
       <c r="H72" s="72">
-        <v>133.86054605008988</v>
+        <v>135.63866144019516</v>
       </c>
       <c r="I72" s="72">
-        <v>137.09599487198815</v>
+        <v>138.87269515565714</v>
       </c>
       <c r="J72" s="72">
-        <v>140.856505260776</v>
+        <v>142.63156078887999</v>
       </c>
       <c r="M72" s="79"/>
       <c r="N72" s="70">
         <v>0.08</v>
       </c>
       <c r="O72" s="72">
-        <v>127.27600660882996</v>
+        <v>129.0570019159596</v>
       </c>
       <c r="P72" s="72">
-        <v>128.8085261987118</v>
+        <v>130.58885121913477</v>
       </c>
       <c r="Q72" s="72">
-        <v>130.03454187061723</v>
+        <v>131.81433066167489</v>
       </c>
       <c r="R72" s="72">
-        <v>131.03764560217627</v>
+        <v>132.81699566011682</v>
       </c>
       <c r="S72" s="72">
-        <v>131.87356537847543</v>
+        <v>133.65254982548507</v>
       </c>
       <c r="T72" s="72">
-        <v>132.58088211226709</v>
+        <v>134.3595571961813</v>
       </c>
       <c r="U72" s="72">
-        <v>133.18715359837418</v>
+        <v>134.96556351392096</v>
       </c>
     </row>
     <row r="73" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32859,50 +33209,50 @@
         <v>0.09</v>
       </c>
       <c r="D73" s="71">
-        <v>103.80486053792622</v>
+        <v>105.55267576565041</v>
       </c>
       <c r="E73" s="71">
-        <v>104.93898313518808</v>
+        <v>106.68601213345801</v>
       </c>
       <c r="F73" s="71">
-        <v>106.16894398274675</v>
+        <v>107.91512031178291</v>
       </c>
       <c r="G73" s="72">
-        <v>107.51271275253276</v>
+        <v>109.2579575150971</v>
       </c>
       <c r="H73" s="71">
-        <v>108.99305102899173</v>
+        <v>110.73726954839852</v>
       </c>
       <c r="I73" s="71">
-        <v>110.63922370641065</v>
+        <v>112.38230101811291</v>
       </c>
       <c r="J73" s="71">
-        <v>112.48950026193407</v>
+        <v>114.23129487110485</v>
       </c>
       <c r="M73" s="79"/>
       <c r="N73" s="70">
         <v>0.09</v>
       </c>
       <c r="O73" s="71">
-        <v>104.48747108593838</v>
+        <v>106.2348130945239</v>
       </c>
       <c r="P73" s="71">
-        <v>105.71997695010647</v>
+        <v>107.4664645251278</v>
       </c>
       <c r="Q73" s="71">
-        <v>106.70598164144094</v>
+        <v>108.45178566961093</v>
       </c>
       <c r="R73" s="72">
-        <v>107.51271275253276</v>
+        <v>109.2579575150971</v>
       </c>
       <c r="S73" s="71">
-        <v>108.18498867844264</v>
+        <v>109.9297673863356</v>
       </c>
       <c r="T73" s="71">
-        <v>108.75383753882792</v>
+        <v>110.4982218927682</v>
       </c>
       <c r="U73" s="71">
-        <v>109.24142227630104</v>
+        <v>110.98546861256753</v>
       </c>
     </row>
     <row r="74" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32911,50 +33261,50 @@
         <v>0.1</v>
       </c>
       <c r="D74" s="71">
-        <v>87.248049337119639</v>
+        <v>88.968502075179373</v>
       </c>
       <c r="E74" s="71">
-        <v>87.849813015684788</v>
+        <v>89.569696051330695</v>
       </c>
       <c r="F74" s="71">
-        <v>88.483985019656131</v>
+        <v>90.203267671240468</v>
       </c>
       <c r="G74" s="72">
-        <v>89.155966736601371</v>
+        <v>90.874613208868382</v>
       </c>
       <c r="H74" s="71">
-        <v>89.872430468810023</v>
+        <v>91.590398649694251</v>
       </c>
       <c r="I74" s="71">
-        <v>90.641716594144</v>
+        <v>92.358956475567553</v>
       </c>
       <c r="J74" s="71">
-        <v>91.474389591228302</v>
+        <v>93.190841163497822</v>
       </c>
       <c r="M74" s="79"/>
       <c r="N74" s="70">
         <v>0.1</v>
       </c>
       <c r="O74" s="71">
-        <v>86.682438127615598</v>
+        <v>88.403426341781355</v>
       </c>
       <c r="P74" s="71">
-        <v>87.690172005350561</v>
+        <v>89.410206176520518</v>
       </c>
       <c r="Q74" s="71">
-        <v>88.496359107538495</v>
+        <v>90.215630044311851</v>
       </c>
       <c r="R74" s="72">
-        <v>89.155966736601371</v>
+        <v>90.874613208868382</v>
       </c>
       <c r="S74" s="71">
-        <v>89.705639760820446</v>
+        <v>91.423765845998872</v>
       </c>
       <c r="T74" s="71">
-        <v>90.170747704390422</v>
+        <v>91.88843346203231</v>
       </c>
       <c r="U74" s="71">
-        <v>90.569411656021828</v>
+        <v>92.286719990061016</v>
       </c>
     </row>
     <row r="75" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32963,50 +33313,50 @@
         <v>0.11</v>
       </c>
       <c r="D75" s="71">
-        <v>73.610669319064939</v>
+        <v>75.308978993630291</v>
       </c>
       <c r="E75" s="71">
-        <v>73.881198815032661</v>
+        <v>75.579184439646355</v>
       </c>
       <c r="F75" s="71">
-        <v>74.151728311000369</v>
+        <v>75.849389885662418</v>
       </c>
       <c r="G75" s="72">
-        <v>74.422257806968076</v>
+        <v>76.119595331678454</v>
       </c>
       <c r="H75" s="71">
-        <v>74.692787302935784</v>
+        <v>76.389800777694518</v>
       </c>
       <c r="I75" s="71">
-        <v>74.96331679890352</v>
+        <v>76.660006223710582</v>
       </c>
       <c r="J75" s="71">
-        <v>75.233846294871242</v>
+        <v>76.930211669726646</v>
       </c>
       <c r="M75" s="79"/>
       <c r="N75" s="70">
         <v>0.11</v>
       </c>
       <c r="O75" s="71">
-        <v>72.372996875012632</v>
+        <v>74.072789078106837</v>
       </c>
       <c r="P75" s="71">
-        <v>73.207880958401887</v>
+        <v>74.906673107339728</v>
       </c>
       <c r="Q75" s="71">
-        <v>73.875788225113297</v>
+        <v>75.573780330726024</v>
       </c>
       <c r="R75" s="72">
-        <v>74.422257806968076</v>
+        <v>76.119595331678454</v>
       </c>
       <c r="S75" s="71">
-        <v>74.877649125180383</v>
+        <v>76.574441165805496</v>
       </c>
       <c r="T75" s="71">
-        <v>75.262980240590849</v>
+        <v>76.959310717759138</v>
       </c>
       <c r="U75" s="71">
-        <v>75.593264053799786</v>
+        <v>77.289198905147998</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -33015,50 +33365,50 @@
         <v>0.12</v>
       </c>
       <c r="D76" s="71">
-        <v>62.189147682629788</v>
+        <v>63.869250204873325</v>
       </c>
       <c r="E76" s="71">
-        <v>62.252282264622771</v>
+        <v>63.932293454091585</v>
       </c>
       <c r="F76" s="71">
-        <v>62.299235901116418</v>
+        <v>63.97917916575274</v>
       </c>
       <c r="G76" s="72">
-        <v>62.327802099542595</v>
+        <v>64.007704039280839</v>
       </c>
       <c r="H76" s="71">
-        <v>62.335354083034574</v>
+        <v>64.015245097799777</v>
       </c>
       <c r="I76" s="71">
-        <v>62.318739719352216</v>
+        <v>63.998654769058149</v>
       </c>
       <c r="J76" s="71">
-        <v>62.274143269467977</v>
+        <v>63.954122834014782</v>
       </c>
       <c r="M76" s="80"/>
       <c r="N76" s="70">
         <v>0.12</v>
       </c>
       <c r="O76" s="71">
-        <v>60.611613850989336</v>
+        <v>62.2939984908543</v>
       </c>
       <c r="P76" s="71">
-        <v>61.31080165595548</v>
+        <v>62.992174825398443</v>
       </c>
       <c r="Q76" s="71">
-        <v>61.870151899928402</v>
+        <v>63.550715893033775</v>
       </c>
       <c r="R76" s="72">
-        <v>62.327802099542595</v>
+        <v>64.007704039280839</v>
       </c>
       <c r="S76" s="71">
-        <v>62.709177265887774</v>
+        <v>64.388527494486766</v>
       </c>
       <c r="T76" s="71">
-        <v>63.031879329718308</v>
+        <v>64.710762725814845</v>
       </c>
       <c r="U76" s="71">
-        <v>63.308481098715887</v>
+        <v>64.986964352667485</v>
       </c>
     </row>
   </sheetData>

--- a/STG.CO.xlsx
+++ b/STG.CO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D1EEB2-B5B3-4EB6-BA47-F50CA7A7EB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B610A1C-33E1-41C0-893D-38188E2D9C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{BD75BBDC-C4FD-4EC4-8461-B3C83FDDB12A}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{BD75BBDC-C4FD-4EC4-8461-B3C83FDDB12A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -43,6 +43,7 @@
   <authors>
     <author>tc={5C9504E1-4EE8-490C-9943-0CDEEA70D87B}</author>
     <author>tc={7F70D672-7BA8-4A02-A1F8-509A8E4A96A4}</author>
+    <author>tc={D47EDD5F-1443-4F85-B04F-6D5E5C1791E6}</author>
     <author>tc={301E1A6D-A607-4725-84D3-35AEB480AC53}</author>
   </authors>
   <commentList>
@@ -62,7 +63,15 @@
     Changed reporting from Accessires to Next Gen</t>
       </text>
     </comment>
-    <comment ref="O83" authorId="2" shapeId="0" xr:uid="{301E1A6D-A607-4725-84D3-35AEB480AC53}">
+    <comment ref="U10" authorId="2" shapeId="0" xr:uid="{D47EDD5F-1443-4F85-B04F-6D5E5C1791E6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Guidance Q425: -2% - +2%</t>
+      </text>
+    </comment>
+    <comment ref="O83" authorId="3" shapeId="0" xr:uid="{301E1A6D-A607-4725-84D3-35AEB480AC53}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -682,7 +691,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0;[Red]#,##0.0"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -771,6 +780,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1005,7 +1020,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1133,7 +1148,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1610,6 +1624,9 @@
   <threadedComment ref="R8" dT="2025-11-16T11:33:29.05" personId="{10C33167-272C-4E0C-8732-ACA733750BD3}" id="{7F70D672-7BA8-4A02-A1F8-509A8E4A96A4}">
     <text>Changed reporting from Accessires to Next Gen</text>
   </threadedComment>
+  <threadedComment ref="U10" dT="2026-03-07T14:25:15.91" personId="{10C33167-272C-4E0C-8732-ACA733750BD3}" id="{D47EDD5F-1443-4F85-B04F-6D5E5C1791E6}">
+    <text>Guidance Q425: -2% - +2%</text>
+  </threadedComment>
   <threadedComment ref="O83" dT="2025-11-16T11:45:23.70" personId="{10C33167-272C-4E0C-8732-ACA733750BD3}" id="{301E1A6D-A607-4725-84D3-35AEB480AC53}">
     <text>Roayl Agio Cigars</text>
   </threadedComment>
@@ -1637,7 +1654,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>100.6</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1660,7 +1677,7 @@
       </c>
       <c r="J4" s="6">
         <f>+J2*J3</f>
-        <v>7921.3445999999994</v>
+        <v>5212.6541999999999</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1710,7 +1727,7 @@
       </c>
       <c r="J7" s="6">
         <f>+J4-J5+J6</f>
-        <v>12804.2446</v>
+        <v>10095.5542</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -2614,7 +2631,7 @@
       <c r="I11" s="6">
         <v>1307.0999999999999</v>
       </c>
-      <c r="J11" s="81">
+      <c r="J11" s="6">
         <f>+T11-SUM(G11:I11)</f>
         <v>1322.4</v>
       </c>
@@ -2835,7 +2852,7 @@
       <c r="I13" s="6">
         <v>317.60000000000002</v>
       </c>
-      <c r="J13" s="81">
+      <c r="J13" s="6">
         <f>+T13-SUM(G13:I13)</f>
         <v>363.70000000000005</v>
       </c>
@@ -2938,7 +2955,7 @@
       <c r="I14" s="6">
         <v>232.9</v>
       </c>
-      <c r="J14" s="81">
+      <c r="J14" s="6">
         <f>+T14-SUM(G14:I14)</f>
         <v>221.30000000000007</v>
       </c>
@@ -3041,7 +3058,7 @@
       <c r="I15" s="6">
         <v>18.899999999999999</v>
       </c>
-      <c r="J15" s="81">
+      <c r="J15" s="6">
         <f>+T15-SUM(G15:I15)</f>
         <v>20.399999999999999</v>
       </c>
@@ -3150,7 +3167,7 @@
         <f>61.2+50.1+41.3</f>
         <v>152.60000000000002</v>
       </c>
-      <c r="J16" s="81">
+      <c r="J16" s="6">
         <f>+T16-SUM(G16:I16)</f>
         <v>169.99999999999989</v>
       </c>
@@ -3380,7 +3397,7 @@
       <c r="I18" s="6">
         <v>6.7</v>
       </c>
-      <c r="J18" s="81">
+      <c r="J18" s="6">
         <f>+T18-SUM(G18:I18)</f>
         <v>4.8000000000000007</v>
       </c>
@@ -3483,7 +3500,7 @@
       <c r="I19" s="6">
         <v>8.5</v>
       </c>
-      <c r="J19" s="81">
+      <c r="J19" s="6">
         <f>+T19-SUM(G19:I19)</f>
         <v>27.799999999999997</v>
       </c>
@@ -3586,7 +3603,7 @@
       <c r="I20" s="6">
         <v>86.1</v>
       </c>
-      <c r="J20" s="81">
+      <c r="J20" s="6">
         <f>+T20-SUM(G20:I20)</f>
         <v>97.899999999999977</v>
       </c>
@@ -3807,7 +3824,7 @@
       <c r="I22" s="6">
         <v>67.8</v>
       </c>
-      <c r="J22" s="81">
+      <c r="J22" s="6">
         <f>+T22-SUM(G22:I22)</f>
         <v>57.400000000000006</v>
       </c>
@@ -6795,39 +6812,39 @@
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
       <c r="L55" s="7">
-        <f>+L54+L46</f>
+        <f t="shared" ref="L55:T55" si="32">+L54+L46</f>
         <v>12990.400000000001</v>
       </c>
       <c r="M55" s="7">
-        <f>+M54+M46</f>
+        <f t="shared" si="32"/>
         <v>13403.099999999999</v>
       </c>
       <c r="N55" s="7">
-        <f>+N54+N46</f>
+        <f t="shared" si="32"/>
         <v>13872</v>
       </c>
       <c r="O55" s="7">
-        <f>+O54+O46</f>
+        <f t="shared" si="32"/>
         <v>13996</v>
       </c>
       <c r="P55" s="7">
-        <f>+P54+P46</f>
+        <f t="shared" si="32"/>
         <v>14583.700000000004</v>
       </c>
       <c r="Q55" s="7">
-        <f>+Q54+Q46</f>
+        <f t="shared" si="32"/>
         <v>15122.1</v>
       </c>
       <c r="R55" s="7">
-        <f>+R54+R46</f>
+        <f t="shared" si="32"/>
         <v>15853.400000000001</v>
       </c>
       <c r="S55" s="7">
-        <f>+S54+S46</f>
+        <f t="shared" si="32"/>
         <v>17104</v>
       </c>
       <c r="T55" s="7">
-        <f>+T54+T46</f>
+        <f t="shared" si="32"/>
         <v>16303.300000000001</v>
       </c>
       <c r="U55" s="6"/>
@@ -7484,31 +7501,31 @@
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
       <c r="L63" s="6">
-        <f t="shared" ref="L63:P63" si="32">+SUM(L57:L62)</f>
+        <f t="shared" ref="L63:P63" si="33">+SUM(L57:L62)</f>
         <v>3471.7000000000003</v>
       </c>
       <c r="M63" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>3475.7000000000003</v>
       </c>
       <c r="N63" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>3690.2000000000003</v>
       </c>
       <c r="O63" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>3959.8</v>
       </c>
       <c r="P63" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4150</v>
       </c>
       <c r="Q63" s="6">
-        <f t="shared" ref="Q63:R63" si="33">+SUM(Q57:Q62)</f>
+        <f t="shared" ref="Q63:R63" si="34">+SUM(Q57:Q62)</f>
         <v>4303.3</v>
       </c>
       <c r="R63" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4868.7</v>
       </c>
       <c r="S63" s="6">
@@ -8089,39 +8106,39 @@
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
       <c r="L70" s="6">
-        <f t="shared" ref="L70:M70" si="34">+SUM(L64:L69)</f>
+        <f t="shared" ref="L70:M70" si="35">+SUM(L64:L69)</f>
         <v>1070.5</v>
       </c>
       <c r="M70" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1109.2</v>
       </c>
       <c r="N70" s="6">
-        <f t="shared" ref="N70:T70" si="35">+SUM(N64:N69)</f>
+        <f t="shared" ref="N70:T70" si="36">+SUM(N64:N69)</f>
         <v>1079.0999999999999</v>
       </c>
       <c r="O70" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1663.9</v>
       </c>
       <c r="P70" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1465.9</v>
       </c>
       <c r="Q70" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1477.1999999999998</v>
       </c>
       <c r="R70" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1550.6999999999998</v>
       </c>
       <c r="S70" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>2834.2000000000003</v>
       </c>
       <c r="T70" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>2733.7</v>
       </c>
       <c r="U70" s="6"/>
@@ -8183,27 +8200,27 @@
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
       <c r="L71" s="6">
-        <f t="shared" ref="L71" si="36">+L70+L63</f>
+        <f t="shared" ref="L71" si="37">+L70+L63</f>
         <v>4542.2000000000007</v>
       </c>
       <c r="M71" s="6">
-        <f t="shared" ref="M71" si="37">+M70+M63</f>
+        <f t="shared" ref="M71" si="38">+M70+M63</f>
         <v>4584.9000000000005</v>
       </c>
       <c r="N71" s="6">
-        <f t="shared" ref="N71:Q71" si="38">+N70+N63</f>
+        <f t="shared" ref="N71:Q71" si="39">+N70+N63</f>
         <v>4769.3</v>
       </c>
       <c r="O71" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>5623.7000000000007</v>
       </c>
       <c r="P71" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>5615.9</v>
       </c>
       <c r="Q71" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>5780.5</v>
       </c>
       <c r="R71" s="6">
@@ -8278,27 +8295,27 @@
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7">
-        <f t="shared" ref="L72" si="39">+L71+L56</f>
+        <f t="shared" ref="L72" si="40">+L71+L56</f>
         <v>12990.400000000001</v>
       </c>
       <c r="M72" s="7">
-        <f t="shared" ref="M72" si="40">+M71+M56</f>
+        <f t="shared" ref="M72" si="41">+M71+M56</f>
         <v>13403.100000000002</v>
       </c>
       <c r="N72" s="7">
-        <f t="shared" ref="N72:Q72" si="41">+N71+N56</f>
+        <f t="shared" ref="N72:Q72" si="42">+N71+N56</f>
         <v>13872</v>
       </c>
       <c r="O72" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>13996</v>
       </c>
       <c r="P72" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>14583.699999999999</v>
       </c>
       <c r="Q72" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>15122.1</v>
       </c>
       <c r="R72" s="7">
@@ -9116,31 +9133,31 @@
       <c r="J82" s="6"/>
       <c r="K82" s="6"/>
       <c r="L82" s="7">
-        <f t="shared" ref="L82:O82" si="42">+SUM(L74:L81)</f>
+        <f t="shared" ref="L82:O82" si="43">+SUM(L74:L81)</f>
         <v>1048.4999999999998</v>
       </c>
       <c r="M82" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>784.50000000000023</v>
       </c>
       <c r="N82" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1299.6000000000004</v>
       </c>
       <c r="O82" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1585.3999999999999</v>
       </c>
       <c r="P82" s="7">
-        <f t="shared" ref="P82:R82" si="43">+SUM(P74:P81)</f>
+        <f t="shared" ref="P82:R82" si="44">+SUM(P74:P81)</f>
         <v>1566.7</v>
       </c>
       <c r="Q82" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1392.5</v>
       </c>
       <c r="R82" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1347</v>
       </c>
       <c r="S82" s="7">
@@ -9636,31 +9653,31 @@
       <c r="J88" s="6"/>
       <c r="K88" s="6"/>
       <c r="L88" s="7">
-        <f t="shared" ref="L88:P88" si="44">+SUM(L83:L87)</f>
+        <f t="shared" ref="L88:P88" si="45">+SUM(L83:L87)</f>
         <v>-93.7</v>
       </c>
       <c r="M88" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-510.6</v>
       </c>
       <c r="N88" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-49.899999999999991</v>
       </c>
       <c r="O88" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-1751.7</v>
       </c>
       <c r="P88" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-177.50000000000003</v>
       </c>
       <c r="Q88" s="7">
-        <f t="shared" ref="Q88:R88" si="45">+SUM(Q83:Q87)</f>
+        <f t="shared" ref="Q88:R88" si="46">+SUM(Q83:Q87)</f>
         <v>-131.80000000000004</v>
       </c>
       <c r="R88" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-875.30000000000007</v>
       </c>
       <c r="S88" s="7">
@@ -10326,31 +10343,31 @@
       <c r="J96" s="6"/>
       <c r="K96" s="6"/>
       <c r="L96" s="7">
-        <f t="shared" ref="L96:P96" si="46">+SUM(L89:L95)</f>
+        <f t="shared" ref="L96:P96" si="47">+SUM(L89:L95)</f>
         <v>-896.7</v>
       </c>
       <c r="M96" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-572.9</v>
       </c>
       <c r="N96" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-672.5</v>
       </c>
       <c r="O96" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-601.90000000000032</v>
       </c>
       <c r="P96" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-1337.8000000000002</v>
       </c>
       <c r="Q96" s="7">
-        <f t="shared" ref="Q96:R96" si="47">+SUM(Q89:Q95)</f>
+        <f t="shared" ref="Q96:R96" si="48">+SUM(Q89:Q95)</f>
         <v>-1401.5</v>
       </c>
       <c r="R96" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>-386.19999999999993</v>
       </c>
       <c r="S96" s="7">
@@ -10484,31 +10501,31 @@
       <c r="J98" s="6"/>
       <c r="K98" s="6"/>
       <c r="L98" s="7">
-        <f t="shared" ref="L98:O98" si="48">+SUM(L97,L96,L88,L82)</f>
+        <f t="shared" ref="L98:O98" si="49">+SUM(L97,L96,L88,L82)</f>
         <v>58.099999999999682</v>
       </c>
       <c r="M98" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-298.99999999999977</v>
       </c>
       <c r="N98" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>577.20000000000039</v>
       </c>
       <c r="O98" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-768.2000000000005</v>
       </c>
       <c r="P98" s="7">
-        <f t="shared" ref="P98:R98" si="49">+SUM(P97,P96,P88,P82)</f>
+        <f t="shared" ref="P98:R98" si="50">+SUM(P97,P96,P88,P82)</f>
         <v>51.399999999999864</v>
       </c>
       <c r="Q98" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>-140.79999999999995</v>
       </c>
       <c r="R98" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>85.5</v>
       </c>
       <c r="S98" s="7">
@@ -10749,19 +10766,19 @@
       <c r="J101" s="6"/>
       <c r="K101" s="6"/>
       <c r="L101" s="6">
-        <f t="shared" ref="L101:O101" si="50">+L100+L98+L99</f>
+        <f t="shared" ref="L101:O101" si="51">+L100+L98+L99</f>
         <v>605.19999999999959</v>
       </c>
       <c r="M101" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>310.8000000000003</v>
       </c>
       <c r="N101" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>897.50000000000045</v>
       </c>
       <c r="O101" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>116.99999999999955</v>
       </c>
       <c r="P101" s="6">
@@ -31134,14 +31151,14 @@
       </c>
       <c r="J3" s="26">
         <f>+Main!J2</f>
-        <v>100.6</v>
+        <v>66.2</v>
       </c>
       <c r="L3" t="s">
         <v>117</v>
       </c>
       <c r="O3" s="26">
         <f>+J3</f>
-        <v>100.6</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -31150,14 +31167,14 @@
       </c>
       <c r="E4" s="27">
         <f ca="1">+TODAY()</f>
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="G4" t="s">
         <v>119</v>
       </c>
       <c r="J4" s="28">
         <f ca="1">V62</f>
-        <v>109.2579575150971</v>
+        <v>109.25212850067831</v>
       </c>
       <c r="L4" t="s">
         <v>120</v>
@@ -31179,7 +31196,7 @@
       </c>
       <c r="J5" s="31">
         <f ca="1">J4/J3-1</f>
-        <v>8.6063195975120355E-2</v>
+        <v>0.65033426738184752</v>
       </c>
       <c r="L5" t="s">
         <v>122</v>
@@ -32675,43 +32692,43 @@
       <c r="L52" s="57"/>
       <c r="M52" s="57">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>196.88723780053093</v>
+        <v>205.968358291953</v>
       </c>
       <c r="N52" s="57">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>1026.2069906002448</v>
+        <v>1025.4702872101075</v>
       </c>
       <c r="O52" s="57">
         <f t="shared" ref="O52:U52" ca="1" si="15">O51/(1+$E$18)^O53</f>
-        <v>950.88904633600612</v>
+        <v>950.20641291945697</v>
       </c>
       <c r="P52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>881.0990245865745</v>
+        <v>880.46649270518492</v>
       </c>
       <c r="Q52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>816.43120626829375</v>
+        <v>815.8450987451713</v>
       </c>
       <c r="R52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>756.5096498449326</v>
+        <v>755.96655938772744</v>
       </c>
       <c r="S52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>700.98600581961648</v>
+        <v>700.48277521248144</v>
       </c>
       <c r="T52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>649.53749163102054</v>
+        <v>649.0711953803725</v>
       </c>
       <c r="U52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>601.86501518103762</v>
+        <v>601.43294250841871</v>
       </c>
       <c r="V52" s="58">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>557.69143608518141</v>
+        <v>557.29107516835109</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -32720,43 +32737,43 @@
       </c>
       <c r="M53" s="74">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.17777777777777778</v>
+        <v>0.18611111111111112</v>
       </c>
       <c r="N53" s="74">
         <f ca="1">M53+1</f>
-        <v>1.1777777777777778</v>
+        <v>1.1861111111111111</v>
       </c>
       <c r="O53" s="74">
         <f ca="1">N53+1</f>
-        <v>2.177777777777778</v>
+        <v>2.1861111111111109</v>
       </c>
       <c r="P53" s="74">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.177777777777778</v>
+        <v>3.1861111111111109</v>
       </c>
       <c r="Q53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>4.177777777777778</v>
+        <v>4.1861111111111109</v>
       </c>
       <c r="R53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>5.177777777777778</v>
+        <v>5.1861111111111109</v>
       </c>
       <c r="S53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>6.177777777777778</v>
+        <v>6.1861111111111109</v>
       </c>
       <c r="T53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>7.177777777777778</v>
+        <v>7.1861111111111109</v>
       </c>
       <c r="U53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>8.1777777777777771</v>
+        <v>8.18611111111111</v>
       </c>
       <c r="V53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>9.1777777777777771</v>
+        <v>9.18611111111111</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -32769,7 +32786,7 @@
       <c r="Q54" s="59"/>
       <c r="V54" s="3">
         <f ca="1">SUM(M52:V52)</f>
-        <v>7138.1031041534388</v>
+        <v>7142.2011975292244</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -32813,7 +32830,7 @@
       <c r="U56" s="61"/>
       <c r="V56" s="62">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>6347.8777285428223</v>
+        <v>6343.3206527426873</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -32841,7 +32858,7 @@
       <c r="U57" s="64"/>
       <c r="V57" s="65">
         <f ca="1">V54+V56</f>
-        <v>13485.980832696261</v>
+        <v>13485.521850271911</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -32895,7 +32912,7 @@
       <c r="Q60" s="59"/>
       <c r="V60" s="66">
         <f ca="1">V57+V58-V59</f>
-        <v>8603.0808326962615</v>
+        <v>8602.6218502719112</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -32932,7 +32949,7 @@
       </c>
       <c r="V62" s="66">
         <f ca="1">V60/V61</f>
-        <v>109.2579575150971</v>
+        <v>109.25212850067831</v>
       </c>
     </row>
     <row r="66" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -32993,7 +33010,7 @@
       </c>
       <c r="C69" s="68">
         <f ca="1">+J4</f>
-        <v>109.2579575150971</v>
+        <v>109.25212850067831</v>
       </c>
       <c r="D69" s="69">
         <v>-5.0000000000000001E-3</v>
@@ -33021,7 +33038,7 @@
       </c>
       <c r="N69" s="68">
         <f ca="1">+J4</f>
-        <v>109.2579575150971</v>
+        <v>109.25212850067831</v>
       </c>
       <c r="O69" s="69">
         <v>0.08</v>
@@ -33052,25 +33069,25 @@
       </c>
       <c r="D70" s="71">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>186.41716206359601</v>
+        <v>186.41429444338132</v>
       </c>
       <c r="E70" s="71">
-        <v>192.4351924608635</v>
+        <v>192.42940334950404</v>
       </c>
       <c r="F70" s="71">
-        <v>199.47241317944474</v>
+        <v>199.46320780451472</v>
       </c>
       <c r="G70" s="72">
-        <v>207.83458131573406</v>
+        <v>207.82131647307983</v>
       </c>
       <c r="H70" s="71">
-        <v>217.96334600896739</v>
+        <v>217.94516409305083</v>
       </c>
       <c r="I70" s="71">
-        <v>230.52118096799882</v>
+        <v>230.49690277120493</v>
       </c>
       <c r="J70" s="71">
-        <v>246.54911630674161</v>
+        <v>246.51705724676341</v>
       </c>
       <c r="M70" s="79"/>
       <c r="N70" s="70">
@@ -33078,25 +33095,25 @@
       </c>
       <c r="O70" s="71">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>201.58545432061024</v>
+        <v>201.57522315641449</v>
       </c>
       <c r="P70" s="71">
-        <v>204.1313949482533</v>
+        <v>204.11992784098186</v>
       </c>
       <c r="Q70" s="71">
-        <v>206.16814745036774</v>
+        <v>206.15569158863576</v>
       </c>
       <c r="R70" s="72">
-        <v>207.83458131573406</v>
+        <v>207.82131647307983</v>
       </c>
       <c r="S70" s="71">
-        <v>209.22327620353931</v>
+        <v>209.20933721011662</v>
       </c>
       <c r="T70" s="71">
-        <v>210.39832572399007</v>
+        <v>210.38381629530153</v>
       </c>
       <c r="U70" s="71">
-        <v>211.40551102723344</v>
+        <v>211.39051265403154</v>
       </c>
     </row>
     <row r="71" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -33105,50 +33122,50 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="71">
-        <v>152.1965938941056</v>
+        <v>152.19338072219506</v>
       </c>
       <c r="E71" s="71">
-        <v>155.66008943058125</v>
+        <v>155.65492401385686</v>
       </c>
       <c r="F71" s="71">
-        <v>159.59821110637063</v>
+        <v>159.59082591556628</v>
       </c>
       <c r="G71" s="72">
-        <v>164.12961545630219</v>
+        <v>164.11967607983522</v>
       </c>
       <c r="H71" s="71">
-        <v>169.41610684605098</v>
+        <v>169.40318766917994</v>
       </c>
       <c r="I71" s="71">
-        <v>175.6842113875623</v>
+        <v>175.66775911112319</v>
       </c>
       <c r="J71" s="71">
-        <v>183.26113346475691</v>
+        <v>183.24041035653104</v>
       </c>
       <c r="M71" s="79"/>
       <c r="N71" s="70">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="71">
-        <v>159.35199186572927</v>
+        <v>159.3447454596384</v>
       </c>
       <c r="P71" s="71">
-        <v>161.29843110633306</v>
+        <v>161.29008756416303</v>
       </c>
       <c r="Q71" s="71">
-        <v>162.85558249881606</v>
+        <v>162.84636124778277</v>
       </c>
       <c r="R71" s="72">
-        <v>164.12961545630219</v>
+        <v>164.11967607983522</v>
       </c>
       <c r="S71" s="71">
-        <v>165.19130958754059</v>
+        <v>165.18077177321231</v>
       </c>
       <c r="T71" s="71">
-        <v>166.08966616012694</v>
+        <v>166.07862197530062</v>
       </c>
       <c r="U71" s="71">
-        <v>166.85968607948672</v>
+        <v>166.84820786280486</v>
       </c>
     </row>
     <row r="72" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -33157,50 +33174,50 @@
         <v>0.08</v>
       </c>
       <c r="D72" s="72">
-        <v>126.09849781091805</v>
+        <v>126.09521833293665</v>
       </c>
       <c r="E72" s="72">
-        <v>128.10149195457313</v>
+        <v>128.09692828415001</v>
       </c>
       <c r="F72" s="72">
-        <v>130.32522422834532</v>
+        <v>130.31923484223179</v>
       </c>
       <c r="G72" s="72">
-        <v>132.81699566011682</v>
+        <v>132.80940870865373</v>
       </c>
       <c r="H72" s="72">
-        <v>135.63866144019516</v>
+        <v>135.6292654161098</v>
       </c>
       <c r="I72" s="72">
-        <v>138.87269515565714</v>
+        <v>138.86122567485847</v>
       </c>
       <c r="J72" s="72">
-        <v>142.63156078887999</v>
+        <v>142.6176813625251</v>
       </c>
       <c r="M72" s="79"/>
       <c r="N72" s="70">
         <v>0.08</v>
       </c>
       <c r="O72" s="72">
-        <v>129.0570019159596</v>
+        <v>129.05182563332576</v>
       </c>
       <c r="P72" s="72">
-        <v>130.58885121913477</v>
+        <v>130.58269281216309</v>
       </c>
       <c r="Q72" s="72">
-        <v>131.81433066167489</v>
+        <v>131.80738655523294</v>
       </c>
       <c r="R72" s="72">
-        <v>132.81699566011682</v>
+        <v>132.80940870865373</v>
       </c>
       <c r="S72" s="72">
-        <v>133.65254982548507</v>
+        <v>133.64442716983771</v>
       </c>
       <c r="T72" s="72">
-        <v>134.3595571961813</v>
+        <v>134.35098125237803</v>
       </c>
       <c r="U72" s="72">
-        <v>134.96556351392096</v>
+        <v>134.95659903741259</v>
       </c>
     </row>
     <row r="73" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -33209,50 +33226,50 @@
         <v>0.09</v>
       </c>
       <c r="D73" s="71">
-        <v>105.55267576565041</v>
+        <v>105.54950673469622</v>
       </c>
       <c r="E73" s="71">
-        <v>106.68601213345801</v>
+        <v>106.68202949204121</v>
       </c>
       <c r="F73" s="71">
-        <v>107.91512031178291</v>
+        <v>107.9102553063108</v>
       </c>
       <c r="G73" s="72">
-        <v>109.2579575150971</v>
+        <v>109.25212850067831</v>
       </c>
       <c r="H73" s="71">
-        <v>110.73726954839852</v>
+        <v>110.73037855116343</v>
       </c>
       <c r="I73" s="71">
-        <v>112.38230101811291</v>
+        <v>112.37422906979123</v>
       </c>
       <c r="J73" s="71">
-        <v>114.23129487110485</v>
+        <v>114.22189554921006</v>
       </c>
       <c r="M73" s="79"/>
       <c r="N73" s="70">
         <v>0.09</v>
       </c>
       <c r="O73" s="71">
-        <v>106.2348130945239</v>
+        <v>106.23115436423289</v>
       </c>
       <c r="P73" s="71">
-        <v>107.4664645251278</v>
+        <v>107.46192160500695</v>
       </c>
       <c r="Q73" s="71">
-        <v>108.45178566961093</v>
+        <v>108.44653539762622</v>
       </c>
       <c r="R73" s="72">
-        <v>109.2579575150971</v>
+        <v>109.25212850067831</v>
       </c>
       <c r="S73" s="71">
-        <v>109.9297673863356</v>
+        <v>109.92345608655511</v>
       </c>
       <c r="T73" s="71">
-        <v>110.4982218927682</v>
+        <v>110.49150250537392</v>
       </c>
       <c r="U73" s="71">
-        <v>110.98546861256753</v>
+        <v>110.97839943579002</v>
       </c>
     </row>
     <row r="74" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -33261,50 +33278,50 @@
         <v>0.1</v>
       </c>
       <c r="D74" s="71">
-        <v>88.968502075179373</v>
+        <v>88.965558197850839</v>
       </c>
       <c r="E74" s="71">
-        <v>89.569696051330695</v>
+        <v>89.566274864362811</v>
       </c>
       <c r="F74" s="71">
-        <v>90.203267671240468</v>
+        <v>90.199343468850941</v>
       </c>
       <c r="G74" s="72">
-        <v>90.874613208868382</v>
+        <v>90.870156000977929</v>
       </c>
       <c r="H74" s="71">
-        <v>91.590398649694251</v>
+        <v>91.585373153856537</v>
       </c>
       <c r="I74" s="71">
-        <v>92.358956475567553</v>
+        <v>92.353320793877671</v>
       </c>
       <c r="J74" s="71">
-        <v>93.190841163497822</v>
+        <v>93.184545018469805</v>
       </c>
       <c r="M74" s="79"/>
       <c r="N74" s="70">
         <v>0.1</v>
       </c>
       <c r="O74" s="71">
-        <v>88.403426341781355</v>
+        <v>88.400931098513013</v>
       </c>
       <c r="P74" s="71">
-        <v>89.410206176520518</v>
+        <v>89.406911614332046</v>
       </c>
       <c r="Q74" s="71">
-        <v>90.215630044311851</v>
+        <v>90.211696026987312</v>
       </c>
       <c r="R74" s="72">
-        <v>90.874613208868382</v>
+        <v>90.870156000977929</v>
       </c>
       <c r="S74" s="71">
-        <v>91.423765845998872</v>
+        <v>91.41887264597014</v>
       </c>
       <c r="T74" s="71">
-        <v>91.88843346203231</v>
+        <v>91.88317134557893</v>
       </c>
       <c r="U74" s="71">
-        <v>92.286719990061016</v>
+        <v>92.281141659529354</v>
       </c>
     </row>
     <row r="75" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -33313,50 +33330,50 @@
         <v>0.11</v>
       </c>
       <c r="D75" s="71">
-        <v>75.308978993630291</v>
+        <v>75.306335634784389</v>
       </c>
       <c r="E75" s="71">
-        <v>75.579184439646355</v>
+        <v>75.576306194247707</v>
       </c>
       <c r="F75" s="71">
-        <v>75.849389885662418</v>
+        <v>75.846276753711024</v>
       </c>
       <c r="G75" s="72">
-        <v>76.119595331678454</v>
+        <v>76.116247313174327</v>
       </c>
       <c r="H75" s="71">
-        <v>76.389800777694518</v>
+        <v>76.386217872637673</v>
       </c>
       <c r="I75" s="71">
-        <v>76.660006223710582</v>
+        <v>76.656188432101004</v>
       </c>
       <c r="J75" s="71">
-        <v>76.930211669726646</v>
+        <v>76.926158991564321</v>
       </c>
       <c r="M75" s="79"/>
       <c r="N75" s="70">
         <v>0.11</v>
       </c>
       <c r="O75" s="71">
-        <v>74.072789078106837</v>
+        <v>74.071220325239679</v>
       </c>
       <c r="P75" s="71">
-        <v>74.906673107339728</v>
+        <v>74.904379468472314</v>
       </c>
       <c r="Q75" s="71">
-        <v>75.573780330726024</v>
+        <v>75.570906783058447</v>
       </c>
       <c r="R75" s="72">
-        <v>76.119595331678454</v>
+        <v>76.116247313174327</v>
       </c>
       <c r="S75" s="71">
-        <v>76.574441165805496</v>
+        <v>76.570697754937612</v>
       </c>
       <c r="T75" s="71">
-        <v>76.959310717759138</v>
+        <v>76.955232744121901</v>
       </c>
       <c r="U75" s="71">
-        <v>77.289198905147998</v>
+        <v>77.28483416342273</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -33365,50 +33382,50 @@
         <v>0.12</v>
       </c>
       <c r="D76" s="71">
-        <v>63.869250204873325</v>
+        <v>63.866956885678917</v>
       </c>
       <c r="E76" s="71">
-        <v>63.932293454091585</v>
+        <v>63.929940624597933</v>
       </c>
       <c r="F76" s="71">
-        <v>63.97917916575274</v>
+        <v>63.976782078027412</v>
       </c>
       <c r="G76" s="72">
-        <v>64.007704039280839</v>
+        <v>64.005280025218738</v>
       </c>
       <c r="H76" s="71">
-        <v>64.015245097799777</v>
+        <v>64.012813965280841</v>
       </c>
       <c r="I76" s="71">
-        <v>63.998654769058149</v>
+        <v>63.996239297144257</v>
       </c>
       <c r="J76" s="71">
-        <v>63.954122834014782</v>
+        <v>63.951749398461857</v>
       </c>
       <c r="M76" s="80"/>
       <c r="N76" s="70">
         <v>0.12</v>
       </c>
       <c r="O76" s="71">
-        <v>62.2939984908543</v>
+        <v>62.29319214611062</v>
       </c>
       <c r="P76" s="71">
-        <v>62.992174825398443</v>
+        <v>62.990709430191707</v>
       </c>
       <c r="Q76" s="71">
-        <v>63.550715893033775</v>
+        <v>63.548723257456579</v>
       </c>
       <c r="R76" s="72">
-        <v>64.007704039280839</v>
+        <v>64.005280025218738</v>
       </c>
       <c r="S76" s="71">
-        <v>64.388527494486766</v>
+        <v>64.385743998353902</v>
       </c>
       <c r="T76" s="71">
-        <v>64.710762725814845</v>
+        <v>64.707675052545184</v>
       </c>
       <c r="U76" s="71">
-        <v>64.986964352667485</v>
+        <v>64.983615956137712</v>
       </c>
     </row>
   </sheetData>

--- a/STG.CO.xlsx
+++ b/STG.CO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912F8FD6-9DAD-4846-820B-D6ADACF63E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E82CE1-C347-4867-9FAD-F8B3C5DE5697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{BD75BBDC-C4FD-4EC4-8461-B3C83FDDB12A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{BD75BBDC-C4FD-4EC4-8461-B3C83FDDB12A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1660,7 +1660,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>66.2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="J4" s="6">
         <f>+J2*J3</f>
-        <v>5212.6541999999999</v>
+        <v>5511.87</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="J7" s="6">
         <f>+J4-J5+J6</f>
-        <v>9969.7541999999994</v>
+        <v>10268.970000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -33099,14 +33099,14 @@
       </c>
       <c r="J3" s="26">
         <f>+Main!J2</f>
-        <v>66.2</v>
+        <v>70</v>
       </c>
       <c r="L3" t="s">
         <v>117</v>
       </c>
       <c r="O3" s="26">
         <f>+J3</f>
-        <v>66.2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -33115,14 +33115,14 @@
       </c>
       <c r="E4" s="27">
         <f ca="1">+TODAY()</f>
-        <v>46168</v>
+        <v>46226</v>
       </c>
       <c r="G4" t="s">
         <v>119</v>
       </c>
       <c r="J4" s="28">
         <f ca="1">V62</f>
-        <v>110.66787519039349</v>
+        <v>110.50341825100335</v>
       </c>
       <c r="L4" t="s">
         <v>120</v>
@@ -33144,7 +33144,7 @@
       </c>
       <c r="J5" s="31">
         <f ca="1">J4/J3-1</f>
-        <v>0.67172016903917653</v>
+        <v>0.57862026072861927</v>
       </c>
       <c r="L5" t="s">
         <v>122</v>
@@ -34640,43 +34640,43 @@
       <c r="L52" s="57"/>
       <c r="M52" s="57">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>440.41846955703983</v>
+        <v>604.06384593461837</v>
       </c>
       <c r="N52" s="57">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>1006.259617512503</v>
+        <v>992.62265278540872</v>
       </c>
       <c r="O52" s="57">
         <f t="shared" ref="O52:U52" ca="1" si="15">O51/(1+$E$18)^O53</f>
-        <v>932.40570063085102</v>
+        <v>919.76961404886447</v>
       </c>
       <c r="P52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>863.97225471299043</v>
+        <v>852.26358732968174</v>
       </c>
       <c r="Q52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>800.56144702763333</v>
+        <v>789.71213137887923</v>
       </c>
       <c r="R52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>741.80464357606388</v>
+        <v>731.75160797492481</v>
       </c>
       <c r="S52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>687.36026606589417</v>
+        <v>678.04506794006807</v>
       </c>
       <c r="T52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>636.91180617114935</v>
+        <v>628.28029231143887</v>
       </c>
       <c r="U52" s="57">
         <f t="shared" ca="1" si="15"/>
-        <v>590.16598553473489</v>
+        <v>582.16797727940684</v>
       </c>
       <c r="V52" s="58">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>546.85105081658901</v>
+        <v>539.44005234146857</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -34685,43 +34685,43 @@
       </c>
       <c r="M53" s="74">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.40555555555555556</v>
+        <v>0.56388888888888888</v>
       </c>
       <c r="N53" s="74">
         <f ca="1">M53+1</f>
-        <v>1.4055555555555554</v>
+        <v>1.5638888888888889</v>
       </c>
       <c r="O53" s="74">
         <f ca="1">N53+1</f>
-        <v>2.4055555555555554</v>
+        <v>2.5638888888888891</v>
       </c>
       <c r="P53" s="74">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.4055555555555554</v>
+        <v>3.5638888888888891</v>
       </c>
       <c r="Q53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>4.405555555555555</v>
+        <v>4.5638888888888891</v>
       </c>
       <c r="R53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>5.405555555555555</v>
+        <v>5.5638888888888891</v>
       </c>
       <c r="S53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>6.405555555555555</v>
+        <v>6.5638888888888891</v>
       </c>
       <c r="T53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>7.405555555555555</v>
+        <v>7.5638888888888891</v>
       </c>
       <c r="U53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>8.405555555555555</v>
+        <v>8.56388888888889</v>
       </c>
       <c r="V53" s="74">
         <f t="shared" ca="1" si="16"/>
-        <v>9.405555555555555</v>
+        <v>9.56388888888889</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -34734,7 +34734,7 @@
       <c r="Q54" s="59"/>
       <c r="V54" s="3">
         <f ca="1">SUM(M52:V52)</f>
-        <v>7246.7112416054506</v>
+        <v>7318.1168293247592</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -34778,7 +34778,7 @@
       <c r="U56" s="61"/>
       <c r="V56" s="62">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>6224.4879187613233</v>
+        <v>6140.1328271774955</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -34806,7 +34806,7 @@
       <c r="U57" s="64"/>
       <c r="V57" s="65">
         <f ca="1">V54+V56</f>
-        <v>13471.199160366774</v>
+        <v>13458.249656502256</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -34860,7 +34860,7 @@
       <c r="Q60" s="59"/>
       <c r="V60" s="66">
         <f ca="1">V57+V58-V59</f>
-        <v>8714.0991603667735</v>
+        <v>8701.1496565022553</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -34897,7 +34897,7 @@
       </c>
       <c r="V62" s="66">
         <f ca="1">V60/V61</f>
-        <v>110.66787519039349</v>
+        <v>110.50341825100335</v>
       </c>
     </row>
     <row r="66" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -34958,7 +34958,7 @@
       </c>
       <c r="C69" s="68">
         <f ca="1">+J4</f>
-        <v>110.66787519039349</v>
+        <v>110.50341825100335</v>
       </c>
       <c r="D69" s="69">
         <v>-5.0000000000000001E-3</v>
@@ -34986,7 +34986,7 @@
       </c>
       <c r="N69" s="68">
         <f ca="1">+J4</f>
-        <v>110.66787519039349</v>
+        <v>110.50341825100335</v>
       </c>
       <c r="O69" s="69">
         <v>0.08</v>
@@ -35017,25 +35017,25 @@
       </c>
       <c r="D70" s="71">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>187.91652085971879</v>
+        <v>187.82421948574668</v>
       </c>
       <c r="E70" s="71">
-        <v>193.8552054942061</v>
+        <v>193.70836631488461</v>
       </c>
       <c r="F70" s="71">
-        <v>200.79964275891487</v>
+        <v>200.58902946274534</v>
       </c>
       <c r="G70" s="72">
-        <v>209.0515584429117</v>
+        <v>208.7651638249458</v>
       </c>
       <c r="H70" s="71">
-        <v>219.04677868595908</v>
+        <v>218.66859313959904</v>
       </c>
       <c r="I70" s="71">
-        <v>231.43904269770113</v>
+        <v>230.94705301387512</v>
       </c>
       <c r="J70" s="71">
-        <v>247.25565495043548</v>
+        <v>246.61841368761225</v>
       </c>
       <c r="M70" s="79"/>
       <c r="N70" s="70">
@@ -35043,25 +35043,25 @@
       </c>
       <c r="O70" s="71">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>202.88482414363781</v>
+        <v>202.65506162108613</v>
       </c>
       <c r="P70" s="71">
-        <v>205.39719737667534</v>
+        <v>205.14436251895486</v>
       </c>
       <c r="Q70" s="71">
-        <v>207.40709596310532</v>
+        <v>207.13580323724986</v>
       </c>
       <c r="R70" s="72">
-        <v>209.0515584429117</v>
+        <v>208.7651638249458</v>
       </c>
       <c r="S70" s="71">
-        <v>210.42194384275027</v>
+        <v>210.12296431469238</v>
       </c>
       <c r="T70" s="71">
-        <v>211.58150071953685</v>
+        <v>211.27187242140099</v>
       </c>
       <c r="U70" s="71">
-        <v>212.57540661392528</v>
+        <v>212.2566507985799</v>
       </c>
     </row>
     <row r="71" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35070,50 +35070,50 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="71">
-        <v>153.68344326179752</v>
+        <v>153.57882121539748</v>
       </c>
       <c r="E71" s="71">
-        <v>157.09397158624699</v>
+        <v>156.95300884769208</v>
       </c>
       <c r="F71" s="71">
-        <v>160.97186759591685</v>
+        <v>160.7895841552039</v>
       </c>
       <c r="G71" s="72">
-        <v>165.43397321211205</v>
+        <v>165.20414405673716</v>
       </c>
       <c r="H71" s="71">
-        <v>170.63961832752148</v>
+        <v>170.35432071429778</v>
       </c>
       <c r="I71" s="71">
-        <v>176.8118647919093</v>
+        <v>176.46079915469394</v>
       </c>
       <c r="J71" s="71">
-        <v>184.27291305493492</v>
+        <v>183.84234663887088</v>
       </c>
       <c r="M71" s="79"/>
       <c r="N71" s="70">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="71">
-        <v>160.72941378433023</v>
+        <v>160.54971379652849</v>
       </c>
       <c r="P71" s="71">
-        <v>162.64608614379688</v>
+        <v>162.44596316179869</v>
       </c>
       <c r="Q71" s="71">
-        <v>164.17942403137025</v>
+        <v>163.96296265401486</v>
       </c>
       <c r="R71" s="72">
-        <v>165.43397321211205</v>
+        <v>165.20414405673716</v>
       </c>
       <c r="S71" s="71">
-        <v>166.47943086273025</v>
+        <v>166.23846189233907</v>
       </c>
       <c r="T71" s="71">
-        <v>167.36404887479185</v>
+        <v>167.11365390707917</v>
       </c>
       <c r="U71" s="71">
-        <v>168.12229288513032</v>
+        <v>167.86381849114213</v>
       </c>
     </row>
     <row r="72" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35122,50 +35122,50 @@
         <v>0.08</v>
       </c>
       <c r="D72" s="72">
-        <v>127.5804743463768</v>
+        <v>127.46886127812442</v>
       </c>
       <c r="E72" s="72">
-        <v>129.54866194377291</v>
+        <v>129.41321106191708</v>
       </c>
       <c r="F72" s="72">
-        <v>131.73375184782091</v>
+        <v>131.57183612800529</v>
       </c>
       <c r="G72" s="72">
-        <v>134.18222312423177</v>
+        <v>133.9906526083094</v>
       </c>
       <c r="H72" s="72">
-        <v>136.95485608970469</v>
+        <v>136.72970467534094</v>
       </c>
       <c r="I72" s="72">
-        <v>140.1326911665052</v>
+        <v>139.86905122578167</v>
       </c>
       <c r="J72" s="72">
-        <v>143.82623802135899</v>
+        <v>143.5178634823796</v>
       </c>
       <c r="M72" s="79"/>
       <c r="N72" s="70">
         <v>0.08</v>
       </c>
       <c r="O72" s="72">
-        <v>130.48756776191854</v>
+        <v>130.34074527000183</v>
       </c>
       <c r="P72" s="72">
-        <v>131.99279772434244</v>
+        <v>131.827744555979</v>
       </c>
       <c r="Q72" s="72">
-        <v>133.19698169428156</v>
+        <v>133.01734398476074</v>
       </c>
       <c r="R72" s="72">
-        <v>134.18222312423177</v>
+        <v>133.9906526083094</v>
       </c>
       <c r="S72" s="72">
-        <v>135.00325764919023</v>
+        <v>134.80174312793332</v>
       </c>
       <c r="T72" s="72">
-        <v>135.697979170309</v>
+        <v>135.48805049069202</v>
       </c>
       <c r="U72" s="72">
-        <v>136.29345475983934</v>
+        <v>136.07631394448518</v>
       </c>
     </row>
     <row r="73" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35174,50 +35174,50 @@
         <v>0.09</v>
       </c>
       <c r="D73" s="71">
-        <v>107.03461656895939</v>
+        <v>106.91939803564519</v>
       </c>
       <c r="E73" s="71">
-        <v>108.14592318685332</v>
+        <v>108.01564407783336</v>
       </c>
       <c r="F73" s="71">
-        <v>109.35114000639504</v>
+        <v>109.20452763807445</v>
       </c>
       <c r="G73" s="72">
-        <v>110.66787519039349</v>
+        <v>110.50341825100335</v>
       </c>
       <c r="H73" s="71">
-        <v>112.11843241174006</v>
+        <v>111.9343173271577</v>
       </c>
       <c r="I73" s="71">
-        <v>113.73148782129502</v>
+        <v>113.52551239437145</v>
       </c>
       <c r="J73" s="71">
-        <v>115.54454100095262</v>
+        <v>115.31399483519681</v>
       </c>
       <c r="M73" s="79"/>
       <c r="N73" s="70">
         <v>0.09</v>
       </c>
       <c r="O73" s="71">
-        <v>107.7034945379564</v>
+        <v>107.57921128107466</v>
       </c>
       <c r="P73" s="71">
-        <v>108.91120517413447</v>
+        <v>108.77055486141599</v>
       </c>
       <c r="Q73" s="71">
-        <v>109.87737368307694</v>
+        <v>109.72362972568904</v>
       </c>
       <c r="R73" s="72">
-        <v>110.66787519039349</v>
+        <v>110.50341825100335</v>
       </c>
       <c r="S73" s="71">
-        <v>111.32662644649064</v>
+        <v>111.15324202209861</v>
       </c>
       <c r="T73" s="71">
-        <v>111.88403135549588</v>
+        <v>111.70309290533309</v>
       </c>
       <c r="U73" s="71">
-        <v>112.36180699178615</v>
+        <v>112.1743936623912</v>
       </c>
     </row>
     <row r="74" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35226,50 +35226,50 @@
         <v>0.1</v>
       </c>
       <c r="D74" s="71">
-        <v>90.453550399488037</v>
+        <v>90.336936582506851</v>
       </c>
       <c r="E74" s="71">
-        <v>91.041833383329816</v>
+        <v>90.916408567787315</v>
       </c>
       <c r="F74" s="71">
-        <v>91.661798682090847</v>
+        <v>91.527088346644717</v>
       </c>
       <c r="G74" s="72">
-        <v>92.318726681591002</v>
+        <v>92.174177218008509</v>
       </c>
       <c r="H74" s="71">
-        <v>93.019140211372516</v>
+        <v>92.864100315850436</v>
       </c>
       <c r="I74" s="71">
-        <v>93.771192808363153</v>
+        <v>93.60488905763512</v>
       </c>
       <c r="J74" s="71">
-        <v>94.585212286004676</v>
+        <v>94.406716572151097</v>
       </c>
       <c r="M74" s="79"/>
       <c r="N74" s="70">
         <v>0.1</v>
       </c>
       <c r="O74" s="71">
-        <v>89.900609998008832</v>
+        <v>89.792277836652133</v>
       </c>
       <c r="P74" s="71">
-        <v>90.885768646875647</v>
+        <v>90.762681288315846</v>
       </c>
       <c r="Q74" s="71">
-        <v>91.673895565969104</v>
+        <v>91.539004049646806</v>
       </c>
       <c r="R74" s="72">
-        <v>92.318726681591002</v>
+        <v>92.174177218008509</v>
       </c>
       <c r="S74" s="71">
-        <v>92.856085944609262</v>
+        <v>92.70348819164326</v>
       </c>
       <c r="T74" s="71">
-        <v>93.310774551778579</v>
+        <v>93.151366707795745</v>
       </c>
       <c r="U74" s="71">
-        <v>93.700507643637977</v>
+        <v>93.535262578783588</v>
       </c>
     </row>
     <row r="75" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35278,50 +35278,50 @@
         <v>0.11</v>
       </c>
       <c r="D75" s="71">
-        <v>76.799204763187376</v>
+        <v>76.682661715033532</v>
       </c>
       <c r="E75" s="71">
-        <v>77.0630629238225</v>
+        <v>76.942195793966235</v>
       </c>
       <c r="F75" s="71">
-        <v>77.326921084457624</v>
+        <v>77.201729872898952</v>
       </c>
       <c r="G75" s="72">
-        <v>77.590779245092762</v>
+        <v>77.461263951831654</v>
       </c>
       <c r="H75" s="71">
-        <v>77.854637405727885</v>
+        <v>77.720798030764371</v>
       </c>
       <c r="I75" s="71">
-        <v>78.118495566363009</v>
+        <v>77.980332109697059</v>
       </c>
       <c r="J75" s="71">
-        <v>78.382353726998133</v>
+        <v>78.239866188629776</v>
       </c>
       <c r="M75" s="79"/>
       <c r="N75" s="70">
         <v>0.11</v>
       </c>
       <c r="O75" s="71">
-        <v>75.592053678281673</v>
+        <v>75.495293303916398</v>
       </c>
       <c r="P75" s="71">
-        <v>76.406349279575053</v>
+        <v>76.296244308622619</v>
       </c>
       <c r="Q75" s="71">
-        <v>77.057785760609818</v>
+        <v>76.937005112387581</v>
       </c>
       <c r="R75" s="72">
-        <v>77.590779245092762</v>
+        <v>77.461263951831654</v>
       </c>
       <c r="S75" s="71">
-        <v>78.034940482161886</v>
+        <v>77.898146318035046</v>
       </c>
       <c r="T75" s="71">
-        <v>78.410769221220392</v>
+        <v>78.267816012514857</v>
       </c>
       <c r="U75" s="71">
-        <v>78.732908140413414</v>
+        <v>78.5846757506404</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -35330,50 +35330,50 @@
         <v>0.12</v>
       </c>
       <c r="D76" s="71">
-        <v>65.366018799663181</v>
+        <v>65.250524604423859</v>
       </c>
       <c r="E76" s="71">
-        <v>65.427455490683087</v>
+        <v>65.310868725065689</v>
       </c>
       <c r="F76" s="71">
-        <v>65.473146393615522</v>
+        <v>65.355747075657447</v>
       </c>
       <c r="G76" s="72">
-        <v>65.500944355539445</v>
+        <v>65.383050687555922</v>
       </c>
       <c r="H76" s="71">
-        <v>65.508293242025047</v>
+        <v>65.39026888380495</v>
       </c>
       <c r="I76" s="71">
-        <v>65.492125691756684</v>
+        <v>65.374388852057109</v>
       </c>
       <c r="J76" s="71">
-        <v>65.448728583141502</v>
+        <v>65.331763503681287</v>
       </c>
       <c r="M76" s="80"/>
       <c r="N76" s="70">
         <v>0.12</v>
       </c>
       <c r="O76" s="71">
-        <v>63.830909901678844</v>
+        <v>63.742715589965364</v>
       </c>
       <c r="P76" s="71">
-        <v>64.511294308807223</v>
+        <v>64.411000259354111</v>
       </c>
       <c r="Q76" s="71">
-        <v>65.055601834509943</v>
+        <v>64.945627994865106</v>
       </c>
       <c r="R76" s="72">
-        <v>65.500944355539445</v>
+        <v>65.383050687555922</v>
       </c>
       <c r="S76" s="71">
-        <v>65.872063123063995</v>
+        <v>65.747569598131591</v>
       </c>
       <c r="T76" s="71">
-        <v>66.186086695584819</v>
+        <v>66.056008676311038</v>
       </c>
       <c r="U76" s="71">
-        <v>66.455249757745491</v>
+        <v>66.320385029036245</v>
       </c>
     </row>
   </sheetData>
